--- a/wwwroot/ExcelModel/Woolworth_WET_sheet.xlsx
+++ b/wwwroot/ExcelModel/Woolworth_WET_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E8B9BF-DF37-4465-A48F-FE8A59BD2573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8A3662-FAAB-4597-B1F4-D38EA414211E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="768" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10363" yWindow="1689" windowWidth="20494" windowHeight="13054" tabRatio="768" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppearanceAfterWashing" sheetId="25" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="272">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -369,13 +369,7 @@
     <t xml:space="preserve">°C with </t>
   </si>
   <si>
-    <t xml:space="preserve">,using domestic washing </t>
-  </si>
-  <si>
     <t>Warp3</t>
-  </si>
-  <si>
-    <t>machine,</t>
   </si>
   <si>
     <t>Weft2</t>
@@ -450,9 +444,6 @@
     <t>, with 4.0kg total dry ballast,</t>
   </si>
   <si>
-    <t>，</t>
-  </si>
-  <si>
     <t>(cotton&lt;=±5%, synthetics &lt;=±3%;)</t>
   </si>
   <si>
@@ -1489,6 +1480,10 @@
   </si>
   <si>
     <t xml:space="preserve"> ,with 4.0kg total dry </t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>using domestic washing machine,</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2156,7 +2151,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2688,27 +2683,30 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2727,6 +2725,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2787,7 +2788,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2958,11 +2959,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2990,13 +2991,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>21578</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>79780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>81928</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>70890</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -3012,8 +3013,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1721791" y="7299730"/>
-          <a:ext cx="2636862" cy="915035"/>
+          <a:off x="1749685" y="7635146"/>
+          <a:ext cx="2734154" cy="923200"/>
           <a:chOff x="123825" y="8001389"/>
           <a:chExt cx="2749122" cy="893069"/>
         </a:xfrm>
@@ -3844,13 +3845,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>85576</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>65075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>35544</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>141275</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -3868,8 +3869,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="252264" y="7285025"/>
-          <a:ext cx="1088205" cy="1000125"/>
+          <a:off x="259067" y="7620441"/>
+          <a:ext cx="1103173" cy="1008290"/>
           <a:chOff x="8094" y="10480"/>
           <a:chExt cx="2840" cy="3834"/>
         </a:xfrm>
@@ -4439,13 +4440,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>106874</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>72718</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>124458</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>133186</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -4463,8 +4464,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4550287" y="7218373"/>
-          <a:ext cx="1517771" cy="1249188"/>
+          <a:off x="4682276" y="7558007"/>
+          <a:ext cx="1579003" cy="1253135"/>
           <a:chOff x="8181" y="12784"/>
           <a:chExt cx="2520" cy="2160"/>
         </a:xfrm>
@@ -5220,15 +5221,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>20490</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>153730</xdr:rowOff>
+      <xdr:colOff>80</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>12216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>384</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>16204</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>153465</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>26409</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5243,8 +5244,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="187178" y="5923023"/>
-          <a:ext cx="3089806" cy="1070244"/>
+          <a:off x="173571" y="6240885"/>
+          <a:ext cx="3167367" cy="1095962"/>
           <a:chOff x="267953" y="6243120"/>
           <a:chExt cx="3203740" cy="1122705"/>
         </a:xfrm>
@@ -7448,13 +7449,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>165686</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>164158</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>137502</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>23432</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -7472,8 +7473,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4109036" y="5918211"/>
-          <a:ext cx="1305316" cy="1082284"/>
+          <a:off x="4220615" y="6230222"/>
+          <a:ext cx="1359744" cy="1103648"/>
           <a:chOff x="7506" y="10231"/>
           <a:chExt cx="2159" cy="1763"/>
         </a:xfrm>
@@ -8436,23 +8437,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CA54"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="1.6640625" style="8" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="1.640625" style="8" hidden="1" customWidth="1"/>
     <col min="5" max="6" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.88671875" style="8" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" style="8" hidden="1" customWidth="1"/>
     <col min="8" max="13" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.44140625" style="8" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="8" hidden="1" customWidth="1"/>
     <col min="15" max="42" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="2.33203125" style="8" hidden="1" customWidth="1"/>
-    <col min="44" max="58" width="2.33203125" style="8" customWidth="1"/>
-    <col min="59" max="59" width="2.88671875" style="8" customWidth="1"/>
-    <col min="60" max="115" width="2.33203125" style="8" customWidth="1"/>
-    <col min="116" max="16384" width="8.88671875" style="8"/>
+    <col min="43" max="43" width="2.35546875" style="8" hidden="1" customWidth="1"/>
+    <col min="44" max="58" width="2.35546875" style="8" customWidth="1"/>
+    <col min="59" max="59" width="2.85546875" style="8" customWidth="1"/>
+    <col min="60" max="115" width="2.35546875" style="8" customWidth="1"/>
+    <col min="116" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -8485,7 +8486,7 @@
       <c r="BZ1" s="120"/>
       <c r="CA1" s="120"/>
     </row>
-    <row r="2" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.35">
       <c r="AR2" s="63" t="s">
         <v>2</v>
       </c>
@@ -8525,15 +8526,15 @@
       <c r="BZ2" s="63"/>
       <c r="CA2" s="63"/>
     </row>
-    <row r="3" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A3" s="63" t="s">
         <v>3</v>
       </c>
       <c r="AR3" s="90" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:79" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A4" s="121"/>
       <c r="B4" s="121"/>
       <c r="C4" s="121"/>
@@ -8563,7 +8564,7 @@
       <c r="BI4" s="122"/>
       <c r="BJ4" s="122"/>
     </row>
-    <row r="5" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
@@ -8617,7 +8618,7 @@
       <c r="BZ5" s="124"/>
       <c r="CA5" s="124"/>
     </row>
-    <row r="6" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8699,7 +8700,7 @@
       </c>
       <c r="CA6" s="127"/>
     </row>
-    <row r="7" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -8752,7 +8753,7 @@
       <c r="BZ7" s="128"/>
       <c r="CA7" s="128"/>
     </row>
-    <row r="8" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.35">
       <c r="N8" s="70"/>
       <c r="O8" s="70"/>
       <c r="P8" s="70"/>
@@ -8797,7 +8798,7 @@
       <c r="BZ8" s="128"/>
       <c r="CA8" s="128"/>
     </row>
-    <row r="9" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A9" s="121"/>
       <c r="B9" s="121"/>
       <c r="C9" s="121"/>
@@ -8846,7 +8847,7 @@
       <c r="BZ9" s="128"/>
       <c r="CA9" s="128"/>
     </row>
-    <row r="10" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>22</v>
       </c>
@@ -8892,7 +8893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A11" s="121"/>
       <c r="B11" s="121"/>
       <c r="C11" s="8" t="s">
@@ -8902,7 +8903,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:79" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:79" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="121"/>
       <c r="B12" s="121"/>
       <c r="C12" s="121"/>
@@ -8913,7 +8914,7 @@
       <c r="H12" s="121"/>
       <c r="I12" s="121"/>
     </row>
-    <row r="13" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>32</v>
       </c>
@@ -8952,7 +8953,7 @@
       <c r="BT13" s="120"/>
       <c r="BU13" s="82"/>
     </row>
-    <row r="14" spans="1:79" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A14" s="121"/>
       <c r="B14" s="121"/>
       <c r="C14" s="121"/>
@@ -8963,10 +8964,10 @@
       <c r="H14" s="121"/>
       <c r="I14" s="121"/>
       <c r="AR14" s="20" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="1:79" ht="14.4" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
@@ -8981,10 +8982,10 @@
         <v>38</v>
       </c>
       <c r="AR15" s="20" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:79" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A16" s="121"/>
       <c r="B16" s="121"/>
       <c r="C16" s="121"/>
@@ -9004,7 +9005,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A17" s="121"/>
       <c r="B17" s="121"/>
       <c r="C17" s="121"/>
@@ -9018,7 +9019,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>42</v>
       </c>
@@ -9040,7 +9041,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:63" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>22</v>
       </c>
@@ -9055,18 +9056,18 @@
         <v>46</v>
       </c>
       <c r="AR19" s="20" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:63" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:63" x14ac:dyDescent="0.35">
       <c r="AR20" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BK20" s="20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:63" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>47</v>
       </c>
@@ -9081,24 +9082,24 @@
         <v>49</v>
       </c>
       <c r="AR21" s="20" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BK21" s="20" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:63" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>50</v>
       </c>
       <c r="AR22" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="BK22" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="23" spans="1:63" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>51</v>
       </c>
@@ -9115,21 +9116,21 @@
         <v>18</v>
       </c>
       <c r="AR23" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="BK23" s="20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:63" x14ac:dyDescent="0.35">
+      <c r="AR24" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="BK24" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="BK23" s="20" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="AR24" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="BK24" s="20" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="25" spans="1:63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>53</v>
       </c>
@@ -9139,13 +9140,13 @@
         <v>54</v>
       </c>
       <c r="AR25" s="20" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="BK25" s="20" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="26" spans="1:63" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>55</v>
       </c>
@@ -9162,13 +9163,13 @@
         <v>56</v>
       </c>
       <c r="AR26" s="20" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="BK26" s="20" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:63" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A27" s="121"/>
       <c r="B27" s="121"/>
       <c r="C27" s="121"/>
@@ -9182,21 +9183,21 @@
         <v>18</v>
       </c>
       <c r="AR27" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="BK27" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:63" x14ac:dyDescent="0.35">
+      <c r="AR28" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="BK28" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="BK27" s="20" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="28" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="AR28" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="BK28" s="20" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>57</v>
       </c>
@@ -9215,10 +9216,10 @@
       <c r="W29" s="121"/>
       <c r="X29" s="121"/>
       <c r="AR29" s="20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:63" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>58</v>
       </c>
@@ -9240,20 +9241,20 @@
         <v>59</v>
       </c>
       <c r="AR30" s="20" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:63" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:63" x14ac:dyDescent="0.35">
       <c r="AR31" s="20" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:63" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:63" x14ac:dyDescent="0.35">
       <c r="AR32" s="20" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:79" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>60</v>
       </c>
@@ -9267,10 +9268,10 @@
       <c r="AD33" s="131"/>
       <c r="AE33" s="131"/>
       <c r="AR33" s="20" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:79" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A34" s="125"/>
       <c r="B34" s="126"/>
       <c r="C34" s="127"/>
@@ -9333,7 +9334,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A35" s="132"/>
       <c r="B35" s="123"/>
       <c r="C35" s="133"/>
@@ -9393,10 +9394,10 @@
       <c r="AO35" s="72"/>
       <c r="AP35" s="77"/>
       <c r="AR35" s="80" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" spans="1:79" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="36" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A36" s="134" t="s">
         <v>67</v>
       </c>
@@ -9442,10 +9443,10 @@
       <c r="AO36" s="135"/>
       <c r="AP36" s="136"/>
       <c r="AV36" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="37" spans="1:79" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A37" s="137" t="s">
         <v>68</v>
       </c>
@@ -9531,9 +9532,9 @@
       <c r="BZ37" s="140"/>
       <c r="CA37" s="140"/>
     </row>
-    <row r="38" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A38" s="137" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="139"/>
@@ -9577,7 +9578,7 @@
       <c r="AO38" s="138"/>
       <c r="AP38" s="139"/>
       <c r="AR38" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="BE38" s="140"/>
       <c r="BF38" s="140"/>
@@ -9594,10 +9595,10 @@
       <c r="BQ38" s="140"/>
       <c r="BR38" s="140"/>
       <c r="BS38" s="52" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="39" spans="1:79" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A39" s="115"/>
       <c r="B39" s="12"/>
       <c r="C39" s="116"/>
@@ -9641,7 +9642,7 @@
       <c r="AO39" s="12"/>
       <c r="AP39" s="116"/>
       <c r="AR39" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AU39" s="120"/>
       <c r="AV39" s="120"/>
@@ -9654,7 +9655,7 @@
       <c r="BC39" s="120"/>
       <c r="BD39" s="120"/>
       <c r="BE39" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="BF39" s="141"/>
       <c r="BG39" s="141"/>
@@ -9662,7 +9663,7 @@
       <c r="BI39" s="141"/>
       <c r="BJ39" s="141"/>
       <c r="BK39" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="BL39" s="141"/>
       <c r="BM39" s="141"/>
@@ -9674,9 +9675,9 @@
       <c r="BS39" s="58"/>
       <c r="BT39" s="58"/>
     </row>
-    <row r="40" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="137" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B40" s="138"/>
       <c r="C40" s="139"/>
@@ -9756,9 +9757,9 @@
       <c r="BZ40" s="140"/>
       <c r="CA40" s="140"/>
     </row>
-    <row r="41" spans="1:79" ht="7.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:79" ht="7.85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="132" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B41" s="123"/>
       <c r="C41" s="133"/>
@@ -9802,13 +9803,13 @@
       <c r="AO41" s="123"/>
       <c r="AP41" s="133"/>
     </row>
-    <row r="42" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="75"/>
       <c r="AR42" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>60</v>
       </c>
@@ -9822,7 +9823,7 @@
       <c r="AD43" s="131"/>
       <c r="AE43" s="131"/>
     </row>
-    <row r="44" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="125"/>
       <c r="B44" s="126"/>
       <c r="C44" s="127"/>
@@ -9882,7 +9883,7 @@
       <c r="AO44" s="72"/>
       <c r="AP44" s="77"/>
     </row>
-    <row r="45" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="132"/>
       <c r="B45" s="123"/>
       <c r="C45" s="133"/>
@@ -9942,7 +9943,7 @@
       <c r="AO45" s="72"/>
       <c r="AP45" s="77"/>
     </row>
-    <row r="46" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="134" t="s">
         <v>67</v>
       </c>
@@ -9988,7 +9989,7 @@
       <c r="AO46" s="135"/>
       <c r="AP46" s="136"/>
     </row>
-    <row r="47" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="137" t="s">
         <v>68</v>
       </c>
@@ -10034,9 +10035,9 @@
       <c r="AO47" s="138"/>
       <c r="AP47" s="139"/>
     </row>
-    <row r="48" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="137" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B48" s="138"/>
       <c r="C48" s="139"/>
@@ -10080,9 +10081,9 @@
       <c r="AO48" s="138"/>
       <c r="AP48" s="139"/>
     </row>
-    <row r="49" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="137" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B49" s="138"/>
       <c r="C49" s="139"/>
@@ -10126,9 +10127,9 @@
       <c r="AO49" s="135"/>
       <c r="AP49" s="136"/>
     </row>
-    <row r="50" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="137" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B50" s="138"/>
       <c r="C50" s="139"/>
@@ -10172,9 +10173,9 @@
       <c r="AO50" s="138"/>
       <c r="AP50" s="139"/>
     </row>
-    <row r="51" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="132" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B51" s="123"/>
       <c r="C51" s="133"/>
@@ -10218,9 +10219,9 @@
       <c r="AO51" s="123"/>
       <c r="AP51" s="133"/>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A52" s="125" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B52" s="126"/>
       <c r="C52" s="126"/>
@@ -10264,9 +10265,9 @@
       <c r="AO52" s="126"/>
       <c r="AP52" s="127"/>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -10473,26 +10474,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CD75"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="1.6640625" style="8" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="1.640625" style="8" hidden="1" customWidth="1"/>
     <col min="5" max="6" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.88671875" style="8" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" style="8" hidden="1" customWidth="1"/>
     <col min="8" max="13" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.44140625" style="8" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="8" hidden="1" customWidth="1"/>
     <col min="15" max="42" width="2" style="8" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="2.33203125" style="8" hidden="1" customWidth="1"/>
-    <col min="44" max="51" width="2.33203125" style="8" customWidth="1"/>
-    <col min="52" max="52" width="2.88671875" style="8" customWidth="1"/>
-    <col min="53" max="68" width="2.33203125" style="8" customWidth="1"/>
-    <col min="69" max="69" width="2.21875" style="8" customWidth="1"/>
-    <col min="70" max="70" width="2.6640625" style="8" customWidth="1"/>
-    <col min="71" max="79" width="2.33203125" style="8" customWidth="1"/>
-    <col min="80" max="16384" width="8.88671875" style="8"/>
+    <col min="43" max="43" width="2.35546875" style="8" hidden="1" customWidth="1"/>
+    <col min="44" max="51" width="2.35546875" style="8" customWidth="1"/>
+    <col min="52" max="52" width="2.85546875" style="8" customWidth="1"/>
+    <col min="53" max="68" width="2.35546875" style="8" customWidth="1"/>
+    <col min="69" max="69" width="2.2109375" style="8" customWidth="1"/>
+    <col min="70" max="70" width="2.640625" style="8" customWidth="1"/>
+    <col min="71" max="79" width="2.35546875" style="8" customWidth="1"/>
+    <col min="80" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -10525,12 +10526,12 @@
       <c r="BZ1" s="120"/>
       <c r="CA1" s="120"/>
     </row>
-    <row r="2" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.35">
       <c r="AR2" s="63" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:82" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A3" s="63" t="s">
         <v>3</v>
       </c>
@@ -10570,7 +10571,7 @@
       <c r="BZ3" s="63"/>
       <c r="CA3" s="63"/>
     </row>
-    <row r="4" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A4" s="121"/>
       <c r="B4" s="121"/>
       <c r="C4" s="121"/>
@@ -10581,7 +10582,7 @@
       <c r="H4" s="121"/>
       <c r="I4" s="121"/>
       <c r="AR4" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AS4" s="117"/>
       <c r="AT4" s="117"/>
@@ -10596,12 +10597,12 @@
       <c r="BC4" s="144"/>
       <c r="BD4" s="144"/>
       <c r="BE4" s="117" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="BF4" s="117"/>
       <c r="BG4" s="117"/>
       <c r="BH4" s="145" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="BI4" s="145"/>
       <c r="BJ4" s="145"/>
@@ -10620,7 +10621,7 @@
       <c r="BW4" s="145"/>
       <c r="BX4" s="145"/>
       <c r="BY4" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="BZ4" s="11"/>
       <c r="CA4" s="11"/>
@@ -10628,7 +10629,7 @@
       <c r="CC4" s="11"/>
       <c r="CD4" s="11"/>
     </row>
-    <row r="5" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
@@ -10644,7 +10645,7 @@
       <c r="AN5" s="123"/>
       <c r="AO5" s="12"/>
       <c r="AR5" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="BB5" s="140"/>
       <c r="BC5" s="140"/>
@@ -10661,13 +10662,13 @@
       <c r="BN5" s="140"/>
       <c r="BO5" s="140"/>
       <c r="BP5" s="52" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="BV5" s="11"/>
       <c r="BW5" s="47"/>
       <c r="BX5" s="47"/>
     </row>
-    <row r="6" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
@@ -10692,7 +10693,7 @@
       <c r="AZ6" s="120"/>
       <c r="BA6" s="120"/>
       <c r="BB6" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="BC6" s="141"/>
       <c r="BD6" s="141"/>
@@ -10700,7 +10701,7 @@
       <c r="BF6" s="141"/>
       <c r="BG6" s="141"/>
       <c r="BH6" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="BI6" s="120"/>
       <c r="BJ6" s="120"/>
@@ -10722,19 +10723,19 @@
       <c r="BZ6" s="120"/>
       <c r="CA6" s="120"/>
     </row>
-    <row r="7" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:82" x14ac:dyDescent="0.35">
       <c r="N7" s="70"/>
       <c r="O7" s="70"/>
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
       <c r="R7" s="12"/>
       <c r="AR7" s="65" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AS7" s="85"/>
       <c r="AT7" s="85"/>
       <c r="AU7" s="140" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AV7" s="140"/>
       <c r="AW7" s="140"/>
@@ -10756,17 +10757,17 @@
       <c r="BM7" s="120"/>
       <c r="BN7" s="43"/>
       <c r="BP7" s="118" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:82" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:82" x14ac:dyDescent="0.35">
       <c r="N8" s="70"/>
       <c r="O8" s="70"/>
       <c r="P8" s="70"/>
       <c r="Q8" s="70"/>
       <c r="R8" s="12"/>
       <c r="AR8" s="143" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AS8" s="143"/>
       <c r="AT8" s="143"/>
@@ -10804,7 +10805,7 @@
       <c r="BZ8" s="146"/>
       <c r="CA8" s="146"/>
     </row>
-    <row r="9" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A9" s="121"/>
       <c r="B9" s="121"/>
       <c r="C9" s="121"/>
@@ -10815,7 +10816,7 @@
       <c r="H9" s="121"/>
       <c r="I9" s="121"/>
       <c r="AR9" s="143" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AS9" s="143"/>
       <c r="AT9" s="143"/>
@@ -10853,7 +10854,7 @@
       <c r="BZ9" s="143"/>
       <c r="CA9" s="143"/>
     </row>
-    <row r="10" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>22</v>
       </c>
@@ -10890,7 +10891,7 @@
       <c r="AO10" s="121"/>
       <c r="AP10" s="121"/>
       <c r="AR10" s="143" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AS10" s="143"/>
       <c r="AT10" s="143"/>
@@ -10928,7 +10929,7 @@
       <c r="BZ10" s="143"/>
       <c r="CA10" s="143"/>
     </row>
-    <row r="11" spans="1:82" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:82" ht="6.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E11" s="65"/>
       <c r="G11" s="66"/>
       <c r="H11" s="64"/>
@@ -10981,7 +10982,7 @@
       <c r="BZ11" s="78"/>
       <c r="CA11" s="78"/>
     </row>
-    <row r="12" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:82" x14ac:dyDescent="0.35">
       <c r="E12" s="65"/>
       <c r="G12" s="66"/>
       <c r="H12" s="64"/>
@@ -11024,7 +11025,7 @@
       <c r="BW12" s="147"/>
       <c r="BX12" s="147"/>
     </row>
-    <row r="13" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>60</v>
       </c>
@@ -11049,12 +11050,12 @@
       <c r="AV13" s="126"/>
       <c r="AW13" s="126"/>
       <c r="AX13" s="149" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AY13" s="150"/>
       <c r="AZ13" s="59"/>
       <c r="BA13" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BB13" s="151"/>
       <c r="BC13" s="125" t="s">
@@ -11077,12 +11078,12 @@
       <c r="BN13" s="128"/>
       <c r="BO13" s="128"/>
       <c r="BP13" s="149" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BQ13" s="150"/>
       <c r="BR13" s="59"/>
       <c r="BS13" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BT13" s="151"/>
       <c r="BU13" s="128" t="s">
@@ -11097,7 +11098,7 @@
       <c r="BZ13" s="128"/>
       <c r="CA13" s="128"/>
     </row>
-    <row r="14" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>60</v>
       </c>
@@ -11166,7 +11167,7 @@
       <c r="BZ14" s="128"/>
       <c r="CA14" s="128"/>
     </row>
-    <row r="15" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A15" s="134"/>
       <c r="B15" s="135"/>
       <c r="C15" s="136"/>
@@ -11176,12 +11177,12 @@
       <c r="E15" s="126"/>
       <c r="F15" s="126"/>
       <c r="G15" s="149" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H15" s="150"/>
       <c r="I15" s="76"/>
       <c r="J15" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K15" s="151"/>
       <c r="L15" s="125" t="s">
@@ -11204,12 +11205,12 @@
       <c r="W15" s="128"/>
       <c r="X15" s="128"/>
       <c r="Y15" s="149" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Z15" s="150"/>
       <c r="AA15" s="76"/>
       <c r="AB15" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AC15" s="151"/>
       <c r="AD15" s="128" t="s">
@@ -11264,7 +11265,7 @@
       <c r="BZ15" s="135"/>
       <c r="CA15" s="136"/>
     </row>
-    <row r="16" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A16" s="132"/>
       <c r="B16" s="123"/>
       <c r="C16" s="133"/>
@@ -11358,7 +11359,7 @@
       <c r="BZ16" s="138"/>
       <c r="CA16" s="139"/>
     </row>
-    <row r="17" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A17" s="125" t="s">
         <v>67</v>
       </c>
@@ -11400,7 +11401,7 @@
       <c r="AI17" s="135"/>
       <c r="AJ17" s="136"/>
       <c r="AR17" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS17" s="126"/>
       <c r="AT17" s="127"/>
@@ -11420,7 +11421,7 @@
       <c r="BH17" s="123"/>
       <c r="BI17" s="133"/>
       <c r="BJ17" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BK17" s="126"/>
       <c r="BL17" s="127"/>
@@ -11440,7 +11441,7 @@
       <c r="BZ17" s="123"/>
       <c r="CA17" s="133"/>
     </row>
-    <row r="18" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A18" s="125" t="s">
         <v>68</v>
       </c>
@@ -11482,7 +11483,7 @@
       <c r="AI18" s="138"/>
       <c r="AJ18" s="139"/>
       <c r="AR18" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AS18" s="126"/>
       <c r="AT18" s="127"/>
@@ -11502,7 +11503,7 @@
       <c r="BH18" s="135"/>
       <c r="BI18" s="136"/>
       <c r="BJ18" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BK18" s="126"/>
       <c r="BL18" s="127"/>
@@ -11522,9 +11523,9 @@
       <c r="BZ18" s="135"/>
       <c r="CA18" s="136"/>
     </row>
-    <row r="19" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A19" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="126"/>
       <c r="C19" s="127"/>
@@ -11544,7 +11545,7 @@
       <c r="Q19" s="123"/>
       <c r="R19" s="133"/>
       <c r="S19" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T19" s="126"/>
       <c r="U19" s="127"/>
@@ -11564,7 +11565,7 @@
       <c r="AI19" s="123"/>
       <c r="AJ19" s="133"/>
       <c r="AR19" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AS19" s="126"/>
       <c r="AT19" s="127"/>
@@ -11584,7 +11585,7 @@
       <c r="BH19" s="138"/>
       <c r="BI19" s="139"/>
       <c r="BJ19" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BK19" s="126"/>
       <c r="BL19" s="127"/>
@@ -11604,9 +11605,9 @@
       <c r="BZ19" s="138"/>
       <c r="CA19" s="139"/>
     </row>
-    <row r="20" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A20" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B20" s="126"/>
       <c r="C20" s="127"/>
@@ -11626,7 +11627,7 @@
       <c r="Q20" s="135"/>
       <c r="R20" s="136"/>
       <c r="S20" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="T20" s="126"/>
       <c r="U20" s="127"/>
@@ -11646,7 +11647,7 @@
       <c r="AI20" s="135"/>
       <c r="AJ20" s="136"/>
       <c r="AR20" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AS20" s="126"/>
       <c r="AT20" s="127"/>
@@ -11666,7 +11667,7 @@
       <c r="BH20" s="123"/>
       <c r="BI20" s="133"/>
       <c r="BJ20" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="BK20" s="126"/>
       <c r="BL20" s="127"/>
@@ -11686,9 +11687,9 @@
       <c r="BZ20" s="123"/>
       <c r="CA20" s="133"/>
     </row>
-    <row r="21" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A21" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B21" s="126"/>
       <c r="C21" s="127"/>
@@ -11708,7 +11709,7 @@
       <c r="Q21" s="138"/>
       <c r="R21" s="139"/>
       <c r="S21" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T21" s="126"/>
       <c r="U21" s="127"/>
@@ -11728,16 +11729,16 @@
       <c r="AI21" s="138"/>
       <c r="AJ21" s="139"/>
       <c r="AR21" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="BK21" s="12"/>
       <c r="BL21" s="65" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:79" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:79" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="126"/>
       <c r="C22" s="127"/>
@@ -11757,7 +11758,7 @@
       <c r="Q22" s="123"/>
       <c r="R22" s="133"/>
       <c r="S22" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="T22" s="126"/>
       <c r="U22" s="127"/>
@@ -11813,7 +11814,7 @@
       <c r="BZ22" s="78"/>
       <c r="CA22" s="78"/>
     </row>
-    <row r="23" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A23" s="132"/>
       <c r="B23" s="123"/>
       <c r="C23" s="133"/>
@@ -11893,7 +11894,7 @@
       <c r="BW23" s="147"/>
       <c r="BX23" s="147"/>
     </row>
-    <row r="24" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A24" s="125" t="s">
         <v>67</v>
       </c>
@@ -11943,12 +11944,12 @@
       <c r="AV24" s="126"/>
       <c r="AW24" s="126"/>
       <c r="AX24" s="149" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AY24" s="150"/>
       <c r="AZ24" s="59"/>
       <c r="BA24" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BB24" s="151"/>
       <c r="BC24" s="125" t="s">
@@ -11971,12 +11972,12 @@
       <c r="BN24" s="128"/>
       <c r="BO24" s="128"/>
       <c r="BP24" s="149" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BQ24" s="150"/>
       <c r="BR24" s="59"/>
       <c r="BS24" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BT24" s="151"/>
       <c r="BU24" s="128" t="s">
@@ -11991,7 +11992,7 @@
       <c r="BZ24" s="128"/>
       <c r="CA24" s="128"/>
     </row>
-    <row r="25" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A25" s="125" t="s">
         <v>68</v>
       </c>
@@ -12085,9 +12086,9 @@
       <c r="BZ25" s="128"/>
       <c r="CA25" s="128"/>
     </row>
-    <row r="26" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A26" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="126"/>
       <c r="C26" s="127"/>
@@ -12107,7 +12108,7 @@
       <c r="Q26" s="123"/>
       <c r="R26" s="133"/>
       <c r="S26" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T26" s="126"/>
       <c r="U26" s="127"/>
@@ -12167,9 +12168,9 @@
       <c r="BZ26" s="135"/>
       <c r="CA26" s="136"/>
     </row>
-    <row r="27" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A27" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B27" s="126"/>
       <c r="C27" s="127"/>
@@ -12189,7 +12190,7 @@
       <c r="Q27" s="135"/>
       <c r="R27" s="136"/>
       <c r="S27" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="T27" s="126"/>
       <c r="U27" s="127"/>
@@ -12249,9 +12250,9 @@
       <c r="BZ27" s="138"/>
       <c r="CA27" s="139"/>
     </row>
-    <row r="28" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A28" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B28" s="126"/>
       <c r="C28" s="127"/>
@@ -12271,7 +12272,7 @@
       <c r="Q28" s="138"/>
       <c r="R28" s="139"/>
       <c r="S28" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T28" s="126"/>
       <c r="U28" s="127"/>
@@ -12291,7 +12292,7 @@
       <c r="AI28" s="138"/>
       <c r="AJ28" s="139"/>
       <c r="AR28" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS28" s="126"/>
       <c r="AT28" s="127"/>
@@ -12311,7 +12312,7 @@
       <c r="BH28" s="123"/>
       <c r="BI28" s="133"/>
       <c r="BJ28" s="125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BK28" s="126"/>
       <c r="BL28" s="127"/>
@@ -12331,9 +12332,9 @@
       <c r="BZ28" s="123"/>
       <c r="CA28" s="133"/>
     </row>
-    <row r="29" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A29" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B29" s="126"/>
       <c r="C29" s="127"/>
@@ -12353,7 +12354,7 @@
       <c r="Q29" s="123"/>
       <c r="R29" s="133"/>
       <c r="S29" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="T29" s="126"/>
       <c r="U29" s="127"/>
@@ -12373,7 +12374,7 @@
       <c r="AI29" s="123"/>
       <c r="AJ29" s="133"/>
       <c r="AR29" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AS29" s="126"/>
       <c r="AT29" s="127"/>
@@ -12393,7 +12394,7 @@
       <c r="BH29" s="135"/>
       <c r="BI29" s="136"/>
       <c r="BJ29" s="125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="BK29" s="126"/>
       <c r="BL29" s="127"/>
@@ -12413,16 +12414,16 @@
       <c r="BZ29" s="135"/>
       <c r="CA29" s="136"/>
     </row>
-    <row r="30" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T30" s="12"/>
       <c r="U30" s="65" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AR30" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AS30" s="126"/>
       <c r="AT30" s="127"/>
@@ -12442,7 +12443,7 @@
       <c r="BH30" s="138"/>
       <c r="BI30" s="139"/>
       <c r="BJ30" s="125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BK30" s="126"/>
       <c r="BL30" s="127"/>
@@ -12462,14 +12463,14 @@
       <c r="BZ30" s="138"/>
       <c r="CA30" s="139"/>
     </row>
-    <row r="31" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A31" s="121"/>
       <c r="B31" s="121"/>
       <c r="C31" s="8" t="s">
         <v>18</v>
       </c>
       <c r="AR31" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AS31" s="126"/>
       <c r="AT31" s="127"/>
@@ -12489,7 +12490,7 @@
       <c r="BH31" s="123"/>
       <c r="BI31" s="133"/>
       <c r="BJ31" s="125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="BK31" s="126"/>
       <c r="BL31" s="127"/>
@@ -12509,7 +12510,7 @@
       <c r="BZ31" s="123"/>
       <c r="CA31" s="133"/>
     </row>
-    <row r="32" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:79" x14ac:dyDescent="0.35">
       <c r="A32" s="121"/>
       <c r="B32" s="121"/>
       <c r="C32" s="121"/>
@@ -12520,14 +12521,14 @@
       <c r="H32" s="121"/>
       <c r="I32" s="121"/>
       <c r="AR32" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="BK32" s="12"/>
       <c r="BL32" s="65" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>32</v>
       </c>
@@ -12545,10 +12546,10 @@
         <v>34</v>
       </c>
       <c r="AR33" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A34" s="121"/>
       <c r="B34" s="121"/>
       <c r="C34" s="121"/>
@@ -12559,7 +12560,7 @@
       <c r="H34" s="121"/>
       <c r="I34" s="121"/>
     </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>4</v>
       </c>
@@ -12574,7 +12575,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A36" s="121"/>
       <c r="B36" s="121"/>
       <c r="C36" s="121"/>
@@ -12599,7 +12600,7 @@
       <c r="AO36" s="72"/>
       <c r="AP36" s="77"/>
     </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A37" s="121"/>
       <c r="B37" s="121"/>
       <c r="C37" s="121"/>
@@ -12618,7 +12619,7 @@
       <c r="AO37" s="72"/>
       <c r="AP37" s="77"/>
     </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>42</v>
       </c>
@@ -12643,7 +12644,7 @@
       <c r="AO38" s="135"/>
       <c r="AP38" s="136"/>
     </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>22</v>
       </c>
@@ -12664,9 +12665,9 @@
       <c r="AO39" s="138"/>
       <c r="AP39" s="139"/>
     </row>
-    <row r="40" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F40" s="121"/>
       <c r="G40" s="121"/>
@@ -12690,7 +12691,7 @@
       <c r="AO40" s="138"/>
       <c r="AP40" s="139"/>
     </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.35">
       <c r="AK41" s="67"/>
       <c r="AL41" s="69"/>
       <c r="AM41" s="134"/>
@@ -12698,7 +12699,7 @@
       <c r="AO41" s="135"/>
       <c r="AP41" s="136"/>
     </row>
-    <row r="42" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>47</v>
       </c>
@@ -12719,7 +12720,7 @@
       <c r="AO42" s="138"/>
       <c r="AP42" s="139"/>
     </row>
-    <row r="43" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>50</v>
       </c>
@@ -12730,7 +12731,7 @@
       <c r="AO43" s="123"/>
       <c r="AP43" s="133"/>
     </row>
-    <row r="44" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>51</v>
       </c>
@@ -12747,8 +12748,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>53</v>
       </c>
@@ -12766,7 +12767,7 @@
       <c r="AO46" s="72"/>
       <c r="AP46" s="77"/>
     </row>
-    <row r="47" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>55</v>
       </c>
@@ -12791,7 +12792,7 @@
       <c r="AO47" s="72"/>
       <c r="AP47" s="77"/>
     </row>
-    <row r="48" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="121"/>
       <c r="B48" s="121"/>
       <c r="C48" s="121"/>
@@ -12811,7 +12812,7 @@
       <c r="AO48" s="135"/>
       <c r="AP48" s="136"/>
     </row>
-    <row r="49" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AK49" s="67"/>
       <c r="AL49" s="69"/>
       <c r="AM49" s="137"/>
@@ -12819,7 +12820,7 @@
       <c r="AO49" s="138"/>
       <c r="AP49" s="139"/>
     </row>
-    <row r="50" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>57</v>
       </c>
@@ -12844,7 +12845,7 @@
       <c r="AO50" s="138"/>
       <c r="AP50" s="139"/>
     </row>
-    <row r="51" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>58</v>
       </c>
@@ -12872,7 +12873,7 @@
       <c r="AO51" s="135"/>
       <c r="AP51" s="136"/>
     </row>
-    <row r="52" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AK52" s="67"/>
       <c r="AL52" s="69"/>
       <c r="AM52" s="137"/>
@@ -12880,7 +12881,7 @@
       <c r="AO52" s="138"/>
       <c r="AP52" s="139"/>
     </row>
-    <row r="53" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AK53" s="67"/>
       <c r="AL53" s="69"/>
       <c r="AM53" s="132"/>
@@ -12888,7 +12889,7 @@
       <c r="AO53" s="123"/>
       <c r="AP53" s="133"/>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>60</v>
       </c>
@@ -12908,7 +12909,7 @@
       <c r="AO54" s="67"/>
       <c r="AP54" s="69"/>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A55" s="125"/>
       <c r="B55" s="126"/>
       <c r="C55" s="127"/>
@@ -12960,7 +12961,7 @@
       <c r="AI55" s="72"/>
       <c r="AJ55" s="72"/>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A56" s="132"/>
       <c r="B56" s="123"/>
       <c r="C56" s="133"/>
@@ -13012,7 +13013,7 @@
       <c r="AI56" s="72"/>
       <c r="AJ56" s="72"/>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A57" s="134" t="s">
         <v>67</v>
       </c>
@@ -13052,7 +13053,7 @@
       <c r="AI57" s="67"/>
       <c r="AJ57" s="67"/>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A58" s="137" t="s">
         <v>68</v>
       </c>
@@ -13092,9 +13093,9 @@
       <c r="AI58" s="67"/>
       <c r="AJ58" s="67"/>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A59" s="137" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59" s="138"/>
       <c r="C59" s="139"/>
@@ -13132,9 +13133,9 @@
       <c r="AI59" s="67"/>
       <c r="AJ59" s="67"/>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A60" s="137" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B60" s="138"/>
       <c r="C60" s="139"/>
@@ -13172,9 +13173,9 @@
       <c r="AI60" s="67"/>
       <c r="AJ60" s="67"/>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A61" s="137" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B61" s="138"/>
       <c r="C61" s="139"/>
@@ -13212,9 +13213,9 @@
       <c r="AI61" s="67"/>
       <c r="AJ61" s="67"/>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A62" s="132" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B62" s="123"/>
       <c r="C62" s="133"/>
@@ -13252,10 +13253,10 @@
       <c r="AI62" s="67"/>
       <c r="AJ62" s="67"/>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A63" s="75"/>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
         <v>60</v>
       </c>
@@ -13269,7 +13270,7 @@
       <c r="AD64" s="131"/>
       <c r="AE64" s="131"/>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A65" s="125"/>
       <c r="B65" s="126"/>
       <c r="C65" s="127"/>
@@ -13321,7 +13322,7 @@
       <c r="AI65" s="72"/>
       <c r="AJ65" s="72"/>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A66" s="132"/>
       <c r="B66" s="123"/>
       <c r="C66" s="133"/>
@@ -13373,7 +13374,7 @@
       <c r="AI66" s="72"/>
       <c r="AJ66" s="72"/>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A67" s="134" t="s">
         <v>67</v>
       </c>
@@ -13413,7 +13414,7 @@
       <c r="AI67" s="67"/>
       <c r="AJ67" s="67"/>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A68" s="137" t="s">
         <v>68</v>
       </c>
@@ -13453,9 +13454,9 @@
       <c r="AI68" s="67"/>
       <c r="AJ68" s="67"/>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A69" s="137" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" s="138"/>
       <c r="C69" s="139"/>
@@ -13493,9 +13494,9 @@
       <c r="AI69" s="67"/>
       <c r="AJ69" s="67"/>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A70" s="137" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B70" s="138"/>
       <c r="C70" s="139"/>
@@ -13533,9 +13534,9 @@
       <c r="AI70" s="67"/>
       <c r="AJ70" s="67"/>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A71" s="137" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B71" s="138"/>
       <c r="C71" s="139"/>
@@ -13573,9 +13574,9 @@
       <c r="AI71" s="67"/>
       <c r="AJ71" s="67"/>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A72" s="132" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B72" s="123"/>
       <c r="C72" s="133"/>
@@ -13613,9 +13614,9 @@
       <c r="AI72" s="67"/>
       <c r="AJ72" s="67"/>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A73" s="68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B73" s="67"/>
       <c r="C73" s="67"/>
@@ -13653,9 +13654,9 @@
       <c r="AI73" s="67"/>
       <c r="AJ73" s="67"/>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14046,6 +14047,9 @@
     <mergeCell ref="BY14:CA14"/>
     <mergeCell ref="BJ13:BL14"/>
     <mergeCell ref="AU14:AW14"/>
+    <mergeCell ref="AZ10:BF10"/>
+    <mergeCell ref="BG10:BM10"/>
+    <mergeCell ref="BN10:BT10"/>
     <mergeCell ref="BN9:BT9"/>
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="X13:AA13"/>
@@ -14070,9 +14074,6 @@
     <mergeCell ref="AI10:AJ10"/>
     <mergeCell ref="AN10:AP10"/>
     <mergeCell ref="AR10:AY10"/>
-    <mergeCell ref="AZ10:BF10"/>
-    <mergeCell ref="BG10:BM10"/>
-    <mergeCell ref="BN10:BT10"/>
     <mergeCell ref="BU9:CA9"/>
     <mergeCell ref="BC1:CA1"/>
     <mergeCell ref="A4:I4"/>
@@ -14119,34 +14120,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AO71"/>
-  <sheetFormatPr defaultColWidth="8.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.35546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="2.33203125" customWidth="1"/>
+    <col min="1" max="4" width="2.35546875" customWidth="1"/>
     <col min="5" max="8" width="1" customWidth="1"/>
-    <col min="9" max="10" width="2.33203125" customWidth="1"/>
-    <col min="11" max="11" width="2.109375" customWidth="1"/>
+    <col min="9" max="10" width="2.35546875" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" customWidth="1"/>
     <col min="12" max="12" width="1" customWidth="1"/>
-    <col min="13" max="13" width="2.33203125" customWidth="1"/>
+    <col min="13" max="13" width="2.35546875" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="0.6640625" customWidth="1"/>
-    <col min="16" max="19" width="2.33203125" customWidth="1"/>
+    <col min="15" max="15" width="0.640625" customWidth="1"/>
+    <col min="16" max="19" width="2.35546875" customWidth="1"/>
     <col min="20" max="20" width="2" customWidth="1"/>
-    <col min="21" max="21" width="2.33203125" customWidth="1"/>
-    <col min="22" max="22" width="2.88671875" customWidth="1"/>
-    <col min="23" max="23" width="3.21875" customWidth="1"/>
-    <col min="24" max="26" width="2.33203125" customWidth="1"/>
-    <col min="27" max="27" width="2.88671875" customWidth="1"/>
-    <col min="28" max="28" width="1.44140625" customWidth="1"/>
-    <col min="29" max="30" width="2.33203125" customWidth="1"/>
-    <col min="31" max="31" width="2.44140625" customWidth="1"/>
-    <col min="32" max="33" width="2.6640625" customWidth="1"/>
-    <col min="34" max="36" width="2.44140625" customWidth="1"/>
-    <col min="37" max="37" width="2.88671875" customWidth="1"/>
+    <col min="21" max="21" width="2.35546875" customWidth="1"/>
+    <col min="22" max="22" width="2.85546875" customWidth="1"/>
+    <col min="23" max="23" width="3.2109375" customWidth="1"/>
+    <col min="24" max="26" width="2.35546875" customWidth="1"/>
+    <col min="27" max="27" width="2.85546875" customWidth="1"/>
+    <col min="28" max="28" width="1.42578125" customWidth="1"/>
+    <col min="29" max="30" width="2.35546875" customWidth="1"/>
+    <col min="31" max="31" width="2.42578125" customWidth="1"/>
+    <col min="32" max="33" width="2.640625" customWidth="1"/>
+    <col min="34" max="36" width="2.42578125" customWidth="1"/>
+    <col min="37" max="37" width="2.85546875" customWidth="1"/>
     <col min="38" max="38" width="2" customWidth="1"/>
-    <col min="39" max="40" width="2.44140625" customWidth="1"/>
+    <col min="39" max="40" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -14176,12 +14177,12 @@
       <c r="AM1" s="140"/>
       <c r="AN1" s="140"/>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A2" s="42" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="140"/>
       <c r="B3" s="140"/>
       <c r="C3" s="140"/>
@@ -14223,9 +14224,9 @@
       <c r="AM3" s="60"/>
       <c r="AN3" s="60"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B4" s="117"/>
       <c r="C4" s="117"/>
@@ -14242,12 +14243,12 @@
       <c r="N4" s="140"/>
       <c r="O4" s="140"/>
       <c r="P4" s="117" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q4" s="117"/>
       <c r="R4" s="117"/>
       <c r="S4" s="145" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T4" s="145"/>
       <c r="U4" s="145"/>
@@ -14265,7 +14266,7 @@
       <c r="AG4" s="145"/>
       <c r="AH4" s="145"/>
       <c r="AI4" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="11"/>
@@ -14273,9 +14274,9 @@
       <c r="AM4" s="11"/>
       <c r="AN4" s="11"/>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -14300,7 +14301,7 @@
       <c r="V5" s="140"/>
       <c r="W5" s="140"/>
       <c r="X5" s="52" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y5" s="8"/>
       <c r="Z5" s="8"/>
@@ -14319,7 +14320,7 @@
       <c r="AM5" s="120"/>
       <c r="AN5" s="120"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6" s="120"/>
       <c r="B6" s="120"/>
       <c r="C6" s="120"/>
@@ -14327,10 +14328,10 @@
       <c r="E6" s="120"/>
       <c r="F6" s="120"/>
       <c r="G6" s="47" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H6" s="152" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I6" s="152"/>
       <c r="J6" s="153"/>
@@ -14365,7 +14366,7 @@
       <c r="AM6" s="140"/>
       <c r="AN6" s="140"/>
     </row>
-    <row r="7" spans="1:41" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" ht="10.85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="65"/>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
@@ -14406,11 +14407,11 @@
       <c r="AL7" s="43"/>
       <c r="AM7" s="43"/>
       <c r="AN7" s="62" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AO7" s="60"/>
     </row>
-    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="166"/>
       <c r="B8" s="151"/>
       <c r="C8" s="151"/>
@@ -14427,46 +14428,46 @@
       <c r="N8" s="151"/>
       <c r="O8" s="151"/>
       <c r="P8" s="168" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q8" s="151"/>
       <c r="R8" s="151"/>
       <c r="S8" s="151"/>
       <c r="T8" s="156"/>
       <c r="U8" s="154" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="V8" s="154"/>
       <c r="W8" s="59"/>
       <c r="X8" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Y8" s="151"/>
       <c r="Z8" s="155" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AA8" s="154"/>
       <c r="AB8" s="88"/>
       <c r="AC8" s="151" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AD8" s="156"/>
       <c r="AE8" s="155" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AF8" s="154"/>
       <c r="AG8" s="154"/>
       <c r="AH8" s="154"/>
       <c r="AI8" s="169"/>
       <c r="AJ8" s="155" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AK8" s="154"/>
       <c r="AL8" s="154"/>
       <c r="AM8" s="154"/>
       <c r="AN8" s="169"/>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" s="167"/>
       <c r="B9" s="162"/>
       <c r="C9" s="162"/>
@@ -14488,14 +14489,14 @@
       <c r="S9" s="162"/>
       <c r="T9" s="164"/>
       <c r="U9" s="161" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="V9" s="162"/>
       <c r="W9" s="162"/>
       <c r="X9" s="162"/>
       <c r="Y9" s="162"/>
       <c r="Z9" s="163" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AA9" s="162"/>
       <c r="AB9" s="162"/>
@@ -14512,7 +14513,7 @@
       <c r="AM9" s="171"/>
       <c r="AN9" s="172"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
         <v>60</v>
       </c>
@@ -14546,27 +14547,27 @@
       <c r="AC10" s="159"/>
       <c r="AD10" s="160"/>
       <c r="AE10" s="157" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AF10" s="158"/>
       <c r="AG10" s="59"/>
       <c r="AH10" s="159" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AI10" s="160"/>
       <c r="AJ10" s="158" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AK10" s="158"/>
       <c r="AL10" s="61"/>
       <c r="AM10" s="159" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AN10" s="160"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" s="44" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
@@ -14608,9 +14609,9 @@
       <c r="AM11" s="174"/>
       <c r="AN11" s="174"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" s="46" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G12" s="47"/>
       <c r="H12" s="47"/>
@@ -14644,9 +14645,9 @@
       <c r="AM12" s="174"/>
       <c r="AN12" s="174"/>
     </row>
-    <row r="13" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G13" s="47"/>
       <c r="H13" s="47"/>
@@ -14680,9 +14681,9 @@
       <c r="AM13" s="174"/>
       <c r="AN13" s="174"/>
     </row>
-    <row r="14" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G14" s="47"/>
       <c r="H14" s="47"/>
@@ -14716,9 +14717,9 @@
       <c r="AM14" s="174"/>
       <c r="AN14" s="174"/>
     </row>
-    <row r="15" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G15" s="47"/>
       <c r="H15" s="47"/>
@@ -14752,9 +14753,9 @@
       <c r="AM15" s="174"/>
       <c r="AN15" s="174"/>
     </row>
-    <row r="16" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="47"/>
@@ -14788,9 +14789,9 @@
       <c r="AM16" s="174"/>
       <c r="AN16" s="174"/>
     </row>
-    <row r="17" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G17" s="47"/>
       <c r="H17" s="47"/>
@@ -14824,9 +14825,9 @@
       <c r="AM17" s="174"/>
       <c r="AN17" s="174"/>
     </row>
-    <row r="18" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G18" s="47"/>
       <c r="H18" s="47"/>
@@ -14860,9 +14861,9 @@
       <c r="AM18" s="174"/>
       <c r="AN18" s="174"/>
     </row>
-    <row r="19" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G19" s="47"/>
       <c r="H19" s="47"/>
@@ -14896,9 +14897,9 @@
       <c r="AM19" s="174"/>
       <c r="AN19" s="174"/>
     </row>
-    <row r="20" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G20" s="47"/>
       <c r="H20" s="47"/>
@@ -14932,9 +14933,9 @@
       <c r="AM20" s="174"/>
       <c r="AN20" s="174"/>
     </row>
-    <row r="21" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G21" s="47"/>
       <c r="H21" s="47"/>
@@ -14968,9 +14969,9 @@
       <c r="AM21" s="174"/>
       <c r="AN21" s="174"/>
     </row>
-    <row r="22" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="46" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G22" s="47"/>
       <c r="H22" s="47"/>
@@ -15004,9 +15005,9 @@
       <c r="AM22" s="174"/>
       <c r="AN22" s="174"/>
     </row>
-    <row r="23" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G23" s="47"/>
       <c r="H23" s="47"/>
@@ -15040,9 +15041,9 @@
       <c r="AM23" s="174"/>
       <c r="AN23" s="174"/>
     </row>
-    <row r="24" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="46" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G24" s="47"/>
       <c r="H24" s="47"/>
@@ -15076,9 +15077,9 @@
       <c r="AM24" s="174"/>
       <c r="AN24" s="174"/>
     </row>
-    <row r="25" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="48" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G25" s="47"/>
       <c r="H25" s="47"/>
@@ -15112,9 +15113,9 @@
       <c r="AM25" s="176"/>
       <c r="AN25" s="176"/>
     </row>
-    <row r="26" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B26" s="49"/>
       <c r="C26" s="49"/>
@@ -15156,9 +15157,9 @@
       <c r="AM26" s="178"/>
       <c r="AN26" s="178"/>
     </row>
-    <row r="27" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="46" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G27" s="47"/>
       <c r="H27" s="47"/>
@@ -15192,9 +15193,9 @@
       <c r="AM27" s="174"/>
       <c r="AN27" s="174"/>
     </row>
-    <row r="28" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="46" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G28" s="47"/>
       <c r="H28" s="47"/>
@@ -15228,9 +15229,9 @@
       <c r="AM28" s="174"/>
       <c r="AN28" s="174"/>
     </row>
-    <row r="29" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="46" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G29" s="47"/>
       <c r="H29" s="47"/>
@@ -15264,9 +15265,9 @@
       <c r="AM29" s="174"/>
       <c r="AN29" s="174"/>
     </row>
-    <row r="30" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="46" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G30" s="47"/>
       <c r="H30" s="47"/>
@@ -15300,9 +15301,9 @@
       <c r="AM30" s="174"/>
       <c r="AN30" s="174"/>
     </row>
-    <row r="31" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="46" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G31" s="47"/>
       <c r="H31" s="47"/>
@@ -15336,9 +15337,9 @@
       <c r="AM31" s="174"/>
       <c r="AN31" s="174"/>
     </row>
-    <row r="32" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="46" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G32" s="47"/>
       <c r="H32" s="47"/>
@@ -15372,9 +15373,9 @@
       <c r="AM32" s="174"/>
       <c r="AN32" s="174"/>
     </row>
-    <row r="33" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="46" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G33" s="47"/>
       <c r="H33" s="47"/>
@@ -15408,9 +15409,9 @@
       <c r="AM33" s="174"/>
       <c r="AN33" s="174"/>
     </row>
-    <row r="34" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="46" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G34" s="47"/>
       <c r="H34" s="47"/>
@@ -15444,9 +15445,9 @@
       <c r="AM34" s="174"/>
       <c r="AN34" s="174"/>
     </row>
-    <row r="35" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
@@ -15488,12 +15489,12 @@
       <c r="AM35" s="174"/>
       <c r="AN35" s="174"/>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A37" s="41"/>
       <c r="B37" s="41"/>
       <c r="C37" s="41"/>
@@ -15526,7 +15527,7 @@
       <c r="AM37" s="11"/>
       <c r="AN37" s="11"/>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
       <c r="V38" s="11"/>
       <c r="Z38" s="11"/>
       <c r="AA38" s="11"/>
@@ -15544,10 +15545,10 @@
       <c r="AM38" s="11"/>
       <c r="AN38" s="11"/>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
       <c r="U40" s="11"/>
     </row>
-    <row r="41" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I41" s="11"/>
       <c r="J41" s="11"/>
       <c r="L41" s="11"/>
@@ -15557,7 +15558,7 @@
       <c r="T41" s="11"/>
       <c r="U41" s="11"/>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
       <c r="I42" s="11"/>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
@@ -15570,18 +15571,18 @@
       <c r="R42" s="11"/>
       <c r="T42" s="11"/>
     </row>
-    <row r="60" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="145">
     <mergeCell ref="P35:T35"/>
@@ -15751,30 +15752,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A977F46-8BA4-4351-B711-8B8C14C849A9}">
   <dimension ref="A1:AR68"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="2.33203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="3.21875" style="8" customWidth="1"/>
+    <col min="1" max="4" width="2.35546875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="3.2109375" style="8" customWidth="1"/>
     <col min="6" max="8" width="1" style="8" customWidth="1"/>
-    <col min="9" max="10" width="2.33203125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="2.109375" style="8" customWidth="1"/>
+    <col min="9" max="10" width="2.35546875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" style="8" customWidth="1"/>
     <col min="12" max="12" width="1" style="8" customWidth="1"/>
-    <col min="13" max="13" width="2.33203125" style="8" customWidth="1"/>
+    <col min="13" max="13" width="2.35546875" style="8" customWidth="1"/>
     <col min="14" max="14" width="1" style="8" customWidth="1"/>
-    <col min="15" max="19" width="2.33203125" style="8" customWidth="1"/>
-    <col min="20" max="20" width="1.6640625" style="8" customWidth="1"/>
-    <col min="21" max="21" width="2.33203125" style="8" customWidth="1"/>
-    <col min="22" max="22" width="2.88671875" style="8" customWidth="1"/>
-    <col min="23" max="26" width="2.33203125" style="8" customWidth="1"/>
-    <col min="27" max="27" width="2.88671875" style="8" customWidth="1"/>
-    <col min="28" max="30" width="2.33203125" style="8" customWidth="1"/>
-    <col min="31" max="40" width="2.44140625" style="8" customWidth="1"/>
-    <col min="41" max="16384" width="8.6640625" style="8"/>
+    <col min="15" max="19" width="2.35546875" style="8" customWidth="1"/>
+    <col min="20" max="20" width="1.640625" style="8" customWidth="1"/>
+    <col min="21" max="21" width="2.35546875" style="8" customWidth="1"/>
+    <col min="22" max="22" width="2.85546875" style="8" customWidth="1"/>
+    <col min="23" max="26" width="2.35546875" style="8" customWidth="1"/>
+    <col min="27" max="27" width="2.85546875" style="8" customWidth="1"/>
+    <col min="28" max="30" width="2.35546875" style="8" customWidth="1"/>
+    <col min="31" max="40" width="2.42578125" style="8" customWidth="1"/>
+    <col min="41" max="16384" width="8.640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N1" s="120"/>
       <c r="O1" s="120"/>
@@ -15804,48 +15805,48 @@
       <c r="AM1" s="120"/>
       <c r="AN1" s="120"/>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A2" s="90" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A3" s="191"/>
-      <c r="B3" s="191"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="191"/>
-      <c r="H3" s="191"/>
-      <c r="I3" s="191"/>
-      <c r="J3" s="191"/>
-      <c r="K3" s="191"/>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
-      <c r="N3" s="191"/>
-      <c r="O3" s="191"/>
-      <c r="P3" s="191"/>
-      <c r="Q3" s="191"/>
-      <c r="R3" s="191"/>
-      <c r="S3" s="191"/>
-      <c r="T3" s="191"/>
-      <c r="U3" s="191"/>
-      <c r="V3" s="191"/>
-      <c r="W3" s="191"/>
-      <c r="X3" s="191"/>
-      <c r="Y3" s="191"/>
-      <c r="Z3" s="191"/>
-      <c r="AA3" s="191"/>
-      <c r="AB3" s="191"/>
-      <c r="AC3" s="191"/>
-      <c r="AD3" s="191"/>
-      <c r="AE3" s="191"/>
-      <c r="AF3" s="191"/>
-      <c r="AG3" s="191"/>
-      <c r="AH3" s="191"/>
-      <c r="AI3" s="191"/>
-      <c r="AJ3" s="191"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A3" s="192"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="192"/>
+      <c r="I3" s="192"/>
+      <c r="J3" s="192"/>
+      <c r="K3" s="192"/>
+      <c r="L3" s="192"/>
+      <c r="M3" s="192"/>
+      <c r="N3" s="192"/>
+      <c r="O3" s="192"/>
+      <c r="P3" s="192"/>
+      <c r="Q3" s="192"/>
+      <c r="R3" s="192"/>
+      <c r="S3" s="192"/>
+      <c r="T3" s="192"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="192"/>
+      <c r="W3" s="192"/>
+      <c r="X3" s="192"/>
+      <c r="Y3" s="192"/>
+      <c r="Z3" s="192"/>
+      <c r="AA3" s="192"/>
+      <c r="AB3" s="192"/>
+      <c r="AC3" s="192"/>
+      <c r="AD3" s="192"/>
+      <c r="AE3" s="192"/>
+      <c r="AF3" s="192"/>
+      <c r="AG3" s="192"/>
+      <c r="AH3" s="192"/>
+      <c r="AI3" s="192"/>
+      <c r="AJ3" s="192"/>
       <c r="AK3" s="102"/>
       <c r="AL3" s="102"/>
       <c r="AM3" s="102"/>
@@ -15855,9 +15856,9 @@
       <c r="AQ3" s="102"/>
       <c r="AR3" s="102"/>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B4" s="117"/>
       <c r="C4" s="117"/>
@@ -15874,12 +15875,12 @@
       <c r="N4" s="140"/>
       <c r="O4" s="140"/>
       <c r="P4" s="117" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q4" s="117"/>
       <c r="R4" s="117"/>
       <c r="S4" s="145" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T4" s="145"/>
       <c r="U4" s="145"/>
@@ -15897,7 +15898,7 @@
       <c r="AG4" s="145"/>
       <c r="AH4" s="145"/>
       <c r="AI4" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="11"/>
@@ -15906,9 +15907,9 @@
       <c r="AN4" s="11"/>
       <c r="AO4" s="103"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J5" s="140"/>
       <c r="K5" s="140"/>
@@ -15925,7 +15926,7 @@
       <c r="V5" s="140"/>
       <c r="W5" s="140"/>
       <c r="X5" s="52" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AE5" s="47"/>
@@ -15939,7 +15940,7 @@
       <c r="AM5" s="120"/>
       <c r="AN5" s="120"/>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A6" s="120"/>
       <c r="B6" s="120"/>
       <c r="C6" s="120"/>
@@ -15947,10 +15948,10 @@
       <c r="E6" s="120"/>
       <c r="F6" s="120"/>
       <c r="G6" s="47" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H6" s="152" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I6" s="152"/>
       <c r="J6" s="153"/>
@@ -15985,7 +15986,7 @@
       <c r="AM6" s="140"/>
       <c r="AN6" s="140"/>
     </row>
-    <row r="7" spans="1:44" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="120"/>
       <c r="B7" s="120"/>
       <c r="C7" s="120"/>
@@ -16029,9 +16030,9 @@
       <c r="AO7" s="103"/>
       <c r="AP7" s="103"/>
     </row>
-    <row r="8" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="179" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B8" s="180"/>
       <c r="C8" s="180"/>
@@ -16047,49 +16048,49 @@
       <c r="M8" s="105"/>
       <c r="N8" s="105"/>
       <c r="O8" s="105"/>
-      <c r="P8" s="273" t="s">
-        <v>176</v>
+      <c r="P8" s="183" t="s">
+        <v>173</v>
       </c>
       <c r="Q8" s="184"/>
       <c r="R8" s="184"/>
       <c r="S8" s="184"/>
       <c r="T8" s="185"/>
-      <c r="U8" s="183" t="s">
-        <v>87</v>
-      </c>
-      <c r="V8" s="183"/>
+      <c r="U8" s="190" t="s">
+        <v>84</v>
+      </c>
+      <c r="V8" s="190"/>
       <c r="W8" s="101"/>
       <c r="X8" s="184" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Y8" s="184"/>
-      <c r="Z8" s="190" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA8" s="183"/>
+      <c r="Z8" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA8" s="190"/>
       <c r="AB8" s="101"/>
       <c r="AC8" s="184" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AD8" s="185"/>
-      <c r="AE8" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF8" s="183"/>
-      <c r="AG8" s="183"/>
-      <c r="AH8" s="183"/>
-      <c r="AI8" s="192"/>
-      <c r="AJ8" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK8" s="183"/>
-      <c r="AL8" s="183"/>
-      <c r="AM8" s="183"/>
-      <c r="AN8" s="192"/>
+      <c r="AE8" s="191" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF8" s="190"/>
+      <c r="AG8" s="190"/>
+      <c r="AH8" s="190"/>
+      <c r="AI8" s="193"/>
+      <c r="AJ8" s="191" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK8" s="190"/>
+      <c r="AL8" s="190"/>
+      <c r="AM8" s="190"/>
+      <c r="AN8" s="193"/>
       <c r="AO8" s="103"/>
       <c r="AP8" s="103"/>
     </row>
-    <row r="9" spans="1:44" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="181"/>
       <c r="B9" s="182"/>
       <c r="C9" s="182"/>
@@ -16110,34 +16111,34 @@
       <c r="R9" s="186"/>
       <c r="S9" s="186"/>
       <c r="T9" s="187"/>
-      <c r="U9" s="274" t="s">
-        <v>177</v>
+      <c r="U9" s="197" t="s">
+        <v>174</v>
       </c>
       <c r="V9" s="186"/>
       <c r="W9" s="186"/>
       <c r="X9" s="186"/>
       <c r="Y9" s="186"/>
-      <c r="Z9" s="274" t="s">
-        <v>177</v>
+      <c r="Z9" s="197" t="s">
+        <v>174</v>
       </c>
       <c r="AA9" s="186"/>
       <c r="AB9" s="186"/>
       <c r="AC9" s="186"/>
       <c r="AD9" s="186"/>
-      <c r="AE9" s="193"/>
-      <c r="AF9" s="194"/>
-      <c r="AG9" s="194"/>
-      <c r="AH9" s="194"/>
-      <c r="AI9" s="195"/>
-      <c r="AJ9" s="193"/>
-      <c r="AK9" s="194"/>
-      <c r="AL9" s="194"/>
-      <c r="AM9" s="194"/>
-      <c r="AN9" s="195"/>
+      <c r="AE9" s="194"/>
+      <c r="AF9" s="195"/>
+      <c r="AG9" s="195"/>
+      <c r="AH9" s="195"/>
+      <c r="AI9" s="196"/>
+      <c r="AJ9" s="194"/>
+      <c r="AK9" s="195"/>
+      <c r="AL9" s="195"/>
+      <c r="AM9" s="195"/>
+      <c r="AN9" s="196"/>
       <c r="AO9" s="103"/>
       <c r="AP9" s="103"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A10" s="106" t="s">
         <v>60</v>
       </c>
@@ -16170,28 +16171,28 @@
       <c r="AB10" s="188"/>
       <c r="AC10" s="188"/>
       <c r="AD10" s="188"/>
-      <c r="AE10" s="196" t="s">
-        <v>87</v>
+      <c r="AE10" s="198" t="s">
+        <v>84</v>
       </c>
       <c r="AF10" s="188"/>
       <c r="AG10" s="100"/>
       <c r="AH10" s="188" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AI10" s="189"/>
-      <c r="AJ10" s="196" t="s">
-        <v>87</v>
+      <c r="AJ10" s="198" t="s">
+        <v>84</v>
       </c>
       <c r="AK10" s="188"/>
       <c r="AL10" s="100"/>
       <c r="AM10" s="188" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AN10" s="189"/>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A11" s="107" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -16202,11 +16203,11 @@
       <c r="H11" s="109"/>
       <c r="I11" s="109"/>
       <c r="J11" s="109"/>
-      <c r="K11" s="197"/>
-      <c r="L11" s="197"/>
-      <c r="M11" s="197"/>
-      <c r="N11" s="197"/>
-      <c r="O11" s="197"/>
+      <c r="K11" s="199"/>
+      <c r="L11" s="199"/>
+      <c r="M11" s="199"/>
+      <c r="N11" s="199"/>
+      <c r="O11" s="199"/>
       <c r="P11" s="127"/>
       <c r="Q11" s="128"/>
       <c r="R11" s="128"/>
@@ -16233,19 +16234,19 @@
       <c r="AM11" s="128"/>
       <c r="AN11" s="128"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A12" s="110" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G12" s="86"/>
       <c r="H12" s="86"/>
       <c r="I12" s="86"/>
       <c r="J12" s="86"/>
-      <c r="K12" s="198"/>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="198"/>
-      <c r="O12" s="198"/>
+      <c r="K12" s="200"/>
+      <c r="L12" s="200"/>
+      <c r="M12" s="200"/>
+      <c r="N12" s="200"/>
+      <c r="O12" s="200"/>
       <c r="P12" s="127"/>
       <c r="Q12" s="128"/>
       <c r="R12" s="128"/>
@@ -16272,19 +16273,19 @@
       <c r="AM12" s="128"/>
       <c r="AN12" s="128"/>
     </row>
-    <row r="13" spans="1:44" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="110" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G13" s="86"/>
       <c r="H13" s="86"/>
       <c r="I13" s="86"/>
       <c r="J13" s="86"/>
-      <c r="K13" s="198"/>
-      <c r="L13" s="198"/>
-      <c r="M13" s="198"/>
-      <c r="N13" s="198"/>
-      <c r="O13" s="198"/>
+      <c r="K13" s="200"/>
+      <c r="L13" s="200"/>
+      <c r="M13" s="200"/>
+      <c r="N13" s="200"/>
+      <c r="O13" s="200"/>
       <c r="P13" s="127"/>
       <c r="Q13" s="128"/>
       <c r="R13" s="128"/>
@@ -16311,19 +16312,19 @@
       <c r="AM13" s="128"/>
       <c r="AN13" s="128"/>
     </row>
-    <row r="14" spans="1:44" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:44" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="110" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G14" s="86"/>
       <c r="H14" s="86"/>
       <c r="I14" s="86"/>
       <c r="J14" s="86"/>
-      <c r="K14" s="198"/>
-      <c r="L14" s="198"/>
-      <c r="M14" s="198"/>
-      <c r="N14" s="198"/>
-      <c r="O14" s="198"/>
+      <c r="K14" s="200"/>
+      <c r="L14" s="200"/>
+      <c r="M14" s="200"/>
+      <c r="N14" s="200"/>
+      <c r="O14" s="200"/>
       <c r="P14" s="127"/>
       <c r="Q14" s="128"/>
       <c r="R14" s="128"/>
@@ -16350,9 +16351,9 @@
       <c r="AM14" s="128"/>
       <c r="AN14" s="128"/>
     </row>
-    <row r="15" spans="1:44" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:44" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="111" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B15" s="74"/>
       <c r="C15" s="74"/>
@@ -16394,51 +16395,51 @@
       <c r="AM15" s="128"/>
       <c r="AN15" s="128"/>
     </row>
-    <row r="16" spans="1:44" ht="5.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="199"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="199"/>
-      <c r="D16" s="199"/>
-      <c r="E16" s="199"/>
-      <c r="F16" s="199"/>
-      <c r="G16" s="199"/>
-      <c r="H16" s="199"/>
-      <c r="I16" s="199"/>
-      <c r="J16" s="199"/>
-      <c r="K16" s="199"/>
-      <c r="L16" s="199"/>
-      <c r="M16" s="199"/>
-      <c r="N16" s="199"/>
-      <c r="O16" s="199"/>
-      <c r="P16" s="199"/>
-      <c r="Q16" s="199"/>
-      <c r="R16" s="199"/>
-      <c r="S16" s="199"/>
-      <c r="T16" s="199"/>
-      <c r="U16" s="199"/>
-      <c r="V16" s="199"/>
-      <c r="W16" s="199"/>
-      <c r="X16" s="199"/>
-      <c r="Y16" s="199"/>
-      <c r="Z16" s="199"/>
-      <c r="AA16" s="199"/>
-      <c r="AB16" s="199"/>
-      <c r="AC16" s="199"/>
-      <c r="AD16" s="199"/>
-      <c r="AE16" s="199"/>
-      <c r="AF16" s="199"/>
-      <c r="AG16" s="199"/>
-      <c r="AH16" s="199"/>
-      <c r="AI16" s="199"/>
-      <c r="AJ16" s="199"/>
-      <c r="AK16" s="199"/>
-      <c r="AL16" s="199"/>
-      <c r="AM16" s="199"/>
-      <c r="AN16" s="199"/>
-    </row>
-    <row r="17" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" ht="5.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="201"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
+      <c r="F16" s="201"/>
+      <c r="G16" s="201"/>
+      <c r="H16" s="201"/>
+      <c r="I16" s="201"/>
+      <c r="J16" s="201"/>
+      <c r="K16" s="201"/>
+      <c r="L16" s="201"/>
+      <c r="M16" s="201"/>
+      <c r="N16" s="201"/>
+      <c r="O16" s="201"/>
+      <c r="P16" s="201"/>
+      <c r="Q16" s="201"/>
+      <c r="R16" s="201"/>
+      <c r="S16" s="201"/>
+      <c r="T16" s="201"/>
+      <c r="U16" s="201"/>
+      <c r="V16" s="201"/>
+      <c r="W16" s="201"/>
+      <c r="X16" s="201"/>
+      <c r="Y16" s="201"/>
+      <c r="Z16" s="201"/>
+      <c r="AA16" s="201"/>
+      <c r="AB16" s="201"/>
+      <c r="AC16" s="201"/>
+      <c r="AD16" s="201"/>
+      <c r="AE16" s="201"/>
+      <c r="AF16" s="201"/>
+      <c r="AG16" s="201"/>
+      <c r="AH16" s="201"/>
+      <c r="AI16" s="201"/>
+      <c r="AJ16" s="201"/>
+      <c r="AK16" s="201"/>
+      <c r="AL16" s="201"/>
+      <c r="AM16" s="201"/>
+      <c r="AN16" s="201"/>
+    </row>
+    <row r="17" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="179" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B17" s="180"/>
       <c r="C17" s="180"/>
@@ -16454,47 +16455,47 @@
       <c r="M17" s="105"/>
       <c r="N17" s="105"/>
       <c r="O17" s="105"/>
-      <c r="P17" s="273" t="s">
-        <v>176</v>
+      <c r="P17" s="183" t="s">
+        <v>173</v>
       </c>
       <c r="Q17" s="184"/>
       <c r="R17" s="184"/>
       <c r="S17" s="184"/>
       <c r="T17" s="185"/>
-      <c r="U17" s="183" t="s">
-        <v>87</v>
-      </c>
-      <c r="V17" s="183"/>
+      <c r="U17" s="190" t="s">
+        <v>84</v>
+      </c>
+      <c r="V17" s="190"/>
       <c r="W17" s="101"/>
       <c r="X17" s="184" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Y17" s="184"/>
-      <c r="Z17" s="190" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA17" s="183"/>
+      <c r="Z17" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA17" s="190"/>
       <c r="AB17" s="101"/>
       <c r="AC17" s="184" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AD17" s="185"/>
-      <c r="AE17" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF17" s="183"/>
-      <c r="AG17" s="183"/>
-      <c r="AH17" s="183"/>
-      <c r="AI17" s="192"/>
-      <c r="AJ17" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK17" s="183"/>
-      <c r="AL17" s="183"/>
-      <c r="AM17" s="183"/>
-      <c r="AN17" s="192"/>
-    </row>
-    <row r="18" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE17" s="191" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF17" s="190"/>
+      <c r="AG17" s="190"/>
+      <c r="AH17" s="190"/>
+      <c r="AI17" s="193"/>
+      <c r="AJ17" s="191" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK17" s="190"/>
+      <c r="AL17" s="190"/>
+      <c r="AM17" s="190"/>
+      <c r="AN17" s="193"/>
+    </row>
+    <row r="18" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="181"/>
       <c r="B18" s="182"/>
       <c r="C18" s="182"/>
@@ -16515,32 +16516,32 @@
       <c r="R18" s="186"/>
       <c r="S18" s="186"/>
       <c r="T18" s="187"/>
-      <c r="U18" s="274" t="s">
-        <v>177</v>
+      <c r="U18" s="197" t="s">
+        <v>174</v>
       </c>
       <c r="V18" s="186"/>
       <c r="W18" s="186"/>
       <c r="X18" s="186"/>
       <c r="Y18" s="186"/>
-      <c r="Z18" s="274" t="s">
-        <v>177</v>
+      <c r="Z18" s="197" t="s">
+        <v>174</v>
       </c>
       <c r="AA18" s="186"/>
       <c r="AB18" s="186"/>
       <c r="AC18" s="186"/>
       <c r="AD18" s="186"/>
-      <c r="AE18" s="193"/>
-      <c r="AF18" s="194"/>
-      <c r="AG18" s="194"/>
-      <c r="AH18" s="194"/>
-      <c r="AI18" s="195"/>
-      <c r="AJ18" s="193"/>
-      <c r="AK18" s="194"/>
-      <c r="AL18" s="194"/>
-      <c r="AM18" s="194"/>
-      <c r="AN18" s="195"/>
-    </row>
-    <row r="19" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE18" s="194"/>
+      <c r="AF18" s="195"/>
+      <c r="AG18" s="195"/>
+      <c r="AH18" s="195"/>
+      <c r="AI18" s="196"/>
+      <c r="AJ18" s="194"/>
+      <c r="AK18" s="195"/>
+      <c r="AL18" s="195"/>
+      <c r="AM18" s="195"/>
+      <c r="AN18" s="196"/>
+    </row>
+    <row r="19" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="106" t="s">
         <v>60</v>
       </c>
@@ -16573,28 +16574,28 @@
       <c r="AB19" s="188"/>
       <c r="AC19" s="188"/>
       <c r="AD19" s="188"/>
-      <c r="AE19" s="196" t="s">
-        <v>87</v>
+      <c r="AE19" s="198" t="s">
+        <v>84</v>
       </c>
       <c r="AF19" s="188"/>
       <c r="AG19" s="101"/>
       <c r="AH19" s="188" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AI19" s="189"/>
-      <c r="AJ19" s="196" t="s">
-        <v>87</v>
+      <c r="AJ19" s="198" t="s">
+        <v>84</v>
       </c>
       <c r="AK19" s="188"/>
       <c r="AL19" s="100"/>
       <c r="AM19" s="188" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AN19" s="189"/>
     </row>
-    <row r="20" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="107" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B20" s="108"/>
       <c r="C20" s="108"/>
@@ -16636,9 +16637,9 @@
       <c r="AM20" s="135"/>
       <c r="AN20" s="136"/>
     </row>
-    <row r="21" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="113" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G21" s="86"/>
       <c r="H21" s="86"/>
@@ -16672,9 +16673,9 @@
       <c r="AM21" s="138"/>
       <c r="AN21" s="139"/>
     </row>
-    <row r="22" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="110" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G22" s="86"/>
       <c r="H22" s="86"/>
@@ -16708,9 +16709,9 @@
       <c r="AM22" s="123"/>
       <c r="AN22" s="133"/>
     </row>
-    <row r="23" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="110" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G23" s="86"/>
       <c r="H23" s="86"/>
@@ -16744,9 +16745,9 @@
       <c r="AM23" s="128"/>
       <c r="AN23" s="128"/>
     </row>
-    <row r="24" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="111" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
@@ -16788,51 +16789,51 @@
       <c r="AM24" s="128"/>
       <c r="AN24" s="128"/>
     </row>
-    <row r="25" spans="1:40" ht="4.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="199"/>
-      <c r="B25" s="199"/>
-      <c r="C25" s="199"/>
-      <c r="D25" s="199"/>
-      <c r="E25" s="199"/>
-      <c r="F25" s="199"/>
-      <c r="G25" s="199"/>
-      <c r="H25" s="199"/>
-      <c r="I25" s="199"/>
-      <c r="J25" s="199"/>
-      <c r="K25" s="199"/>
-      <c r="L25" s="199"/>
-      <c r="M25" s="199"/>
-      <c r="N25" s="199"/>
-      <c r="O25" s="199"/>
-      <c r="P25" s="199"/>
-      <c r="Q25" s="199"/>
-      <c r="R25" s="199"/>
-      <c r="S25" s="199"/>
-      <c r="T25" s="199"/>
-      <c r="U25" s="199"/>
-      <c r="V25" s="199"/>
-      <c r="W25" s="199"/>
-      <c r="X25" s="199"/>
-      <c r="Y25" s="199"/>
-      <c r="Z25" s="199"/>
-      <c r="AA25" s="199"/>
-      <c r="AB25" s="199"/>
-      <c r="AC25" s="199"/>
-      <c r="AD25" s="199"/>
-      <c r="AE25" s="199"/>
-      <c r="AF25" s="199"/>
-      <c r="AG25" s="199"/>
-      <c r="AH25" s="199"/>
-      <c r="AI25" s="199"/>
-      <c r="AJ25" s="199"/>
-      <c r="AK25" s="199"/>
-      <c r="AL25" s="199"/>
-      <c r="AM25" s="199"/>
-      <c r="AN25" s="199"/>
-    </row>
-    <row r="26" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" ht="4.8499999999999996" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="201"/>
+      <c r="B25" s="201"/>
+      <c r="C25" s="201"/>
+      <c r="D25" s="201"/>
+      <c r="E25" s="201"/>
+      <c r="F25" s="201"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="201"/>
+      <c r="I25" s="201"/>
+      <c r="J25" s="201"/>
+      <c r="K25" s="201"/>
+      <c r="L25" s="201"/>
+      <c r="M25" s="201"/>
+      <c r="N25" s="201"/>
+      <c r="O25" s="201"/>
+      <c r="P25" s="201"/>
+      <c r="Q25" s="201"/>
+      <c r="R25" s="201"/>
+      <c r="S25" s="201"/>
+      <c r="T25" s="201"/>
+      <c r="U25" s="201"/>
+      <c r="V25" s="201"/>
+      <c r="W25" s="201"/>
+      <c r="X25" s="201"/>
+      <c r="Y25" s="201"/>
+      <c r="Z25" s="201"/>
+      <c r="AA25" s="201"/>
+      <c r="AB25" s="201"/>
+      <c r="AC25" s="201"/>
+      <c r="AD25" s="201"/>
+      <c r="AE25" s="201"/>
+      <c r="AF25" s="201"/>
+      <c r="AG25" s="201"/>
+      <c r="AH25" s="201"/>
+      <c r="AI25" s="201"/>
+      <c r="AJ25" s="201"/>
+      <c r="AK25" s="201"/>
+      <c r="AL25" s="201"/>
+      <c r="AM25" s="201"/>
+      <c r="AN25" s="201"/>
+    </row>
+    <row r="26" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="179" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B26" s="180"/>
       <c r="C26" s="180"/>
@@ -16848,47 +16849,47 @@
       <c r="M26" s="105"/>
       <c r="N26" s="105"/>
       <c r="O26" s="105"/>
-      <c r="P26" s="273" t="s">
-        <v>176</v>
+      <c r="P26" s="183" t="s">
+        <v>173</v>
       </c>
       <c r="Q26" s="184"/>
       <c r="R26" s="184"/>
       <c r="S26" s="184"/>
       <c r="T26" s="185"/>
-      <c r="U26" s="183" t="s">
-        <v>87</v>
-      </c>
-      <c r="V26" s="183"/>
+      <c r="U26" s="190" t="s">
+        <v>84</v>
+      </c>
+      <c r="V26" s="190"/>
       <c r="W26" s="101"/>
       <c r="X26" s="184" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Y26" s="184"/>
-      <c r="Z26" s="190" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA26" s="183"/>
+      <c r="Z26" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA26" s="190"/>
       <c r="AB26" s="101"/>
       <c r="AC26" s="184" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AD26" s="185"/>
-      <c r="AE26" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF26" s="183"/>
-      <c r="AG26" s="183"/>
-      <c r="AH26" s="183"/>
-      <c r="AI26" s="192"/>
-      <c r="AJ26" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK26" s="183"/>
-      <c r="AL26" s="183"/>
-      <c r="AM26" s="183"/>
-      <c r="AN26" s="192"/>
-    </row>
-    <row r="27" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE26" s="191" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF26" s="190"/>
+      <c r="AG26" s="190"/>
+      <c r="AH26" s="190"/>
+      <c r="AI26" s="193"/>
+      <c r="AJ26" s="191" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK26" s="190"/>
+      <c r="AL26" s="190"/>
+      <c r="AM26" s="190"/>
+      <c r="AN26" s="193"/>
+    </row>
+    <row r="27" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="181"/>
       <c r="B27" s="182"/>
       <c r="C27" s="182"/>
@@ -16909,32 +16910,32 @@
       <c r="R27" s="186"/>
       <c r="S27" s="186"/>
       <c r="T27" s="187"/>
-      <c r="U27" s="274" t="s">
-        <v>177</v>
+      <c r="U27" s="197" t="s">
+        <v>174</v>
       </c>
       <c r="V27" s="186"/>
       <c r="W27" s="186"/>
       <c r="X27" s="186"/>
       <c r="Y27" s="186"/>
-      <c r="Z27" s="274" t="s">
-        <v>177</v>
+      <c r="Z27" s="197" t="s">
+        <v>174</v>
       </c>
       <c r="AA27" s="186"/>
       <c r="AB27" s="186"/>
       <c r="AC27" s="186"/>
       <c r="AD27" s="186"/>
-      <c r="AE27" s="193"/>
-      <c r="AF27" s="194"/>
-      <c r="AG27" s="194"/>
-      <c r="AH27" s="194"/>
-      <c r="AI27" s="195"/>
-      <c r="AJ27" s="193"/>
-      <c r="AK27" s="194"/>
-      <c r="AL27" s="194"/>
-      <c r="AM27" s="194"/>
-      <c r="AN27" s="195"/>
-    </row>
-    <row r="28" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE27" s="194"/>
+      <c r="AF27" s="195"/>
+      <c r="AG27" s="195"/>
+      <c r="AH27" s="195"/>
+      <c r="AI27" s="196"/>
+      <c r="AJ27" s="194"/>
+      <c r="AK27" s="195"/>
+      <c r="AL27" s="195"/>
+      <c r="AM27" s="195"/>
+      <c r="AN27" s="196"/>
+    </row>
+    <row r="28" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="106" t="s">
         <v>60</v>
       </c>
@@ -16967,28 +16968,28 @@
       <c r="AB28" s="188"/>
       <c r="AC28" s="188"/>
       <c r="AD28" s="188"/>
-      <c r="AE28" s="196" t="s">
-        <v>87</v>
+      <c r="AE28" s="198" t="s">
+        <v>84</v>
       </c>
       <c r="AF28" s="188"/>
       <c r="AG28" s="101"/>
       <c r="AH28" s="188" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AI28" s="189"/>
-      <c r="AJ28" s="196" t="s">
-        <v>87</v>
+      <c r="AJ28" s="198" t="s">
+        <v>84</v>
       </c>
       <c r="AK28" s="188"/>
       <c r="AL28" s="100"/>
       <c r="AM28" s="188" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AN28" s="189"/>
     </row>
-    <row r="29" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="107" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B29" s="108"/>
       <c r="C29" s="108"/>
@@ -16999,11 +17000,11 @@
       <c r="H29" s="109"/>
       <c r="I29" s="109"/>
       <c r="J29" s="109"/>
-      <c r="K29" s="197"/>
-      <c r="L29" s="197"/>
-      <c r="M29" s="197"/>
-      <c r="N29" s="197"/>
-      <c r="O29" s="197"/>
+      <c r="K29" s="199"/>
+      <c r="L29" s="199"/>
+      <c r="M29" s="199"/>
+      <c r="N29" s="199"/>
+      <c r="O29" s="199"/>
       <c r="P29" s="127"/>
       <c r="Q29" s="128"/>
       <c r="R29" s="128"/>
@@ -17030,19 +17031,19 @@
       <c r="AM29" s="128"/>
       <c r="AN29" s="128"/>
     </row>
-    <row r="30" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="110" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G30" s="86"/>
       <c r="H30" s="86"/>
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
-      <c r="K30" s="198"/>
-      <c r="L30" s="198"/>
-      <c r="M30" s="198"/>
-      <c r="N30" s="198"/>
-      <c r="O30" s="198"/>
+      <c r="K30" s="200"/>
+      <c r="L30" s="200"/>
+      <c r="M30" s="200"/>
+      <c r="N30" s="200"/>
+      <c r="O30" s="200"/>
       <c r="P30" s="127"/>
       <c r="Q30" s="128"/>
       <c r="R30" s="128"/>
@@ -17069,19 +17070,19 @@
       <c r="AM30" s="128"/>
       <c r="AN30" s="128"/>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A31" s="110" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G31" s="86"/>
       <c r="H31" s="86"/>
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
-      <c r="K31" s="198"/>
-      <c r="L31" s="198"/>
-      <c r="M31" s="198"/>
-      <c r="N31" s="198"/>
-      <c r="O31" s="198"/>
+      <c r="K31" s="200"/>
+      <c r="L31" s="200"/>
+      <c r="M31" s="200"/>
+      <c r="N31" s="200"/>
+      <c r="O31" s="200"/>
       <c r="P31" s="127"/>
       <c r="Q31" s="128"/>
       <c r="R31" s="128"/>
@@ -17108,19 +17109,19 @@
       <c r="AM31" s="128"/>
       <c r="AN31" s="128"/>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A32" s="110" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G32" s="86"/>
       <c r="H32" s="86"/>
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
-      <c r="K32" s="198"/>
-      <c r="L32" s="198"/>
-      <c r="M32" s="198"/>
-      <c r="N32" s="198"/>
-      <c r="O32" s="198"/>
+      <c r="K32" s="200"/>
+      <c r="L32" s="200"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="200"/>
+      <c r="O32" s="200"/>
       <c r="P32" s="127"/>
       <c r="Q32" s="128"/>
       <c r="R32" s="128"/>
@@ -17147,19 +17148,19 @@
       <c r="AM32" s="128"/>
       <c r="AN32" s="128"/>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A33" s="110" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G33" s="86"/>
       <c r="H33" s="86"/>
       <c r="I33" s="86"/>
       <c r="J33" s="86"/>
-      <c r="K33" s="198"/>
-      <c r="L33" s="198"/>
-      <c r="M33" s="198"/>
-      <c r="N33" s="198"/>
-      <c r="O33" s="198"/>
+      <c r="K33" s="200"/>
+      <c r="L33" s="200"/>
+      <c r="M33" s="200"/>
+      <c r="N33" s="200"/>
+      <c r="O33" s="200"/>
       <c r="P33" s="127"/>
       <c r="Q33" s="128"/>
       <c r="R33" s="128"/>
@@ -17186,9 +17187,9 @@
       <c r="AM33" s="128"/>
       <c r="AN33" s="128"/>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A34" s="111" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
@@ -17230,7 +17231,7 @@
       <c r="AM34" s="128"/>
       <c r="AN34" s="128"/>
     </row>
-    <row r="35" spans="1:40" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" ht="7.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="103"/>
       <c r="G35" s="86"/>
       <c r="H35" s="86"/>
@@ -17264,9 +17265,9 @@
       <c r="AM35" s="12"/>
       <c r="AN35" s="12"/>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A36" s="96" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G36" s="86"/>
       <c r="H36" s="86"/>
@@ -17300,9 +17301,9 @@
       <c r="AM36" s="12"/>
       <c r="AN36" s="12"/>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A37" s="96" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G37" s="86"/>
       <c r="H37" s="86"/>
@@ -17336,7 +17337,7 @@
       <c r="AM37" s="12"/>
       <c r="AN37" s="12"/>
     </row>
-    <row r="38" spans="1:40" ht="7.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" ht="7.85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="103"/>
       <c r="G38" s="86"/>
       <c r="H38" s="86"/>
@@ -17370,9 +17371,9 @@
       <c r="AM38" s="12"/>
       <c r="AN38" s="12"/>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A39" s="103" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G39" s="86"/>
       <c r="H39" s="86"/>
@@ -17406,7 +17407,7 @@
       <c r="AM39" s="12"/>
       <c r="AN39" s="12"/>
     </row>
-    <row r="40" spans="1:40" ht="7.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" ht="7.85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="103"/>
       <c r="G40" s="86"/>
       <c r="H40" s="86"/>
@@ -17440,9 +17441,9 @@
       <c r="AM40" s="12"/>
       <c r="AN40" s="12"/>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G41" s="86"/>
       <c r="H41" s="86"/>
@@ -17456,7 +17457,7 @@
       <c r="AE41" s="86"/>
       <c r="AF41" s="104"/>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
       <c r="G42" s="86"/>
       <c r="H42" s="86"/>
       <c r="I42" s="86"/>
@@ -17469,7 +17470,7 @@
       <c r="AE42" s="86"/>
       <c r="AF42" s="104"/>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.35">
       <c r="G43" s="86"/>
       <c r="H43" s="86"/>
       <c r="I43" s="86"/>
@@ -17482,7 +17483,7 @@
       <c r="AE43" s="86"/>
       <c r="AF43" s="104"/>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.35">
       <c r="G44" s="86"/>
       <c r="H44" s="86"/>
       <c r="I44" s="86"/>
@@ -17495,7 +17496,7 @@
       <c r="AE44" s="86"/>
       <c r="AF44" s="104"/>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.35">
       <c r="G45" s="86"/>
       <c r="H45" s="86"/>
       <c r="I45" s="86"/>
@@ -17508,7 +17509,7 @@
       <c r="AE45" s="86"/>
       <c r="AF45" s="104"/>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.35">
       <c r="G46" s="86"/>
       <c r="H46" s="86"/>
       <c r="I46" s="86"/>
@@ -17521,7 +17522,7 @@
       <c r="AE46" s="86"/>
       <c r="AF46" s="104"/>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.35">
       <c r="G47" s="86"/>
       <c r="H47" s="86"/>
       <c r="I47" s="86"/>
@@ -17534,7 +17535,7 @@
       <c r="AE47" s="86"/>
       <c r="AF47" s="104"/>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.35">
       <c r="G48" s="86"/>
       <c r="H48" s="86"/>
       <c r="I48" s="86"/>
@@ -17547,7 +17548,7 @@
       <c r="AE48" s="86"/>
       <c r="AF48" s="104"/>
     </row>
-    <row r="49" spans="7:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:32" x14ac:dyDescent="0.35">
       <c r="G49" s="86"/>
       <c r="H49" s="86"/>
       <c r="I49" s="86"/>
@@ -17560,7 +17561,7 @@
       <c r="AE49" s="86"/>
       <c r="AF49" s="104"/>
     </row>
-    <row r="50" spans="7:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:32" x14ac:dyDescent="0.35">
       <c r="G50" s="86"/>
       <c r="H50" s="86"/>
       <c r="I50" s="86"/>
@@ -17573,7 +17574,7 @@
       <c r="AE50" s="86"/>
       <c r="AF50" s="104"/>
     </row>
-    <row r="51" spans="7:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:32" x14ac:dyDescent="0.35">
       <c r="G51" s="86"/>
       <c r="H51" s="86"/>
       <c r="I51" s="86"/>
@@ -17586,7 +17587,7 @@
       <c r="AE51" s="86"/>
       <c r="AF51" s="104"/>
     </row>
-    <row r="52" spans="7:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:32" x14ac:dyDescent="0.35">
       <c r="G52" s="86"/>
       <c r="H52" s="86"/>
       <c r="I52" s="86"/>
@@ -17599,7 +17600,7 @@
       <c r="AE52" s="86"/>
       <c r="AF52" s="104"/>
     </row>
-    <row r="53" spans="7:32" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:32" x14ac:dyDescent="0.35">
       <c r="G53" s="86"/>
       <c r="H53" s="86"/>
       <c r="I53" s="86"/>
@@ -17612,18 +17613,18 @@
       <c r="AE53" s="86"/>
       <c r="AF53" s="104"/>
     </row>
-    <row r="57" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="7:32" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="130">
     <mergeCell ref="H6:L6"/>
@@ -17777,23 +17778,23 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7DE8E7-2625-4A3B-9EAB-8620E596E4ED}">
-  <dimension ref="A1:AS58"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AS59"/>
+  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="2.33203125" style="8" customWidth="1"/>
+    <col min="1" max="4" width="2.35546875" style="8" customWidth="1"/>
     <col min="5" max="8" width="1" style="8" customWidth="1"/>
-    <col min="9" max="10" width="2.33203125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="2.109375" style="8" customWidth="1"/>
+    <col min="9" max="10" width="2.35546875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" style="8" customWidth="1"/>
     <col min="12" max="12" width="1" style="8" customWidth="1"/>
-    <col min="13" max="13" width="2.33203125" style="8" customWidth="1"/>
+    <col min="13" max="13" width="2.35546875" style="8" customWidth="1"/>
     <col min="14" max="14" width="1" style="8" customWidth="1"/>
-    <col min="15" max="40" width="2.33203125" style="8" customWidth="1"/>
-    <col min="41" max="16384" width="8.6640625" style="8"/>
+    <col min="15" max="40" width="2.35546875" style="8" customWidth="1"/>
+    <col min="41" max="16384" width="8.640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P1" s="120"/>
       <c r="Q1" s="120"/>
@@ -17821,34 +17822,34 @@
       <c r="AM1" s="120"/>
       <c r="AN1" s="120"/>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A2" s="90" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A3" s="191"/>
-      <c r="B3" s="191"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="191"/>
-      <c r="H3" s="191"/>
-      <c r="I3" s="191"/>
-      <c r="J3" s="191"/>
-      <c r="K3" s="191"/>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
-      <c r="N3" s="191"/>
-      <c r="O3" s="191"/>
-      <c r="P3" s="191"/>
-      <c r="Q3" s="191"/>
-      <c r="R3" s="191"/>
-      <c r="S3" s="191"/>
-      <c r="T3" s="191"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A3" s="192"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="192"/>
+      <c r="I3" s="192"/>
+      <c r="J3" s="192"/>
+      <c r="K3" s="192"/>
+      <c r="L3" s="192"/>
+      <c r="M3" s="192"/>
+      <c r="N3" s="192"/>
+      <c r="O3" s="192"/>
+      <c r="P3" s="192"/>
+      <c r="Q3" s="192"/>
+      <c r="R3" s="192"/>
+      <c r="S3" s="192"/>
+      <c r="T3" s="192"/>
       <c r="U3" s="91" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="V3" s="92"/>
       <c r="W3" s="92"/>
@@ -17875,7 +17876,7 @@
       <c r="AR3" s="92"/>
       <c r="AS3" s="92"/>
     </row>
-    <row r="4" spans="1:45" ht="4.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" ht="4.8499999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="92"/>
       <c r="B4" s="92"/>
       <c r="C4" s="92"/>
@@ -17920,15 +17921,17 @@
       <c r="AP4" s="94"/>
       <c r="AQ4" s="94"/>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A5" s="92" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="92"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
+      <c r="C5" s="218">
+        <v>1</v>
+      </c>
+      <c r="D5" s="218"/>
       <c r="E5" s="92" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F5" s="92"/>
       <c r="G5" s="92"/>
@@ -17969,7 +17972,7 @@
       <c r="AP5" s="94"/>
       <c r="AQ5" s="94"/>
     </row>
-    <row r="6" spans="1:45" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" ht="3.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="92"/>
       <c r="B6" s="92"/>
       <c r="C6" s="95"/>
@@ -18014,9 +18017,9 @@
       <c r="AP6" s="94"/>
       <c r="AQ6" s="94"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7" s="96" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B7" s="95"/>
       <c r="C7" s="95"/>
@@ -18045,526 +18048,526 @@
       <c r="AA7" s="58"/>
       <c r="AB7" s="58"/>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A8" s="205" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="206"/>
-      <c r="C8" s="206"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="206"/>
-      <c r="H8" s="206"/>
-      <c r="I8" s="207"/>
-      <c r="J8" s="203" t="s">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A8" s="207" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="208"/>
+      <c r="C8" s="208"/>
+      <c r="D8" s="208"/>
+      <c r="E8" s="208"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
+      <c r="I8" s="209"/>
+      <c r="J8" s="205" t="s">
+        <v>209</v>
+      </c>
+      <c r="K8" s="205"/>
+      <c r="L8" s="205"/>
+      <c r="M8" s="205"/>
+      <c r="N8" s="205"/>
+      <c r="O8" s="205"/>
+      <c r="P8" s="205"/>
+      <c r="Q8" s="205"/>
+      <c r="R8" s="205"/>
+      <c r="S8" s="205"/>
+      <c r="T8" s="205"/>
+      <c r="U8" s="205" t="s">
+        <v>210</v>
+      </c>
+      <c r="V8" s="205"/>
+      <c r="W8" s="205"/>
+      <c r="X8" s="205"/>
+      <c r="Y8" s="205"/>
+      <c r="Z8" s="205"/>
+      <c r="AA8" s="205"/>
+      <c r="AB8" s="205"/>
+      <c r="AC8" s="205"/>
+      <c r="AD8" s="205"/>
+      <c r="AE8" s="205" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF8" s="205"/>
+      <c r="AG8" s="205"/>
+      <c r="AH8" s="205"/>
+      <c r="AI8" s="205"/>
+      <c r="AJ8" s="205"/>
+      <c r="AK8" s="205"/>
+      <c r="AL8" s="205"/>
+      <c r="AM8" s="205"/>
+      <c r="AN8" s="205"/>
+    </row>
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A9" s="210"/>
+      <c r="B9" s="211"/>
+      <c r="C9" s="211"/>
+      <c r="D9" s="211"/>
+      <c r="E9" s="211"/>
+      <c r="F9" s="211"/>
+      <c r="G9" s="211"/>
+      <c r="H9" s="211"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="205"/>
+      <c r="L9" s="205"/>
+      <c r="M9" s="205"/>
+      <c r="N9" s="205"/>
+      <c r="O9" s="205"/>
+      <c r="P9" s="205"/>
+      <c r="Q9" s="205"/>
+      <c r="R9" s="205"/>
+      <c r="S9" s="205"/>
+      <c r="T9" s="205"/>
+      <c r="U9" s="205"/>
+      <c r="V9" s="205"/>
+      <c r="W9" s="205"/>
+      <c r="X9" s="205"/>
+      <c r="Y9" s="205"/>
+      <c r="Z9" s="205"/>
+      <c r="AA9" s="205"/>
+      <c r="AB9" s="205"/>
+      <c r="AC9" s="205"/>
+      <c r="AD9" s="205"/>
+      <c r="AE9" s="205"/>
+      <c r="AF9" s="205"/>
+      <c r="AG9" s="205"/>
+      <c r="AH9" s="205"/>
+      <c r="AI9" s="205"/>
+      <c r="AJ9" s="205"/>
+      <c r="AK9" s="205"/>
+      <c r="AL9" s="205"/>
+      <c r="AM9" s="205"/>
+      <c r="AN9" s="205"/>
+    </row>
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A10" s="202"/>
+      <c r="B10" s="203"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="203"/>
+      <c r="H10" s="203"/>
+      <c r="I10" s="204"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="205"/>
+      <c r="L10" s="205"/>
+      <c r="M10" s="205"/>
+      <c r="N10" s="205"/>
+      <c r="O10" s="205"/>
+      <c r="P10" s="205"/>
+      <c r="Q10" s="205"/>
+      <c r="R10" s="205"/>
+      <c r="S10" s="205"/>
+      <c r="T10" s="205"/>
+      <c r="U10" s="205"/>
+      <c r="V10" s="205"/>
+      <c r="W10" s="205"/>
+      <c r="X10" s="205"/>
+      <c r="Y10" s="205"/>
+      <c r="Z10" s="205"/>
+      <c r="AA10" s="205"/>
+      <c r="AB10" s="205"/>
+      <c r="AC10" s="205"/>
+      <c r="AD10" s="205"/>
+      <c r="AE10" s="205"/>
+      <c r="AF10" s="205"/>
+      <c r="AG10" s="205"/>
+      <c r="AH10" s="205"/>
+      <c r="AI10" s="205"/>
+      <c r="AJ10" s="205"/>
+      <c r="AK10" s="205"/>
+      <c r="AL10" s="205"/>
+      <c r="AM10" s="205"/>
+      <c r="AN10" s="205"/>
+    </row>
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A11" s="202"/>
+      <c r="B11" s="203"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="203"/>
+      <c r="H11" s="203"/>
+      <c r="I11" s="204"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="205"/>
+      <c r="L11" s="205"/>
+      <c r="M11" s="205"/>
+      <c r="N11" s="205"/>
+      <c r="O11" s="205"/>
+      <c r="P11" s="205"/>
+      <c r="Q11" s="205"/>
+      <c r="R11" s="205"/>
+      <c r="S11" s="205"/>
+      <c r="T11" s="205"/>
+      <c r="U11" s="205"/>
+      <c r="V11" s="205"/>
+      <c r="W11" s="205"/>
+      <c r="X11" s="205"/>
+      <c r="Y11" s="205"/>
+      <c r="Z11" s="205"/>
+      <c r="AA11" s="205"/>
+      <c r="AB11" s="205"/>
+      <c r="AC11" s="205"/>
+      <c r="AD11" s="205"/>
+      <c r="AE11" s="205"/>
+      <c r="AF11" s="205"/>
+      <c r="AG11" s="205"/>
+      <c r="AH11" s="205"/>
+      <c r="AI11" s="205"/>
+      <c r="AJ11" s="205"/>
+      <c r="AK11" s="205"/>
+      <c r="AL11" s="205"/>
+      <c r="AM11" s="205"/>
+      <c r="AN11" s="205"/>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A12" s="202"/>
+      <c r="B12" s="203"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="203"/>
+      <c r="I12" s="204"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="205"/>
+      <c r="M12" s="205"/>
+      <c r="N12" s="205"/>
+      <c r="O12" s="205"/>
+      <c r="P12" s="205"/>
+      <c r="Q12" s="205"/>
+      <c r="R12" s="205"/>
+      <c r="S12" s="205"/>
+      <c r="T12" s="205"/>
+      <c r="U12" s="205"/>
+      <c r="V12" s="205"/>
+      <c r="W12" s="205"/>
+      <c r="X12" s="205"/>
+      <c r="Y12" s="205"/>
+      <c r="Z12" s="205"/>
+      <c r="AA12" s="205"/>
+      <c r="AB12" s="205"/>
+      <c r="AC12" s="205"/>
+      <c r="AD12" s="205"/>
+      <c r="AE12" s="205"/>
+      <c r="AF12" s="205"/>
+      <c r="AG12" s="205"/>
+      <c r="AH12" s="205"/>
+      <c r="AI12" s="205"/>
+      <c r="AJ12" s="205"/>
+      <c r="AK12" s="205"/>
+      <c r="AL12" s="205"/>
+      <c r="AM12" s="205"/>
+      <c r="AN12" s="205"/>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="K8" s="203"/>
-      <c r="L8" s="203"/>
-      <c r="M8" s="203"/>
-      <c r="N8" s="203"/>
-      <c r="O8" s="203"/>
-      <c r="P8" s="203"/>
-      <c r="Q8" s="203"/>
-      <c r="R8" s="203"/>
-      <c r="S8" s="203"/>
-      <c r="T8" s="203"/>
-      <c r="U8" s="203" t="s">
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A14" s="96" t="s">
         <v>213</v>
       </c>
-      <c r="V8" s="203"/>
-      <c r="W8" s="203"/>
-      <c r="X8" s="203"/>
-      <c r="Y8" s="203"/>
-      <c r="Z8" s="203"/>
-      <c r="AA8" s="203"/>
-      <c r="AB8" s="203"/>
-      <c r="AC8" s="203"/>
-      <c r="AD8" s="203"/>
-      <c r="AE8" s="203" t="s">
+    </row>
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A15" s="207" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+      <c r="F15" s="208"/>
+      <c r="G15" s="208"/>
+      <c r="H15" s="208"/>
+      <c r="I15" s="209"/>
+      <c r="J15" s="205" t="s">
         <v>214</v>
       </c>
-      <c r="AF8" s="203"/>
-      <c r="AG8" s="203"/>
-      <c r="AH8" s="203"/>
-      <c r="AI8" s="203"/>
-      <c r="AJ8" s="203"/>
-      <c r="AK8" s="203"/>
-      <c r="AL8" s="203"/>
-      <c r="AM8" s="203"/>
-      <c r="AN8" s="203"/>
-    </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A9" s="208"/>
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
-      <c r="D9" s="209"/>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="210"/>
-      <c r="J9" s="203"/>
-      <c r="K9" s="203"/>
-      <c r="L9" s="203"/>
-      <c r="M9" s="203"/>
-      <c r="N9" s="203"/>
-      <c r="O9" s="203"/>
-      <c r="P9" s="203"/>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="203"/>
-      <c r="S9" s="203"/>
-      <c r="T9" s="203"/>
-      <c r="U9" s="203"/>
-      <c r="V9" s="203"/>
-      <c r="W9" s="203"/>
-      <c r="X9" s="203"/>
-      <c r="Y9" s="203"/>
-      <c r="Z9" s="203"/>
-      <c r="AA9" s="203"/>
-      <c r="AB9" s="203"/>
-      <c r="AC9" s="203"/>
-      <c r="AD9" s="203"/>
-      <c r="AE9" s="203"/>
-      <c r="AF9" s="203"/>
-      <c r="AG9" s="203"/>
-      <c r="AH9" s="203"/>
-      <c r="AI9" s="203"/>
-      <c r="AJ9" s="203"/>
-      <c r="AK9" s="203"/>
-      <c r="AL9" s="203"/>
-      <c r="AM9" s="203"/>
-      <c r="AN9" s="203"/>
-    </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A10" s="200"/>
-      <c r="B10" s="201"/>
-      <c r="C10" s="201"/>
-      <c r="D10" s="201"/>
-      <c r="E10" s="201"/>
-      <c r="F10" s="201"/>
-      <c r="G10" s="201"/>
-      <c r="H10" s="201"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="203"/>
-      <c r="K10" s="203"/>
-      <c r="L10" s="203"/>
-      <c r="M10" s="203"/>
-      <c r="N10" s="203"/>
-      <c r="O10" s="203"/>
-      <c r="P10" s="203"/>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="203"/>
-      <c r="S10" s="203"/>
-      <c r="T10" s="203"/>
-      <c r="U10" s="203"/>
-      <c r="V10" s="203"/>
-      <c r="W10" s="203"/>
-      <c r="X10" s="203"/>
-      <c r="Y10" s="203"/>
-      <c r="Z10" s="203"/>
-      <c r="AA10" s="203"/>
-      <c r="AB10" s="203"/>
-      <c r="AC10" s="203"/>
-      <c r="AD10" s="203"/>
-      <c r="AE10" s="203"/>
-      <c r="AF10" s="203"/>
-      <c r="AG10" s="203"/>
-      <c r="AH10" s="203"/>
-      <c r="AI10" s="203"/>
-      <c r="AJ10" s="203"/>
-      <c r="AK10" s="203"/>
-      <c r="AL10" s="203"/>
-      <c r="AM10" s="203"/>
-      <c r="AN10" s="203"/>
-    </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A11" s="200"/>
-      <c r="B11" s="201"/>
-      <c r="C11" s="201"/>
-      <c r="D11" s="201"/>
-      <c r="E11" s="201"/>
-      <c r="F11" s="201"/>
-      <c r="G11" s="201"/>
-      <c r="H11" s="201"/>
-      <c r="I11" s="202"/>
-      <c r="J11" s="203"/>
-      <c r="K11" s="203"/>
-      <c r="L11" s="203"/>
-      <c r="M11" s="203"/>
-      <c r="N11" s="203"/>
-      <c r="O11" s="203"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="203"/>
-      <c r="S11" s="203"/>
-      <c r="T11" s="203"/>
-      <c r="U11" s="203"/>
-      <c r="V11" s="203"/>
-      <c r="W11" s="203"/>
-      <c r="X11" s="203"/>
-      <c r="Y11" s="203"/>
-      <c r="Z11" s="203"/>
-      <c r="AA11" s="203"/>
-      <c r="AB11" s="203"/>
-      <c r="AC11" s="203"/>
-      <c r="AD11" s="203"/>
-      <c r="AE11" s="203"/>
-      <c r="AF11" s="203"/>
-      <c r="AG11" s="203"/>
-      <c r="AH11" s="203"/>
-      <c r="AI11" s="203"/>
-      <c r="AJ11" s="203"/>
-      <c r="AK11" s="203"/>
-      <c r="AL11" s="203"/>
-      <c r="AM11" s="203"/>
-      <c r="AN11" s="203"/>
-    </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A12" s="200"/>
-      <c r="B12" s="201"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="201"/>
-      <c r="E12" s="201"/>
-      <c r="F12" s="201"/>
-      <c r="G12" s="201"/>
-      <c r="H12" s="201"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="203"/>
-      <c r="K12" s="203"/>
-      <c r="L12" s="203"/>
-      <c r="M12" s="203"/>
-      <c r="N12" s="203"/>
-      <c r="O12" s="203"/>
-      <c r="P12" s="203"/>
-      <c r="Q12" s="203"/>
-      <c r="R12" s="203"/>
-      <c r="S12" s="203"/>
-      <c r="T12" s="203"/>
-      <c r="U12" s="203"/>
-      <c r="V12" s="203"/>
-      <c r="W12" s="203"/>
-      <c r="X12" s="203"/>
-      <c r="Y12" s="203"/>
-      <c r="Z12" s="203"/>
-      <c r="AA12" s="203"/>
-      <c r="AB12" s="203"/>
-      <c r="AC12" s="203"/>
-      <c r="AD12" s="203"/>
-      <c r="AE12" s="203"/>
-      <c r="AF12" s="203"/>
-      <c r="AG12" s="203"/>
-      <c r="AH12" s="203"/>
-      <c r="AI12" s="203"/>
-      <c r="AJ12" s="203"/>
-      <c r="AK12" s="203"/>
-      <c r="AL12" s="203"/>
-      <c r="AM12" s="203"/>
-      <c r="AN12" s="203"/>
-    </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="K15" s="205"/>
+      <c r="L15" s="205"/>
+      <c r="M15" s="205"/>
+      <c r="N15" s="205"/>
+      <c r="O15" s="205"/>
+      <c r="P15" s="205"/>
+      <c r="Q15" s="205"/>
+      <c r="R15" s="205"/>
+      <c r="S15" s="205"/>
+      <c r="T15" s="205"/>
+      <c r="U15" s="205" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A14" s="96" t="s">
+      <c r="V15" s="205"/>
+      <c r="W15" s="205"/>
+      <c r="X15" s="205"/>
+      <c r="Y15" s="205"/>
+      <c r="Z15" s="205"/>
+      <c r="AA15" s="205"/>
+      <c r="AB15" s="205"/>
+      <c r="AC15" s="205"/>
+      <c r="AD15" s="205"/>
+      <c r="AE15" s="205" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF15" s="205"/>
+      <c r="AG15" s="205"/>
+      <c r="AH15" s="205"/>
+      <c r="AI15" s="205"/>
+      <c r="AJ15" s="205"/>
+      <c r="AK15" s="205"/>
+      <c r="AL15" s="205"/>
+      <c r="AM15" s="205"/>
+      <c r="AN15" s="205"/>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
+      <c r="C16" s="211"/>
+      <c r="D16" s="211"/>
+      <c r="E16" s="211"/>
+      <c r="F16" s="211"/>
+      <c r="G16" s="211"/>
+      <c r="H16" s="211"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="205"/>
+      <c r="M16" s="205"/>
+      <c r="N16" s="205"/>
+      <c r="O16" s="205"/>
+      <c r="P16" s="205"/>
+      <c r="Q16" s="205"/>
+      <c r="R16" s="205"/>
+      <c r="S16" s="205"/>
+      <c r="T16" s="205"/>
+      <c r="U16" s="205"/>
+      <c r="V16" s="205"/>
+      <c r="W16" s="205"/>
+      <c r="X16" s="205"/>
+      <c r="Y16" s="205"/>
+      <c r="Z16" s="205"/>
+      <c r="AA16" s="205"/>
+      <c r="AB16" s="205"/>
+      <c r="AC16" s="205"/>
+      <c r="AD16" s="205"/>
+      <c r="AE16" s="205"/>
+      <c r="AF16" s="205"/>
+      <c r="AG16" s="205"/>
+      <c r="AH16" s="205"/>
+      <c r="AI16" s="205"/>
+      <c r="AJ16" s="205"/>
+      <c r="AK16" s="205"/>
+      <c r="AL16" s="205"/>
+      <c r="AM16" s="205"/>
+      <c r="AN16" s="205"/>
+    </row>
+    <row r="17" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A17" s="202"/>
+      <c r="B17" s="203"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="203"/>
+      <c r="H17" s="203"/>
+      <c r="I17" s="204"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="205"/>
+      <c r="L17" s="205"/>
+      <c r="M17" s="205"/>
+      <c r="N17" s="205"/>
+      <c r="O17" s="205"/>
+      <c r="P17" s="205"/>
+      <c r="Q17" s="205"/>
+      <c r="R17" s="205"/>
+      <c r="S17" s="205"/>
+      <c r="T17" s="205"/>
+      <c r="U17" s="205"/>
+      <c r="V17" s="205"/>
+      <c r="W17" s="205"/>
+      <c r="X17" s="205"/>
+      <c r="Y17" s="205"/>
+      <c r="Z17" s="205"/>
+      <c r="AA17" s="205"/>
+      <c r="AB17" s="205"/>
+      <c r="AC17" s="205"/>
+      <c r="AD17" s="205"/>
+      <c r="AE17" s="205"/>
+      <c r="AF17" s="205"/>
+      <c r="AG17" s="205"/>
+      <c r="AH17" s="205"/>
+      <c r="AI17" s="205"/>
+      <c r="AJ17" s="205"/>
+      <c r="AK17" s="205"/>
+      <c r="AL17" s="205"/>
+      <c r="AM17" s="205"/>
+      <c r="AN17" s="205"/>
+    </row>
+    <row r="18" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A18" s="202"/>
+      <c r="B18" s="203"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="203"/>
+      <c r="I18" s="204"/>
+      <c r="J18" s="205"/>
+      <c r="K18" s="205"/>
+      <c r="L18" s="205"/>
+      <c r="M18" s="205"/>
+      <c r="N18" s="205"/>
+      <c r="O18" s="205"/>
+      <c r="P18" s="205"/>
+      <c r="Q18" s="205"/>
+      <c r="R18" s="205"/>
+      <c r="S18" s="205"/>
+      <c r="T18" s="205"/>
+      <c r="U18" s="205"/>
+      <c r="V18" s="205"/>
+      <c r="W18" s="205"/>
+      <c r="X18" s="205"/>
+      <c r="Y18" s="205"/>
+      <c r="Z18" s="205"/>
+      <c r="AA18" s="205"/>
+      <c r="AB18" s="205"/>
+      <c r="AC18" s="205"/>
+      <c r="AD18" s="205"/>
+      <c r="AE18" s="205"/>
+      <c r="AF18" s="205"/>
+      <c r="AG18" s="205"/>
+      <c r="AH18" s="205"/>
+      <c r="AI18" s="205"/>
+      <c r="AJ18" s="205"/>
+      <c r="AK18" s="205"/>
+      <c r="AL18" s="205"/>
+      <c r="AM18" s="205"/>
+      <c r="AN18" s="205"/>
+    </row>
+    <row r="19" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A15" s="205" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="206"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-      <c r="F15" s="206"/>
-      <c r="G15" s="206"/>
-      <c r="H15" s="206"/>
-      <c r="I15" s="207"/>
-      <c r="J15" s="203" t="s">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A20" s="96" t="s">
         <v>217</v>
       </c>
-      <c r="K15" s="203"/>
-      <c r="L15" s="203"/>
-      <c r="M15" s="203"/>
-      <c r="N15" s="203"/>
-      <c r="O15" s="203"/>
-      <c r="P15" s="203"/>
-      <c r="Q15" s="203"/>
-      <c r="R15" s="203"/>
-      <c r="S15" s="203"/>
-      <c r="T15" s="203"/>
-      <c r="U15" s="203" t="s">
+    </row>
+    <row r="21" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A21" s="207" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="208"/>
+      <c r="C21" s="208"/>
+      <c r="D21" s="208"/>
+      <c r="E21" s="208"/>
+      <c r="F21" s="208"/>
+      <c r="G21" s="208"/>
+      <c r="H21" s="208"/>
+      <c r="I21" s="209"/>
+      <c r="J21" s="207" t="s">
         <v>218</v>
       </c>
-      <c r="V15" s="203"/>
-      <c r="W15" s="203"/>
-      <c r="X15" s="203"/>
-      <c r="Y15" s="203"/>
-      <c r="Z15" s="203"/>
-      <c r="AA15" s="203"/>
-      <c r="AB15" s="203"/>
-      <c r="AC15" s="203"/>
-      <c r="AD15" s="203"/>
-      <c r="AE15" s="203" t="s">
-        <v>214</v>
-      </c>
-      <c r="AF15" s="203"/>
-      <c r="AG15" s="203"/>
-      <c r="AH15" s="203"/>
-      <c r="AI15" s="203"/>
-      <c r="AJ15" s="203"/>
-      <c r="AK15" s="203"/>
-      <c r="AL15" s="203"/>
-      <c r="AM15" s="203"/>
-      <c r="AN15" s="203"/>
-    </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A16" s="208"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
-      <c r="F16" s="209"/>
-      <c r="G16" s="209"/>
-      <c r="H16" s="209"/>
-      <c r="I16" s="210"/>
-      <c r="J16" s="203"/>
-      <c r="K16" s="203"/>
-      <c r="L16" s="203"/>
-      <c r="M16" s="203"/>
-      <c r="N16" s="203"/>
-      <c r="O16" s="203"/>
-      <c r="P16" s="203"/>
-      <c r="Q16" s="203"/>
-      <c r="R16" s="203"/>
-      <c r="S16" s="203"/>
-      <c r="T16" s="203"/>
-      <c r="U16" s="203"/>
-      <c r="V16" s="203"/>
-      <c r="W16" s="203"/>
-      <c r="X16" s="203"/>
-      <c r="Y16" s="203"/>
-      <c r="Z16" s="203"/>
-      <c r="AA16" s="203"/>
-      <c r="AB16" s="203"/>
-      <c r="AC16" s="203"/>
-      <c r="AD16" s="203"/>
-      <c r="AE16" s="203"/>
-      <c r="AF16" s="203"/>
-      <c r="AG16" s="203"/>
-      <c r="AH16" s="203"/>
-      <c r="AI16" s="203"/>
-      <c r="AJ16" s="203"/>
-      <c r="AK16" s="203"/>
-      <c r="AL16" s="203"/>
-      <c r="AM16" s="203"/>
-      <c r="AN16" s="203"/>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A17" s="200"/>
-      <c r="B17" s="201"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="201"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="203"/>
-      <c r="K17" s="203"/>
-      <c r="L17" s="203"/>
-      <c r="M17" s="203"/>
-      <c r="N17" s="203"/>
-      <c r="O17" s="203"/>
-      <c r="P17" s="203"/>
-      <c r="Q17" s="203"/>
-      <c r="R17" s="203"/>
-      <c r="S17" s="203"/>
-      <c r="T17" s="203"/>
-      <c r="U17" s="203"/>
-      <c r="V17" s="203"/>
-      <c r="W17" s="203"/>
-      <c r="X17" s="203"/>
-      <c r="Y17" s="203"/>
-      <c r="Z17" s="203"/>
-      <c r="AA17" s="203"/>
-      <c r="AB17" s="203"/>
-      <c r="AC17" s="203"/>
-      <c r="AD17" s="203"/>
-      <c r="AE17" s="203"/>
-      <c r="AF17" s="203"/>
-      <c r="AG17" s="203"/>
-      <c r="AH17" s="203"/>
-      <c r="AI17" s="203"/>
-      <c r="AJ17" s="203"/>
-      <c r="AK17" s="203"/>
-      <c r="AL17" s="203"/>
-      <c r="AM17" s="203"/>
-      <c r="AN17" s="203"/>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A18" s="200"/>
-      <c r="B18" s="201"/>
-      <c r="C18" s="201"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="201"/>
-      <c r="F18" s="201"/>
-      <c r="G18" s="201"/>
-      <c r="H18" s="201"/>
-      <c r="I18" s="202"/>
-      <c r="J18" s="203"/>
-      <c r="K18" s="203"/>
-      <c r="L18" s="203"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="203"/>
-      <c r="O18" s="203"/>
-      <c r="P18" s="203"/>
-      <c r="Q18" s="203"/>
-      <c r="R18" s="203"/>
-      <c r="S18" s="203"/>
-      <c r="T18" s="203"/>
-      <c r="U18" s="203"/>
-      <c r="V18" s="203"/>
-      <c r="W18" s="203"/>
-      <c r="X18" s="203"/>
-      <c r="Y18" s="203"/>
-      <c r="Z18" s="203"/>
-      <c r="AA18" s="203"/>
-      <c r="AB18" s="203"/>
-      <c r="AC18" s="203"/>
-      <c r="AD18" s="203"/>
-      <c r="AE18" s="203"/>
-      <c r="AF18" s="203"/>
-      <c r="AG18" s="203"/>
-      <c r="AH18" s="203"/>
-      <c r="AI18" s="203"/>
-      <c r="AJ18" s="203"/>
-      <c r="AK18" s="203"/>
-      <c r="AL18" s="203"/>
-      <c r="AM18" s="203"/>
-      <c r="AN18" s="203"/>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="K21" s="208"/>
+      <c r="L21" s="208"/>
+      <c r="M21" s="208"/>
+      <c r="N21" s="208"/>
+      <c r="O21" s="208"/>
+      <c r="P21" s="209"/>
+      <c r="Q21" s="207" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A20" s="96" t="s">
+      <c r="R21" s="208"/>
+      <c r="S21" s="208"/>
+      <c r="T21" s="208"/>
+      <c r="U21" s="208"/>
+      <c r="V21" s="208"/>
+      <c r="W21" s="207" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A21" s="205" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="206"/>
-      <c r="C21" s="206"/>
-      <c r="D21" s="206"/>
-      <c r="E21" s="206"/>
-      <c r="F21" s="206"/>
-      <c r="G21" s="206"/>
-      <c r="H21" s="206"/>
-      <c r="I21" s="207"/>
-      <c r="J21" s="205" t="s">
+      <c r="X21" s="208"/>
+      <c r="Y21" s="208"/>
+      <c r="Z21" s="208"/>
+      <c r="AA21" s="208"/>
+      <c r="AB21" s="208"/>
+      <c r="AC21" s="207" t="s">
         <v>221</v>
       </c>
-      <c r="K21" s="206"/>
-      <c r="L21" s="206"/>
-      <c r="M21" s="206"/>
-      <c r="N21" s="206"/>
-      <c r="O21" s="206"/>
-      <c r="P21" s="207"/>
-      <c r="Q21" s="205" t="s">
-        <v>222</v>
-      </c>
-      <c r="R21" s="206"/>
-      <c r="S21" s="206"/>
-      <c r="T21" s="206"/>
-      <c r="U21" s="206"/>
-      <c r="V21" s="206"/>
-      <c r="W21" s="205" t="s">
-        <v>223</v>
-      </c>
-      <c r="X21" s="206"/>
-      <c r="Y21" s="206"/>
-      <c r="Z21" s="206"/>
-      <c r="AA21" s="206"/>
-      <c r="AB21" s="206"/>
-      <c r="AC21" s="205" t="s">
-        <v>224</v>
-      </c>
-      <c r="AD21" s="206"/>
-      <c r="AE21" s="206"/>
-      <c r="AF21" s="206"/>
-      <c r="AG21" s="206"/>
-      <c r="AH21" s="207"/>
-      <c r="AI21" s="205" t="s">
-        <v>214</v>
-      </c>
-      <c r="AJ21" s="206"/>
-      <c r="AK21" s="206"/>
-      <c r="AL21" s="206"/>
-      <c r="AM21" s="206"/>
-      <c r="AN21" s="207"/>
-    </row>
-    <row r="22" spans="1:44" s="94" customFormat="1" ht="8.5500000000000007" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="208"/>
-      <c r="B22" s="209"/>
-      <c r="C22" s="209"/>
-      <c r="D22" s="209"/>
-      <c r="E22" s="209"/>
-      <c r="F22" s="209"/>
-      <c r="G22" s="209"/>
-      <c r="H22" s="209"/>
-      <c r="I22" s="210"/>
-      <c r="J22" s="208"/>
-      <c r="K22" s="209"/>
-      <c r="L22" s="209"/>
-      <c r="M22" s="209"/>
-      <c r="N22" s="209"/>
-      <c r="O22" s="209"/>
-      <c r="P22" s="210"/>
-      <c r="Q22" s="208"/>
-      <c r="R22" s="209"/>
-      <c r="S22" s="209"/>
-      <c r="T22" s="209"/>
-      <c r="U22" s="209"/>
-      <c r="V22" s="209"/>
-      <c r="W22" s="208"/>
-      <c r="X22" s="209"/>
-      <c r="Y22" s="209"/>
-      <c r="Z22" s="209"/>
-      <c r="AA22" s="209"/>
-      <c r="AB22" s="209"/>
-      <c r="AC22" s="208"/>
-      <c r="AD22" s="209"/>
-      <c r="AE22" s="209"/>
-      <c r="AF22" s="209"/>
-      <c r="AG22" s="209"/>
-      <c r="AH22" s="210"/>
-      <c r="AI22" s="213"/>
-      <c r="AJ22" s="214"/>
-      <c r="AK22" s="214"/>
-      <c r="AL22" s="214"/>
-      <c r="AM22" s="214"/>
-      <c r="AN22" s="215"/>
-    </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A23" s="211"/>
-      <c r="B23" s="211"/>
-      <c r="C23" s="211"/>
-      <c r="D23" s="211"/>
-      <c r="E23" s="211"/>
-      <c r="F23" s="211"/>
-      <c r="G23" s="211"/>
-      <c r="H23" s="211"/>
-      <c r="I23" s="211"/>
+      <c r="AD21" s="208"/>
+      <c r="AE21" s="208"/>
+      <c r="AF21" s="208"/>
+      <c r="AG21" s="208"/>
+      <c r="AH21" s="209"/>
+      <c r="AI21" s="207" t="s">
+        <v>211</v>
+      </c>
+      <c r="AJ21" s="208"/>
+      <c r="AK21" s="208"/>
+      <c r="AL21" s="208"/>
+      <c r="AM21" s="208"/>
+      <c r="AN21" s="209"/>
+    </row>
+    <row r="22" spans="1:44" s="94" customFormat="1" ht="8.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="210"/>
+      <c r="B22" s="211"/>
+      <c r="C22" s="211"/>
+      <c r="D22" s="211"/>
+      <c r="E22" s="211"/>
+      <c r="F22" s="211"/>
+      <c r="G22" s="211"/>
+      <c r="H22" s="211"/>
+      <c r="I22" s="212"/>
+      <c r="J22" s="210"/>
+      <c r="K22" s="211"/>
+      <c r="L22" s="211"/>
+      <c r="M22" s="211"/>
+      <c r="N22" s="211"/>
+      <c r="O22" s="211"/>
+      <c r="P22" s="212"/>
+      <c r="Q22" s="210"/>
+      <c r="R22" s="211"/>
+      <c r="S22" s="211"/>
+      <c r="T22" s="211"/>
+      <c r="U22" s="211"/>
+      <c r="V22" s="211"/>
+      <c r="W22" s="210"/>
+      <c r="X22" s="211"/>
+      <c r="Y22" s="211"/>
+      <c r="Z22" s="211"/>
+      <c r="AA22" s="211"/>
+      <c r="AB22" s="211"/>
+      <c r="AC22" s="210"/>
+      <c r="AD22" s="211"/>
+      <c r="AE22" s="211"/>
+      <c r="AF22" s="211"/>
+      <c r="AG22" s="211"/>
+      <c r="AH22" s="212"/>
+      <c r="AI22" s="215"/>
+      <c r="AJ22" s="216"/>
+      <c r="AK22" s="216"/>
+      <c r="AL22" s="216"/>
+      <c r="AM22" s="216"/>
+      <c r="AN22" s="217"/>
+    </row>
+    <row r="23" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A23" s="213"/>
+      <c r="B23" s="213"/>
+      <c r="C23" s="213"/>
+      <c r="D23" s="213"/>
+      <c r="E23" s="213"/>
+      <c r="F23" s="213"/>
+      <c r="G23" s="213"/>
+      <c r="H23" s="213"/>
+      <c r="I23" s="213"/>
       <c r="J23" s="128"/>
       <c r="K23" s="128"/>
       <c r="L23" s="128"/>
@@ -18590,23 +18593,23 @@
       <c r="AF23" s="128"/>
       <c r="AG23" s="128"/>
       <c r="AH23" s="128"/>
-      <c r="AI23" s="212"/>
-      <c r="AJ23" s="212"/>
-      <c r="AK23" s="212"/>
-      <c r="AL23" s="212"/>
-      <c r="AM23" s="212"/>
-      <c r="AN23" s="212"/>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A24" s="211"/>
-      <c r="B24" s="211"/>
-      <c r="C24" s="211"/>
-      <c r="D24" s="211"/>
-      <c r="E24" s="211"/>
-      <c r="F24" s="211"/>
-      <c r="G24" s="211"/>
-      <c r="H24" s="211"/>
-      <c r="I24" s="211"/>
+      <c r="AI23" s="214"/>
+      <c r="AJ23" s="214"/>
+      <c r="AK23" s="214"/>
+      <c r="AL23" s="214"/>
+      <c r="AM23" s="214"/>
+      <c r="AN23" s="214"/>
+    </row>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A24" s="213"/>
+      <c r="B24" s="213"/>
+      <c r="C24" s="213"/>
+      <c r="D24" s="213"/>
+      <c r="E24" s="213"/>
+      <c r="F24" s="213"/>
+      <c r="G24" s="213"/>
+      <c r="H24" s="213"/>
+      <c r="I24" s="213"/>
       <c r="J24" s="128"/>
       <c r="K24" s="128"/>
       <c r="L24" s="128"/>
@@ -18632,16 +18635,16 @@
       <c r="AF24" s="128"/>
       <c r="AG24" s="128"/>
       <c r="AH24" s="128"/>
-      <c r="AI24" s="203"/>
-      <c r="AJ24" s="203"/>
-      <c r="AK24" s="203"/>
-      <c r="AL24" s="203"/>
-      <c r="AM24" s="203"/>
-      <c r="AN24" s="203"/>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AI24" s="205"/>
+      <c r="AJ24" s="205"/>
+      <c r="AK24" s="205"/>
+      <c r="AL24" s="205"/>
+      <c r="AM24" s="205"/>
+      <c r="AN24" s="205"/>
+    </row>
+    <row r="25" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B25" s="97"/>
       <c r="C25" s="97"/>
@@ -18683,239 +18686,239 @@
       <c r="AM25" s="95"/>
       <c r="AN25" s="95"/>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A26" s="96" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A27" s="205" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="206"/>
-      <c r="C27" s="206"/>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="206"/>
-      <c r="G27" s="206"/>
-      <c r="H27" s="206"/>
-      <c r="I27" s="207"/>
-      <c r="J27" s="203" t="s">
-        <v>227</v>
-      </c>
-      <c r="K27" s="203"/>
-      <c r="L27" s="203"/>
-      <c r="M27" s="203"/>
-      <c r="N27" s="203"/>
-      <c r="O27" s="203"/>
-      <c r="P27" s="203"/>
-      <c r="Q27" s="203"/>
-      <c r="R27" s="203"/>
-      <c r="S27" s="203"/>
-      <c r="T27" s="203"/>
-      <c r="U27" s="203" t="s">
-        <v>228</v>
-      </c>
-      <c r="V27" s="203"/>
-      <c r="W27" s="203"/>
-      <c r="X27" s="203"/>
-      <c r="Y27" s="203"/>
-      <c r="Z27" s="203"/>
-      <c r="AA27" s="203"/>
-      <c r="AB27" s="203"/>
-      <c r="AC27" s="203"/>
-      <c r="AD27" s="203"/>
-      <c r="AE27" s="203" t="s">
-        <v>214</v>
-      </c>
-      <c r="AF27" s="203"/>
-      <c r="AG27" s="203"/>
-      <c r="AH27" s="203"/>
-      <c r="AI27" s="203"/>
-      <c r="AJ27" s="203"/>
-      <c r="AK27" s="203"/>
-      <c r="AL27" s="203"/>
-      <c r="AM27" s="203"/>
-      <c r="AN27" s="203"/>
-    </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A28" s="208"/>
-      <c r="B28" s="209"/>
-      <c r="C28" s="209"/>
-      <c r="D28" s="209"/>
-      <c r="E28" s="209"/>
-      <c r="F28" s="209"/>
-      <c r="G28" s="209"/>
-      <c r="H28" s="209"/>
-      <c r="I28" s="210"/>
-      <c r="J28" s="203"/>
-      <c r="K28" s="203"/>
-      <c r="L28" s="203"/>
-      <c r="M28" s="203"/>
-      <c r="N28" s="203"/>
-      <c r="O28" s="203"/>
-      <c r="P28" s="203"/>
-      <c r="Q28" s="203"/>
-      <c r="R28" s="203"/>
-      <c r="S28" s="203"/>
-      <c r="T28" s="203"/>
-      <c r="U28" s="203"/>
-      <c r="V28" s="203"/>
-      <c r="W28" s="203"/>
-      <c r="X28" s="203"/>
-      <c r="Y28" s="203"/>
-      <c r="Z28" s="203"/>
-      <c r="AA28" s="203"/>
-      <c r="AB28" s="203"/>
-      <c r="AC28" s="203"/>
-      <c r="AD28" s="203"/>
-      <c r="AE28" s="203"/>
-      <c r="AF28" s="203"/>
-      <c r="AG28" s="203"/>
-      <c r="AH28" s="203"/>
-      <c r="AI28" s="203"/>
-      <c r="AJ28" s="203"/>
-      <c r="AK28" s="203"/>
-      <c r="AL28" s="203"/>
-      <c r="AM28" s="203"/>
-      <c r="AN28" s="203"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A27" s="207" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="208"/>
+      <c r="C27" s="208"/>
+      <c r="D27" s="208"/>
+      <c r="E27" s="208"/>
+      <c r="F27" s="208"/>
+      <c r="G27" s="208"/>
+      <c r="H27" s="208"/>
+      <c r="I27" s="209"/>
+      <c r="J27" s="205" t="s">
+        <v>224</v>
+      </c>
+      <c r="K27" s="205"/>
+      <c r="L27" s="205"/>
+      <c r="M27" s="205"/>
+      <c r="N27" s="205"/>
+      <c r="O27" s="205"/>
+      <c r="P27" s="205"/>
+      <c r="Q27" s="205"/>
+      <c r="R27" s="205"/>
+      <c r="S27" s="205"/>
+      <c r="T27" s="205"/>
+      <c r="U27" s="205" t="s">
+        <v>225</v>
+      </c>
+      <c r="V27" s="205"/>
+      <c r="W27" s="205"/>
+      <c r="X27" s="205"/>
+      <c r="Y27" s="205"/>
+      <c r="Z27" s="205"/>
+      <c r="AA27" s="205"/>
+      <c r="AB27" s="205"/>
+      <c r="AC27" s="205"/>
+      <c r="AD27" s="205"/>
+      <c r="AE27" s="205" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF27" s="205"/>
+      <c r="AG27" s="205"/>
+      <c r="AH27" s="205"/>
+      <c r="AI27" s="205"/>
+      <c r="AJ27" s="205"/>
+      <c r="AK27" s="205"/>
+      <c r="AL27" s="205"/>
+      <c r="AM27" s="205"/>
+      <c r="AN27" s="205"/>
+    </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A28" s="210"/>
+      <c r="B28" s="211"/>
+      <c r="C28" s="211"/>
+      <c r="D28" s="211"/>
+      <c r="E28" s="211"/>
+      <c r="F28" s="211"/>
+      <c r="G28" s="211"/>
+      <c r="H28" s="211"/>
+      <c r="I28" s="212"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="205"/>
+      <c r="L28" s="205"/>
+      <c r="M28" s="205"/>
+      <c r="N28" s="205"/>
+      <c r="O28" s="205"/>
+      <c r="P28" s="205"/>
+      <c r="Q28" s="205"/>
+      <c r="R28" s="205"/>
+      <c r="S28" s="205"/>
+      <c r="T28" s="205"/>
+      <c r="U28" s="205"/>
+      <c r="V28" s="205"/>
+      <c r="W28" s="205"/>
+      <c r="X28" s="205"/>
+      <c r="Y28" s="205"/>
+      <c r="Z28" s="205"/>
+      <c r="AA28" s="205"/>
+      <c r="AB28" s="205"/>
+      <c r="AC28" s="205"/>
+      <c r="AD28" s="205"/>
+      <c r="AE28" s="205"/>
+      <c r="AF28" s="205"/>
+      <c r="AG28" s="205"/>
+      <c r="AH28" s="205"/>
+      <c r="AI28" s="205"/>
+      <c r="AJ28" s="205"/>
+      <c r="AK28" s="205"/>
+      <c r="AL28" s="205"/>
+      <c r="AM28" s="205"/>
+      <c r="AN28" s="205"/>
       <c r="AO28" s="94"/>
       <c r="AP28" s="94"/>
       <c r="AQ28" s="94"/>
       <c r="AR28" s="94"/>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A29" s="200"/>
-      <c r="B29" s="201"/>
-      <c r="C29" s="201"/>
-      <c r="D29" s="201"/>
-      <c r="E29" s="201"/>
-      <c r="F29" s="201"/>
-      <c r="G29" s="201"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="203"/>
-      <c r="K29" s="203"/>
-      <c r="L29" s="203"/>
-      <c r="M29" s="203"/>
-      <c r="N29" s="203"/>
-      <c r="O29" s="203"/>
-      <c r="P29" s="203"/>
-      <c r="Q29" s="203"/>
-      <c r="R29" s="203"/>
-      <c r="S29" s="203"/>
-      <c r="T29" s="203"/>
-      <c r="U29" s="203"/>
-      <c r="V29" s="203"/>
-      <c r="W29" s="203"/>
-      <c r="X29" s="203"/>
-      <c r="Y29" s="203"/>
-      <c r="Z29" s="203"/>
-      <c r="AA29" s="203"/>
-      <c r="AB29" s="203"/>
-      <c r="AC29" s="203"/>
-      <c r="AD29" s="203"/>
-      <c r="AE29" s="203"/>
-      <c r="AF29" s="203"/>
-      <c r="AG29" s="203"/>
-      <c r="AH29" s="203"/>
-      <c r="AI29" s="203"/>
-      <c r="AJ29" s="203"/>
-      <c r="AK29" s="203"/>
-      <c r="AL29" s="203"/>
-      <c r="AM29" s="203"/>
-      <c r="AN29" s="203"/>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A29" s="202"/>
+      <c r="B29" s="203"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="203"/>
+      <c r="I29" s="204"/>
+      <c r="J29" s="205"/>
+      <c r="K29" s="205"/>
+      <c r="L29" s="205"/>
+      <c r="M29" s="205"/>
+      <c r="N29" s="205"/>
+      <c r="O29" s="205"/>
+      <c r="P29" s="205"/>
+      <c r="Q29" s="205"/>
+      <c r="R29" s="205"/>
+      <c r="S29" s="205"/>
+      <c r="T29" s="205"/>
+      <c r="U29" s="205"/>
+      <c r="V29" s="205"/>
+      <c r="W29" s="205"/>
+      <c r="X29" s="205"/>
+      <c r="Y29" s="205"/>
+      <c r="Z29" s="205"/>
+      <c r="AA29" s="205"/>
+      <c r="AB29" s="205"/>
+      <c r="AC29" s="205"/>
+      <c r="AD29" s="205"/>
+      <c r="AE29" s="205"/>
+      <c r="AF29" s="205"/>
+      <c r="AG29" s="205"/>
+      <c r="AH29" s="205"/>
+      <c r="AI29" s="205"/>
+      <c r="AJ29" s="205"/>
+      <c r="AK29" s="205"/>
+      <c r="AL29" s="205"/>
+      <c r="AM29" s="205"/>
+      <c r="AN29" s="205"/>
       <c r="AO29" s="92"/>
       <c r="AP29" s="92"/>
       <c r="AQ29" s="94"/>
     </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A30" s="200"/>
-      <c r="B30" s="201"/>
-      <c r="C30" s="201"/>
-      <c r="D30" s="201"/>
-      <c r="E30" s="201"/>
-      <c r="F30" s="201"/>
-      <c r="G30" s="201"/>
-      <c r="H30" s="201"/>
-      <c r="I30" s="202"/>
-      <c r="J30" s="203"/>
-      <c r="K30" s="203"/>
-      <c r="L30" s="203"/>
-      <c r="M30" s="203"/>
-      <c r="N30" s="203"/>
-      <c r="O30" s="203"/>
-      <c r="P30" s="203"/>
-      <c r="Q30" s="203"/>
-      <c r="R30" s="203"/>
-      <c r="S30" s="203"/>
-      <c r="T30" s="203"/>
-      <c r="U30" s="203"/>
-      <c r="V30" s="203"/>
-      <c r="W30" s="203"/>
-      <c r="X30" s="203"/>
-      <c r="Y30" s="203"/>
-      <c r="Z30" s="203"/>
-      <c r="AA30" s="203"/>
-      <c r="AB30" s="203"/>
-      <c r="AC30" s="203"/>
-      <c r="AD30" s="203"/>
-      <c r="AE30" s="203"/>
-      <c r="AF30" s="203"/>
-      <c r="AG30" s="203"/>
-      <c r="AH30" s="203"/>
-      <c r="AI30" s="203"/>
-      <c r="AJ30" s="203"/>
-      <c r="AK30" s="203"/>
-      <c r="AL30" s="203"/>
-      <c r="AM30" s="203"/>
-      <c r="AN30" s="203"/>
-    </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A31" s="200"/>
-      <c r="B31" s="201"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="201"/>
-      <c r="F31" s="201"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="203"/>
-      <c r="K31" s="203"/>
-      <c r="L31" s="204"/>
-      <c r="M31" s="204"/>
-      <c r="N31" s="204"/>
-      <c r="O31" s="204"/>
-      <c r="P31" s="204"/>
-      <c r="Q31" s="204"/>
-      <c r="R31" s="204"/>
-      <c r="S31" s="204"/>
-      <c r="T31" s="204"/>
-      <c r="U31" s="204"/>
-      <c r="V31" s="204"/>
-      <c r="W31" s="204"/>
-      <c r="X31" s="204"/>
-      <c r="Y31" s="204"/>
-      <c r="Z31" s="204"/>
-      <c r="AA31" s="204"/>
-      <c r="AB31" s="204"/>
-      <c r="AC31" s="204"/>
-      <c r="AD31" s="204"/>
-      <c r="AE31" s="203"/>
-      <c r="AF31" s="203"/>
-      <c r="AG31" s="203"/>
-      <c r="AH31" s="203"/>
-      <c r="AI31" s="203"/>
-      <c r="AJ31" s="203"/>
-      <c r="AK31" s="203"/>
-      <c r="AL31" s="203"/>
-      <c r="AM31" s="203"/>
-      <c r="AN31" s="203"/>
-    </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A30" s="202"/>
+      <c r="B30" s="203"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="203"/>
+      <c r="H30" s="203"/>
+      <c r="I30" s="204"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="205"/>
+      <c r="L30" s="205"/>
+      <c r="M30" s="205"/>
+      <c r="N30" s="205"/>
+      <c r="O30" s="205"/>
+      <c r="P30" s="205"/>
+      <c r="Q30" s="205"/>
+      <c r="R30" s="205"/>
+      <c r="S30" s="205"/>
+      <c r="T30" s="205"/>
+      <c r="U30" s="205"/>
+      <c r="V30" s="205"/>
+      <c r="W30" s="205"/>
+      <c r="X30" s="205"/>
+      <c r="Y30" s="205"/>
+      <c r="Z30" s="205"/>
+      <c r="AA30" s="205"/>
+      <c r="AB30" s="205"/>
+      <c r="AC30" s="205"/>
+      <c r="AD30" s="205"/>
+      <c r="AE30" s="205"/>
+      <c r="AF30" s="205"/>
+      <c r="AG30" s="205"/>
+      <c r="AH30" s="205"/>
+      <c r="AI30" s="205"/>
+      <c r="AJ30" s="205"/>
+      <c r="AK30" s="205"/>
+      <c r="AL30" s="205"/>
+      <c r="AM30" s="205"/>
+      <c r="AN30" s="205"/>
+    </row>
+    <row r="31" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A31" s="202"/>
+      <c r="B31" s="203"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="203"/>
+      <c r="H31" s="203"/>
+      <c r="I31" s="204"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="205"/>
+      <c r="L31" s="206"/>
+      <c r="M31" s="206"/>
+      <c r="N31" s="206"/>
+      <c r="O31" s="206"/>
+      <c r="P31" s="206"/>
+      <c r="Q31" s="206"/>
+      <c r="R31" s="206"/>
+      <c r="S31" s="206"/>
+      <c r="T31" s="206"/>
+      <c r="U31" s="206"/>
+      <c r="V31" s="206"/>
+      <c r="W31" s="206"/>
+      <c r="X31" s="206"/>
+      <c r="Y31" s="206"/>
+      <c r="Z31" s="206"/>
+      <c r="AA31" s="206"/>
+      <c r="AB31" s="206"/>
+      <c r="AC31" s="206"/>
+      <c r="AD31" s="206"/>
+      <c r="AE31" s="205"/>
+      <c r="AF31" s="205"/>
+      <c r="AG31" s="205"/>
+      <c r="AH31" s="205"/>
+      <c r="AI31" s="205"/>
+      <c r="AJ31" s="205"/>
+      <c r="AK31" s="205"/>
+      <c r="AL31" s="205"/>
+      <c r="AM31" s="205"/>
+      <c r="AN31" s="205"/>
+    </row>
+    <row r="32" spans="1:44" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B32" s="97"/>
       <c r="C32" s="97"/>
@@ -18957,7 +18960,7 @@
       <c r="AM32" s="95"/>
       <c r="AN32" s="95"/>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>69</v>
       </c>
@@ -18991,58 +18994,47 @@
       <c r="AA33" s="140"/>
       <c r="AB33" s="140"/>
       <c r="AC33" s="140"/>
-      <c r="AD33" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ33" s="63"/>
-      <c r="AK33" s="63"/>
-      <c r="AL33" s="63"/>
-    </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AD33" s="140"/>
+      <c r="AE33" s="140"/>
+      <c r="AF33" s="140"/>
+      <c r="AG33" s="140"/>
+      <c r="AH33" s="140"/>
+      <c r="AI33" s="140"/>
+      <c r="AJ33" s="140"/>
+      <c r="AK33" s="140"/>
+      <c r="AL33" s="140"/>
+      <c r="AM33" s="140"/>
+      <c r="AN33" s="140"/>
+    </row>
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" s="140"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="140"/>
-      <c r="H34" s="140"/>
-      <c r="I34" s="140"/>
-      <c r="J34" s="140"/>
-      <c r="K34" s="140"/>
-      <c r="L34" s="140"/>
-      <c r="M34" s="140"/>
-      <c r="N34" s="140"/>
-      <c r="O34" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="P34" s="52"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
-      <c r="S34" s="43"/>
-      <c r="T34" s="52"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
+        <v>271</v>
+      </c>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="120"/>
+      <c r="S34" s="120"/>
+      <c r="T34" s="120"/>
+      <c r="U34" s="120"/>
+      <c r="V34" s="120"/>
+      <c r="W34" s="120"/>
+      <c r="X34" s="120"/>
       <c r="Y34" s="120"/>
       <c r="Z34" s="120"/>
       <c r="AA34" s="120"/>
       <c r="AB34" s="120"/>
-      <c r="AC34" s="120"/>
-      <c r="AD34" s="120"/>
-      <c r="AE34" s="120"/>
-      <c r="AF34" s="120"/>
-      <c r="AG34" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH34" s="120"/>
-      <c r="AI34" s="120"/>
-      <c r="AJ34" s="120"/>
-      <c r="AK34" s="8" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AC34" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD34" s="52"/>
+      <c r="AE34" s="43"/>
+      <c r="AF34" s="43"/>
+      <c r="AG34" s="43"/>
+      <c r="AH34" s="52"/>
+      <c r="AI34" s="17"/>
+      <c r="AJ34" s="17"/>
+      <c r="AK34" s="17"/>
+    </row>
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" s="120"/>
       <c r="B35" s="120"/>
       <c r="C35" s="120"/>
@@ -19059,7 +19051,9 @@
       <c r="N35" s="120"/>
       <c r="O35" s="120"/>
       <c r="P35" s="120"/>
-      <c r="Q35" s="120"/>
+      <c r="Q35" s="276" t="s">
+        <v>267</v>
+      </c>
       <c r="R35" s="120"/>
       <c r="S35" s="120"/>
       <c r="T35" s="120"/>
@@ -19071,115 +19065,168 @@
       <c r="Z35" s="120"/>
       <c r="AA35" s="120"/>
       <c r="AB35" s="120"/>
-      <c r="AC35" s="120"/>
-      <c r="AD35" s="120"/>
-      <c r="AE35" s="120"/>
-      <c r="AF35" s="120"/>
-      <c r="AG35" s="120"/>
-      <c r="AH35" s="120"/>
-      <c r="AI35" s="120"/>
-      <c r="AJ35" s="120"/>
-      <c r="AL35" s="120"/>
-      <c r="AM35" s="120"/>
-      <c r="AN35" s="120"/>
-    </row>
-    <row r="36" spans="1:40" ht="5.4" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="G43" s="98" t="s">
+      <c r="AC35" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="AD35" s="140"/>
+      <c r="AE35" s="140"/>
+      <c r="AF35" s="140"/>
+      <c r="AG35" s="140"/>
+      <c r="AH35" s="140"/>
+      <c r="AI35" s="276" t="s">
+        <v>227</v>
+      </c>
+      <c r="AJ35" s="275"/>
+      <c r="AK35" s="275"/>
+      <c r="AL35" s="275"/>
+      <c r="AN35" s="275"/>
+      <c r="AO35" s="275"/>
+      <c r="AP35" s="275"/>
+    </row>
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="A36" s="120"/>
+      <c r="B36" s="120"/>
+      <c r="C36" s="120"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="120"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="120"/>
+      <c r="N36" s="120"/>
+      <c r="O36" s="120"/>
+      <c r="P36" s="120"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="120"/>
+      <c r="S36" s="120"/>
+      <c r="T36" s="120"/>
+      <c r="U36" s="120"/>
+      <c r="V36" s="120"/>
+      <c r="W36" s="120"/>
+      <c r="X36" s="120"/>
+      <c r="Y36" s="120"/>
+      <c r="Z36" s="120"/>
+      <c r="AA36" s="120"/>
+      <c r="AB36" s="120"/>
+      <c r="AC36" s="120"/>
+      <c r="AD36" s="120"/>
+      <c r="AE36" s="120"/>
+      <c r="AF36" s="120"/>
+      <c r="AG36" s="120"/>
+      <c r="AH36" s="120"/>
+      <c r="AI36" s="120"/>
+      <c r="AJ36" s="120"/>
+      <c r="AK36" s="120"/>
+      <c r="AL36" s="120"/>
+      <c r="AM36" s="120"/>
+      <c r="AN36" s="120"/>
+    </row>
+    <row r="37" spans="1:42" ht="5.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="G44" s="98" t="s">
+        <v>228</v>
+      </c>
+      <c r="H44" s="98"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="98"/>
+      <c r="N44" s="98"/>
+      <c r="O44" s="98"/>
+      <c r="P44" s="98"/>
+      <c r="Q44" s="98"/>
+      <c r="R44" s="98"/>
+      <c r="S44" s="98"/>
+      <c r="T44" s="98"/>
+      <c r="AB44" s="98" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="45" spans="1:42" ht="5.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="98"/>
+      <c r="G45" s="94"/>
+      <c r="R45" s="98"/>
+      <c r="AB45" s="98"/>
+      <c r="AC45" s="98"/>
+      <c r="AD45" s="98"/>
+      <c r="AE45" s="98"/>
+      <c r="AF45" s="98"/>
+      <c r="AG45" s="98"/>
+      <c r="AH45" s="98"/>
+      <c r="AI45" s="98"/>
+      <c r="AJ45" s="98"/>
+      <c r="AK45" s="98"/>
+      <c r="AL45" s="98"/>
+      <c r="AM45" s="98"/>
+    </row>
+    <row r="48" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="98" t="s">
+        <v>228</v>
+      </c>
+      <c r="B52" s="98"/>
+      <c r="C52" s="98"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="98"/>
+      <c r="F52" s="98"/>
+      <c r="G52" s="98"/>
+      <c r="H52" s="98"/>
+      <c r="I52" s="98"/>
+      <c r="J52" s="98"/>
+      <c r="K52" s="98"/>
+      <c r="L52" s="98"/>
+      <c r="N52" s="94"/>
+      <c r="Q52" s="98" t="s">
+        <v>230</v>
+      </c>
+      <c r="V52" s="98"/>
+      <c r="W52" s="98"/>
+      <c r="X52" s="98"/>
+      <c r="Y52" s="98"/>
+      <c r="Z52" s="98"/>
+      <c r="AB52" s="94"/>
+      <c r="AD52" s="98"/>
+      <c r="AE52" s="98" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF52" s="98"/>
+      <c r="AG52" s="98"/>
+      <c r="AH52" s="98"/>
+    </row>
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="99"/>
+      <c r="C53" s="98" t="s">
         <v>231</v>
       </c>
-      <c r="H43" s="98"/>
-      <c r="I43" s="98"/>
-      <c r="J43" s="98"/>
-      <c r="K43" s="98"/>
-      <c r="L43" s="98"/>
-      <c r="M43" s="98"/>
-      <c r="N43" s="98"/>
-      <c r="O43" s="98"/>
-      <c r="P43" s="98"/>
-      <c r="Q43" s="98"/>
-      <c r="R43" s="98"/>
-      <c r="S43" s="98"/>
-      <c r="T43" s="98"/>
-      <c r="AB43" s="98" t="s">
+      <c r="S53" s="98" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="44" spans="1:40" ht="5.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="98"/>
-      <c r="G44" s="94"/>
-      <c r="R44" s="98"/>
-      <c r="AB44" s="98"/>
-      <c r="AC44" s="98"/>
-      <c r="AD44" s="98"/>
-      <c r="AE44" s="98"/>
-      <c r="AF44" s="98"/>
-      <c r="AG44" s="98"/>
-      <c r="AH44" s="98"/>
-      <c r="AI44" s="98"/>
-      <c r="AJ44" s="98"/>
-      <c r="AK44" s="98"/>
-      <c r="AL44" s="98"/>
-      <c r="AM44" s="98"/>
-    </row>
-    <row r="47" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="98" t="s">
-        <v>231</v>
-      </c>
-      <c r="B51" s="98"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="98"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="98"/>
-      <c r="G51" s="98"/>
-      <c r="H51" s="98"/>
-      <c r="I51" s="98"/>
-      <c r="J51" s="98"/>
-      <c r="K51" s="98"/>
-      <c r="L51" s="98"/>
-      <c r="N51" s="94"/>
-      <c r="Q51" s="98" t="s">
-        <v>233</v>
-      </c>
-      <c r="V51" s="98"/>
-      <c r="W51" s="98"/>
-      <c r="X51" s="98"/>
-      <c r="Y51" s="98"/>
-      <c r="Z51" s="98"/>
-      <c r="AB51" s="94"/>
-      <c r="AD51" s="98"/>
-      <c r="AE51" s="98" t="s">
-        <v>232</v>
-      </c>
-      <c r="AF51" s="98"/>
-      <c r="AG51" s="98"/>
-      <c r="AH51" s="98"/>
-    </row>
-    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="99"/>
-      <c r="C52" s="98" t="s">
-        <v>234</v>
-      </c>
-      <c r="S52" s="98" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="S33:AN33"/>
+    <mergeCell ref="A35:P35"/>
+    <mergeCell ref="R35:AB35"/>
+    <mergeCell ref="AD35:AH35"/>
+    <mergeCell ref="A36:AN36"/>
     <mergeCell ref="P1:AN1"/>
     <mergeCell ref="A3:T3"/>
     <mergeCell ref="C5:D5"/>
@@ -19237,7 +19284,6 @@
     <mergeCell ref="J29:T29"/>
     <mergeCell ref="U29:AD29"/>
     <mergeCell ref="AE29:AN29"/>
-    <mergeCell ref="AL35:AN35"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="J30:T30"/>
     <mergeCell ref="U30:AD30"/>
@@ -19247,11 +19293,7 @@
     <mergeCell ref="U31:AD31"/>
     <mergeCell ref="AE31:AN31"/>
     <mergeCell ref="L33:O33"/>
-    <mergeCell ref="S33:AC33"/>
-    <mergeCell ref="E34:N34"/>
-    <mergeCell ref="Y34:AF34"/>
-    <mergeCell ref="A35:AJ35"/>
-    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="Q34:AB34"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -19275,44 +19317,44 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="4.44140625" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" customWidth="1"/>
-    <col min="6" max="7" width="4.6640625" customWidth="1"/>
-    <col min="8" max="11" width="2.33203125" customWidth="1"/>
-    <col min="12" max="17" width="4.6640625" customWidth="1"/>
-    <col min="18" max="18" width="5.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.35546875" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" customWidth="1"/>
+    <col min="5" max="5" width="5.35546875" customWidth="1"/>
+    <col min="6" max="7" width="4.640625" customWidth="1"/>
+    <col min="8" max="11" width="2.35546875" customWidth="1"/>
+    <col min="12" max="17" width="4.640625" customWidth="1"/>
+    <col min="18" max="18" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
@@ -19332,10 +19374,10 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="218"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="220"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="220"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -19351,17 +19393,17 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H4" s="1"/>
       <c r="K4" s="1"/>
@@ -19372,9 +19414,9 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="29" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -19383,7 +19425,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G5" s="31"/>
       <c r="H5" s="1"/>
@@ -19392,7 +19434,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="2"/>
       <c r="M5" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="1"/>
@@ -19400,7 +19442,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -19419,207 +19461,207 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="219" t="s">
+    <row r="7" spans="1:18" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="221" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="220"/>
-      <c r="C7" s="221"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="222"/>
-      <c r="I7" s="224"/>
-      <c r="J7" s="224"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="222"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="222"/>
-      <c r="O7" s="223"/>
-      <c r="P7" s="222"/>
-      <c r="Q7" s="223"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="225"/>
+      <c r="H7" s="224"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="224"/>
+      <c r="M7" s="225"/>
+      <c r="N7" s="224"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="224"/>
+      <c r="Q7" s="225"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="225" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="226"/>
-      <c r="C8" s="227"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="230"/>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="227" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="228"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="E8" s="231"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="231"/>
+      <c r="H8" s="232"/>
       <c r="I8" s="144"/>
       <c r="J8" s="144"/>
-      <c r="K8" s="231"/>
-      <c r="L8" s="228"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="228"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="228"/>
-      <c r="Q8" s="229"/>
+      <c r="K8" s="233"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="231"/>
+      <c r="N8" s="230"/>
+      <c r="O8" s="231"/>
+      <c r="P8" s="230"/>
+      <c r="Q8" s="231"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="232" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="220"/>
-      <c r="C9" s="221"/>
-      <c r="D9" s="228"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="230"/>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" s="234" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="222"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="231"/>
+      <c r="H9" s="232"/>
       <c r="I9" s="144"/>
       <c r="J9" s="144"/>
-      <c r="K9" s="231"/>
-      <c r="L9" s="228"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="228"/>
-      <c r="O9" s="229"/>
-      <c r="P9" s="228"/>
-      <c r="Q9" s="229"/>
+      <c r="K9" s="233"/>
+      <c r="L9" s="230"/>
+      <c r="M9" s="231"/>
+      <c r="N9" s="230"/>
+      <c r="O9" s="231"/>
+      <c r="P9" s="230"/>
+      <c r="Q9" s="231"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="233" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="226"/>
-      <c r="C10" s="227"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="230"/>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10" s="235" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="228"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="230"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="230"/>
+      <c r="G10" s="231"/>
+      <c r="H10" s="232"/>
       <c r="I10" s="144"/>
       <c r="J10" s="144"/>
-      <c r="K10" s="231"/>
-      <c r="L10" s="228"/>
-      <c r="M10" s="229"/>
-      <c r="N10" s="228"/>
-      <c r="O10" s="229"/>
-      <c r="P10" s="228"/>
-      <c r="Q10" s="229"/>
+      <c r="K10" s="233"/>
+      <c r="L10" s="230"/>
+      <c r="M10" s="231"/>
+      <c r="N10" s="230"/>
+      <c r="O10" s="231"/>
+      <c r="P10" s="230"/>
+      <c r="Q10" s="231"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="233" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="226"/>
-      <c r="C11" s="227"/>
-      <c r="D11" s="228"/>
-      <c r="E11" s="229"/>
-      <c r="F11" s="228"/>
-      <c r="G11" s="229"/>
-      <c r="H11" s="230"/>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" s="235" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="228"/>
+      <c r="C11" s="229"/>
+      <c r="D11" s="230"/>
+      <c r="E11" s="231"/>
+      <c r="F11" s="230"/>
+      <c r="G11" s="231"/>
+      <c r="H11" s="232"/>
       <c r="I11" s="144"/>
       <c r="J11" s="144"/>
-      <c r="K11" s="231"/>
-      <c r="L11" s="228"/>
-      <c r="M11" s="229"/>
-      <c r="N11" s="228"/>
-      <c r="O11" s="229"/>
-      <c r="P11" s="228"/>
-      <c r="Q11" s="229"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="230"/>
+      <c r="M11" s="231"/>
+      <c r="N11" s="230"/>
+      <c r="O11" s="231"/>
+      <c r="P11" s="230"/>
+      <c r="Q11" s="231"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="233" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="226"/>
-      <c r="C12" s="227"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="229"/>
-      <c r="H12" s="230"/>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" s="235" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="228"/>
+      <c r="C12" s="229"/>
+      <c r="D12" s="230"/>
+      <c r="E12" s="231"/>
+      <c r="F12" s="230"/>
+      <c r="G12" s="231"/>
+      <c r="H12" s="232"/>
       <c r="I12" s="144"/>
       <c r="J12" s="144"/>
-      <c r="K12" s="231"/>
-      <c r="L12" s="228"/>
-      <c r="M12" s="229"/>
-      <c r="N12" s="228"/>
-      <c r="O12" s="229"/>
-      <c r="P12" s="228"/>
-      <c r="Q12" s="229"/>
+      <c r="K12" s="233"/>
+      <c r="L12" s="230"/>
+      <c r="M12" s="231"/>
+      <c r="N12" s="230"/>
+      <c r="O12" s="231"/>
+      <c r="P12" s="230"/>
+      <c r="Q12" s="231"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="233" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="226"/>
-      <c r="C13" s="227"/>
-      <c r="D13" s="228"/>
-      <c r="E13" s="229"/>
-      <c r="F13" s="228"/>
-      <c r="G13" s="229"/>
-      <c r="H13" s="230"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13" s="235" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="228"/>
+      <c r="C13" s="229"/>
+      <c r="D13" s="230"/>
+      <c r="E13" s="231"/>
+      <c r="F13" s="230"/>
+      <c r="G13" s="231"/>
+      <c r="H13" s="232"/>
       <c r="I13" s="144"/>
       <c r="J13" s="144"/>
-      <c r="K13" s="231"/>
-      <c r="L13" s="228"/>
-      <c r="M13" s="229"/>
-      <c r="N13" s="228"/>
-      <c r="O13" s="229"/>
-      <c r="P13" s="228"/>
-      <c r="Q13" s="229"/>
+      <c r="K13" s="233"/>
+      <c r="L13" s="230"/>
+      <c r="M13" s="231"/>
+      <c r="N13" s="230"/>
+      <c r="O13" s="231"/>
+      <c r="P13" s="230"/>
+      <c r="Q13" s="231"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="232" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="220"/>
-      <c r="C14" s="221"/>
-      <c r="D14" s="228"/>
-      <c r="E14" s="229"/>
-      <c r="F14" s="228"/>
-      <c r="G14" s="229"/>
-      <c r="H14" s="230"/>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A14" s="234" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="222"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="230"/>
+      <c r="E14" s="231"/>
+      <c r="F14" s="230"/>
+      <c r="G14" s="231"/>
+      <c r="H14" s="232"/>
       <c r="I14" s="144"/>
       <c r="J14" s="144"/>
-      <c r="K14" s="231"/>
-      <c r="L14" s="228"/>
-      <c r="M14" s="229"/>
-      <c r="N14" s="228"/>
-      <c r="O14" s="229"/>
-      <c r="P14" s="228"/>
-      <c r="Q14" s="229"/>
+      <c r="K14" s="233"/>
+      <c r="L14" s="230"/>
+      <c r="M14" s="231"/>
+      <c r="N14" s="230"/>
+      <c r="O14" s="231"/>
+      <c r="P14" s="230"/>
+      <c r="Q14" s="231"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="232" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="220"/>
-      <c r="C15" s="221"/>
-      <c r="D15" s="228"/>
-      <c r="E15" s="229"/>
-      <c r="F15" s="228"/>
-      <c r="G15" s="229"/>
-      <c r="H15" s="230"/>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15" s="234" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="222"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="230"/>
+      <c r="E15" s="231"/>
+      <c r="F15" s="230"/>
+      <c r="G15" s="231"/>
+      <c r="H15" s="232"/>
       <c r="I15" s="144"/>
       <c r="J15" s="144"/>
-      <c r="K15" s="231"/>
-      <c r="L15" s="228"/>
-      <c r="M15" s="229"/>
-      <c r="N15" s="228"/>
-      <c r="O15" s="229"/>
-      <c r="P15" s="228"/>
-      <c r="Q15" s="229"/>
+      <c r="K15" s="233"/>
+      <c r="L15" s="230"/>
+      <c r="M15" s="231"/>
+      <c r="N15" s="230"/>
+      <c r="O15" s="231"/>
+      <c r="P15" s="230"/>
+      <c r="Q15" s="231"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -19639,7 +19681,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="6.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -19659,7 +19701,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" ht="6.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="6.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -19679,9 +19721,9 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -19701,11 +19743,11 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="218"/>
-      <c r="B20" s="218"/>
-      <c r="C20" s="218"/>
-      <c r="D20" s="218"/>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A20" s="220"/>
+      <c r="B20" s="220"/>
+      <c r="C20" s="220"/>
+      <c r="D20" s="220"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -19721,40 +19763,40 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="219" t="s">
+    <row r="21" spans="1:18" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="221" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="220"/>
-      <c r="C21" s="221"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="234"/>
-      <c r="F21" s="234"/>
-      <c r="G21" s="234"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="224"/>
-      <c r="J21" s="224"/>
-      <c r="K21" s="223"/>
-      <c r="L21" s="234"/>
-      <c r="M21" s="234"/>
-      <c r="N21" s="234"/>
-      <c r="O21" s="234"/>
-      <c r="P21" s="234"/>
-      <c r="Q21" s="234"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="219" t="s">
-        <v>134</v>
-      </c>
-      <c r="B22" s="220"/>
-      <c r="C22" s="220"/>
+      <c r="B21" s="222"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="236"/>
+      <c r="E21" s="236"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="236"/>
+      <c r="H21" s="224"/>
+      <c r="I21" s="226"/>
+      <c r="J21" s="226"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="236"/>
+      <c r="M21" s="236"/>
+      <c r="N21" s="236"/>
+      <c r="O21" s="236"/>
+      <c r="P21" s="236"/>
+      <c r="Q21" s="236"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A22" s="221" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="222"/>
+      <c r="C22" s="222"/>
       <c r="D22" s="174"/>
       <c r="E22" s="174"/>
       <c r="F22" s="174"/>
       <c r="G22" s="174"/>
-      <c r="H22" s="235"/>
-      <c r="I22" s="236"/>
-      <c r="J22" s="236"/>
+      <c r="H22" s="237"/>
+      <c r="I22" s="238"/>
+      <c r="J22" s="238"/>
       <c r="K22" s="173"/>
       <c r="L22" s="174"/>
       <c r="M22" s="174"/>
@@ -19763,19 +19805,19 @@
       <c r="P22" s="174"/>
       <c r="Q22" s="174"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="219" t="s">
-        <v>135</v>
-      </c>
-      <c r="B23" s="220"/>
-      <c r="C23" s="221"/>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A23" s="221" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="222"/>
+      <c r="C23" s="223"/>
       <c r="D23" s="174"/>
       <c r="E23" s="174"/>
       <c r="F23" s="174"/>
       <c r="G23" s="174"/>
-      <c r="H23" s="235"/>
-      <c r="I23" s="236"/>
-      <c r="J23" s="236"/>
+      <c r="H23" s="237"/>
+      <c r="I23" s="238"/>
+      <c r="J23" s="238"/>
       <c r="K23" s="173"/>
       <c r="L23" s="174"/>
       <c r="M23" s="174"/>
@@ -19784,9 +19826,9 @@
       <c r="P23" s="174"/>
       <c r="Q23" s="174"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -19805,7 +19847,7 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:18" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="7.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -19825,46 +19867,46 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" ht="4.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="4.2" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="218"/>
-      <c r="B28" s="218"/>
-      <c r="C28" s="218"/>
-      <c r="D28" s="218"/>
-    </row>
-    <row r="29" spans="1:18" ht="5.4" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A28" s="220"/>
+      <c r="B28" s="220"/>
+      <c r="C28" s="220"/>
+      <c r="D28" s="220"/>
+    </row>
+    <row r="29" spans="1:18" ht="5.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:18" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="32" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="119"/>
-      <c r="D30" s="234"/>
-      <c r="E30" s="234"/>
-      <c r="F30" s="234"/>
-      <c r="G30" s="234"/>
-      <c r="H30" s="222"/>
-      <c r="I30" s="224"/>
-      <c r="J30" s="224"/>
-      <c r="K30" s="223"/>
-      <c r="L30" s="234"/>
-      <c r="M30" s="234"/>
-      <c r="N30" s="234"/>
-      <c r="O30" s="234"/>
-      <c r="P30" s="234"/>
-      <c r="Q30" s="234"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D30" s="236"/>
+      <c r="E30" s="236"/>
+      <c r="F30" s="236"/>
+      <c r="G30" s="236"/>
+      <c r="H30" s="224"/>
+      <c r="I30" s="226"/>
+      <c r="J30" s="226"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="236"/>
+      <c r="M30" s="236"/>
+      <c r="N30" s="236"/>
+      <c r="O30" s="236"/>
+      <c r="P30" s="236"/>
+      <c r="Q30" s="236"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="32" t="s">
         <v>14</v>
       </c>
@@ -19874,9 +19916,9 @@
       <c r="E31" s="174"/>
       <c r="F31" s="174"/>
       <c r="G31" s="174"/>
-      <c r="H31" s="235"/>
-      <c r="I31" s="236"/>
-      <c r="J31" s="236"/>
+      <c r="H31" s="237"/>
+      <c r="I31" s="238"/>
+      <c r="J31" s="238"/>
       <c r="K31" s="173"/>
       <c r="L31" s="174"/>
       <c r="M31" s="174"/>
@@ -19885,9 +19927,9 @@
       <c r="P31" s="174"/>
       <c r="Q31" s="174"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" s="35" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B32" s="36"/>
       <c r="C32" s="34"/>
@@ -19895,9 +19937,9 @@
       <c r="E32" s="174"/>
       <c r="F32" s="174"/>
       <c r="G32" s="174"/>
-      <c r="H32" s="235"/>
-      <c r="I32" s="236"/>
-      <c r="J32" s="236"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="238"/>
+      <c r="J32" s="238"/>
       <c r="K32" s="173"/>
       <c r="L32" s="174"/>
       <c r="M32" s="174"/>
@@ -19906,220 +19948,220 @@
       <c r="P32" s="174"/>
       <c r="Q32" s="174"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="4.8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="4.8499999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:17" ht="15" x14ac:dyDescent="0.35">
       <c r="A35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="38"/>
+      <c r="M35" s="242"/>
+      <c r="N35" s="242"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36" s="239"/>
+      <c r="B36" s="239"/>
+      <c r="C36" s="239"/>
+      <c r="D36" s="239"/>
+      <c r="M36" s="243"/>
+      <c r="N36" s="243"/>
+    </row>
+    <row r="37" spans="1:17" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="234" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="240"/>
+      <c r="C37" s="241"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="225"/>
+      <c r="F37" s="224"/>
+      <c r="G37" s="225"/>
+      <c r="H37" s="224"/>
+      <c r="I37" s="226"/>
+      <c r="J37" s="226"/>
+      <c r="K37" s="225"/>
+      <c r="L37" s="224"/>
+      <c r="M37" s="225"/>
+      <c r="N37" s="224"/>
+      <c r="O37" s="225"/>
+      <c r="P37" s="224"/>
+      <c r="Q37" s="225"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="235" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="244"/>
+      <c r="C38" s="245"/>
+      <c r="D38" s="246"/>
+      <c r="E38" s="247"/>
+      <c r="F38" s="246"/>
+      <c r="G38" s="247"/>
+      <c r="H38" s="246"/>
+      <c r="I38" s="248"/>
+      <c r="J38" s="248"/>
+      <c r="K38" s="247"/>
+      <c r="L38" s="246"/>
+      <c r="M38" s="247"/>
+      <c r="N38" s="246"/>
+      <c r="O38" s="247"/>
+      <c r="P38" s="246"/>
+      <c r="Q38" s="247"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="234" t="s">
+        <v>137</v>
+      </c>
+      <c r="B39" s="222"/>
+      <c r="C39" s="223"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="237"/>
+      <c r="I39" s="238"/>
+      <c r="J39" s="238"/>
+      <c r="K39" s="173"/>
+      <c r="L39" s="237"/>
+      <c r="M39" s="173"/>
+      <c r="N39" s="237"/>
+      <c r="O39" s="173"/>
+      <c r="P39" s="237"/>
+      <c r="Q39" s="173"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="235" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="38"/>
-      <c r="M35" s="240"/>
-      <c r="N35" s="240"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="237"/>
-      <c r="B36" s="237"/>
-      <c r="C36" s="237"/>
-      <c r="D36" s="237"/>
-      <c r="M36" s="241"/>
-      <c r="N36" s="241"/>
-    </row>
-    <row r="37" spans="1:17" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="232" t="s">
+      <c r="B40" s="228"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="237"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="237"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="237"/>
+      <c r="I40" s="238"/>
+      <c r="J40" s="238"/>
+      <c r="K40" s="173"/>
+      <c r="L40" s="237"/>
+      <c r="M40" s="173"/>
+      <c r="N40" s="237"/>
+      <c r="O40" s="173"/>
+      <c r="P40" s="237"/>
+      <c r="Q40" s="173"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41" s="235" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="238"/>
-      <c r="C37" s="239"/>
-      <c r="D37" s="222"/>
-      <c r="E37" s="223"/>
-      <c r="F37" s="222"/>
-      <c r="G37" s="223"/>
-      <c r="H37" s="222"/>
-      <c r="I37" s="224"/>
-      <c r="J37" s="224"/>
-      <c r="K37" s="223"/>
-      <c r="L37" s="222"/>
-      <c r="M37" s="223"/>
-      <c r="N37" s="222"/>
-      <c r="O37" s="223"/>
-      <c r="P37" s="222"/>
-      <c r="Q37" s="223"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="233" t="s">
-        <v>124</v>
-      </c>
-      <c r="B38" s="242"/>
-      <c r="C38" s="243"/>
-      <c r="D38" s="244"/>
-      <c r="E38" s="245"/>
-      <c r="F38" s="244"/>
-      <c r="G38" s="245"/>
-      <c r="H38" s="244"/>
-      <c r="I38" s="246"/>
-      <c r="J38" s="246"/>
-      <c r="K38" s="245"/>
-      <c r="L38" s="244"/>
-      <c r="M38" s="245"/>
-      <c r="N38" s="244"/>
-      <c r="O38" s="245"/>
-      <c r="P38" s="244"/>
-      <c r="Q38" s="245"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="232" t="s">
+      <c r="B41" s="228"/>
+      <c r="C41" s="229"/>
+      <c r="D41" s="237"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="237"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="237"/>
+      <c r="I41" s="238"/>
+      <c r="J41" s="238"/>
+      <c r="K41" s="173"/>
+      <c r="L41" s="237"/>
+      <c r="M41" s="173"/>
+      <c r="N41" s="237"/>
+      <c r="O41" s="173"/>
+      <c r="P41" s="237"/>
+      <c r="Q41" s="173"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42" s="235" t="s">
         <v>140</v>
       </c>
-      <c r="B39" s="220"/>
-      <c r="C39" s="221"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="173"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="235"/>
-      <c r="I39" s="236"/>
-      <c r="J39" s="236"/>
-      <c r="K39" s="173"/>
-      <c r="L39" s="235"/>
-      <c r="M39" s="173"/>
-      <c r="N39" s="235"/>
-      <c r="O39" s="173"/>
-      <c r="P39" s="235"/>
-      <c r="Q39" s="173"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="233" t="s">
+      <c r="B42" s="228"/>
+      <c r="C42" s="229"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="173"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="237"/>
+      <c r="I42" s="238"/>
+      <c r="J42" s="238"/>
+      <c r="K42" s="173"/>
+      <c r="L42" s="237"/>
+      <c r="M42" s="173"/>
+      <c r="N42" s="237"/>
+      <c r="O42" s="173"/>
+      <c r="P42" s="237"/>
+      <c r="Q42" s="173"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43" s="235" t="s">
         <v>141</v>
       </c>
-      <c r="B40" s="226"/>
-      <c r="C40" s="227"/>
-      <c r="D40" s="235"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="235"/>
-      <c r="G40" s="173"/>
-      <c r="H40" s="235"/>
-      <c r="I40" s="236"/>
-      <c r="J40" s="236"/>
-      <c r="K40" s="173"/>
-      <c r="L40" s="235"/>
-      <c r="M40" s="173"/>
-      <c r="N40" s="235"/>
-      <c r="O40" s="173"/>
-      <c r="P40" s="235"/>
-      <c r="Q40" s="173"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="233" t="s">
+      <c r="B43" s="228"/>
+      <c r="C43" s="229"/>
+      <c r="D43" s="237"/>
+      <c r="E43" s="173"/>
+      <c r="F43" s="237"/>
+      <c r="G43" s="173"/>
+      <c r="H43" s="237"/>
+      <c r="I43" s="238"/>
+      <c r="J43" s="238"/>
+      <c r="K43" s="173"/>
+      <c r="L43" s="237"/>
+      <c r="M43" s="173"/>
+      <c r="N43" s="237"/>
+      <c r="O43" s="173"/>
+      <c r="P43" s="237"/>
+      <c r="Q43" s="173"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44" s="234" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="226"/>
-      <c r="C41" s="227"/>
-      <c r="D41" s="235"/>
-      <c r="E41" s="173"/>
-      <c r="F41" s="235"/>
-      <c r="G41" s="173"/>
-      <c r="H41" s="235"/>
-      <c r="I41" s="236"/>
-      <c r="J41" s="236"/>
-      <c r="K41" s="173"/>
-      <c r="L41" s="235"/>
-      <c r="M41" s="173"/>
-      <c r="N41" s="235"/>
-      <c r="O41" s="173"/>
-      <c r="P41" s="235"/>
-      <c r="Q41" s="173"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="233" t="s">
+      <c r="B44" s="222"/>
+      <c r="C44" s="223"/>
+      <c r="D44" s="237"/>
+      <c r="E44" s="173"/>
+      <c r="F44" s="237"/>
+      <c r="G44" s="173"/>
+      <c r="H44" s="237"/>
+      <c r="I44" s="238"/>
+      <c r="J44" s="238"/>
+      <c r="K44" s="173"/>
+      <c r="L44" s="237"/>
+      <c r="M44" s="173"/>
+      <c r="N44" s="237"/>
+      <c r="O44" s="173"/>
+      <c r="P44" s="237"/>
+      <c r="Q44" s="173"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A45" s="249" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="240"/>
+      <c r="C45" s="241"/>
+      <c r="D45" s="237"/>
+      <c r="E45" s="173"/>
+      <c r="F45" s="237"/>
+      <c r="G45" s="173"/>
+      <c r="H45" s="237"/>
+      <c r="I45" s="238"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="173"/>
+      <c r="L45" s="237"/>
+      <c r="M45" s="173"/>
+      <c r="N45" s="237"/>
+      <c r="O45" s="173"/>
+      <c r="P45" s="237"/>
+      <c r="Q45" s="173"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A46" s="39" t="s">
         <v>143</v>
-      </c>
-      <c r="B42" s="226"/>
-      <c r="C42" s="227"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="173"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="173"/>
-      <c r="H42" s="235"/>
-      <c r="I42" s="236"/>
-      <c r="J42" s="236"/>
-      <c r="K42" s="173"/>
-      <c r="L42" s="235"/>
-      <c r="M42" s="173"/>
-      <c r="N42" s="235"/>
-      <c r="O42" s="173"/>
-      <c r="P42" s="235"/>
-      <c r="Q42" s="173"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="233" t="s">
-        <v>144</v>
-      </c>
-      <c r="B43" s="226"/>
-      <c r="C43" s="227"/>
-      <c r="D43" s="235"/>
-      <c r="E43" s="173"/>
-      <c r="F43" s="235"/>
-      <c r="G43" s="173"/>
-      <c r="H43" s="235"/>
-      <c r="I43" s="236"/>
-      <c r="J43" s="236"/>
-      <c r="K43" s="173"/>
-      <c r="L43" s="235"/>
-      <c r="M43" s="173"/>
-      <c r="N43" s="235"/>
-      <c r="O43" s="173"/>
-      <c r="P43" s="235"/>
-      <c r="Q43" s="173"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="232" t="s">
-        <v>145</v>
-      </c>
-      <c r="B44" s="220"/>
-      <c r="C44" s="221"/>
-      <c r="D44" s="235"/>
-      <c r="E44" s="173"/>
-      <c r="F44" s="235"/>
-      <c r="G44" s="173"/>
-      <c r="H44" s="235"/>
-      <c r="I44" s="236"/>
-      <c r="J44" s="236"/>
-      <c r="K44" s="173"/>
-      <c r="L44" s="235"/>
-      <c r="M44" s="173"/>
-      <c r="N44" s="235"/>
-      <c r="O44" s="173"/>
-      <c r="P44" s="235"/>
-      <c r="Q44" s="173"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="247" t="s">
-        <v>131</v>
-      </c>
-      <c r="B45" s="238"/>
-      <c r="C45" s="239"/>
-      <c r="D45" s="235"/>
-      <c r="E45" s="173"/>
-      <c r="F45" s="235"/>
-      <c r="G45" s="173"/>
-      <c r="H45" s="235"/>
-      <c r="I45" s="236"/>
-      <c r="J45" s="236"/>
-      <c r="K45" s="173"/>
-      <c r="L45" s="235"/>
-      <c r="M45" s="173"/>
-      <c r="N45" s="235"/>
-      <c r="O45" s="173"/>
-      <c r="P45" s="235"/>
-      <c r="Q45" s="173"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="39" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -20315,406 +20357,406 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O45"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="15" width="4.88671875" customWidth="1"/>
+    <col min="4" max="15" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="220"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="220"/>
+      <c r="D3" s="220"/>
+      <c r="E3" s="220"/>
+      <c r="F3" s="220"/>
+      <c r="G3" s="220"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:15" ht="40.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="221" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="224"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="224"/>
+      <c r="M5" s="225"/>
+      <c r="N5" s="224"/>
+      <c r="O5" s="225"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="227" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="228"/>
+      <c r="C6" s="229"/>
+      <c r="D6" s="230"/>
+      <c r="E6" s="231"/>
+      <c r="F6" s="230"/>
+      <c r="G6" s="231"/>
+      <c r="H6" s="230"/>
+      <c r="I6" s="231"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="230"/>
+      <c r="M6" s="231"/>
+      <c r="N6" s="230"/>
+      <c r="O6" s="231"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="227" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="228"/>
+      <c r="C7" s="229"/>
+      <c r="D7" s="230"/>
+      <c r="E7" s="231"/>
+      <c r="F7" s="230"/>
+      <c r="G7" s="231"/>
+      <c r="H7" s="230"/>
+      <c r="I7" s="231"/>
+      <c r="J7" s="230"/>
+      <c r="K7" s="231"/>
+      <c r="L7" s="230"/>
+      <c r="M7" s="231"/>
+      <c r="N7" s="230"/>
+      <c r="O7" s="231"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="254" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="255"/>
+      <c r="C8" s="256"/>
+      <c r="D8" s="230"/>
+      <c r="E8" s="231"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="231"/>
+      <c r="H8" s="230"/>
+      <c r="I8" s="231"/>
+      <c r="J8" s="230"/>
+      <c r="K8" s="231"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="231"/>
+      <c r="N8" s="230"/>
+      <c r="O8" s="231"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="254" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="218"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="B9" s="255"/>
+      <c r="C9" s="256"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="231"/>
+      <c r="H9" s="230"/>
+      <c r="I9" s="231"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="231"/>
+      <c r="L9" s="230"/>
+      <c r="M9" s="231"/>
+      <c r="N9" s="230"/>
+      <c r="O9" s="231"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="254" t="s">
         <v>148</v>
       </c>
-      <c r="K4" s="11"/>
-    </row>
-    <row r="5" spans="1:15" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="219" t="s">
+      <c r="B10" s="255"/>
+      <c r="C10" s="256"/>
+      <c r="D10" s="230"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="230"/>
+      <c r="G10" s="231"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="230"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="230"/>
+      <c r="M10" s="231"/>
+      <c r="N10" s="230"/>
+      <c r="O10" s="231"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="254" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="255"/>
+      <c r="C11" s="256"/>
+      <c r="D11" s="230"/>
+      <c r="E11" s="231"/>
+      <c r="F11" s="230"/>
+      <c r="G11" s="231"/>
+      <c r="H11" s="230"/>
+      <c r="I11" s="231"/>
+      <c r="J11" s="230"/>
+      <c r="K11" s="231"/>
+      <c r="L11" s="230"/>
+      <c r="M11" s="231"/>
+      <c r="N11" s="230"/>
+      <c r="O11" s="231"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="254" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="255"/>
+      <c r="C12" s="256"/>
+      <c r="D12" s="230"/>
+      <c r="E12" s="231"/>
+      <c r="F12" s="230"/>
+      <c r="G12" s="231"/>
+      <c r="H12" s="230"/>
+      <c r="I12" s="231"/>
+      <c r="J12" s="230"/>
+      <c r="K12" s="231"/>
+      <c r="L12" s="230"/>
+      <c r="M12" s="231"/>
+      <c r="N12" s="230"/>
+      <c r="O12" s="231"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="254" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="255"/>
+      <c r="C13" s="256"/>
+      <c r="D13" s="230"/>
+      <c r="E13" s="231"/>
+      <c r="F13" s="230"/>
+      <c r="G13" s="231"/>
+      <c r="H13" s="230"/>
+      <c r="I13" s="231"/>
+      <c r="J13" s="230"/>
+      <c r="K13" s="231"/>
+      <c r="L13" s="230"/>
+      <c r="M13" s="231"/>
+      <c r="N13" s="230"/>
+      <c r="O13" s="231"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="221" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="222"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="222"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="222"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="222"/>
-      <c r="O5" s="223"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="225" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="226"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="228"/>
-      <c r="E6" s="229"/>
-      <c r="F6" s="228"/>
-      <c r="G6" s="229"/>
-      <c r="H6" s="228"/>
-      <c r="I6" s="229"/>
-      <c r="J6" s="228"/>
-      <c r="K6" s="229"/>
-      <c r="L6" s="228"/>
-      <c r="M6" s="229"/>
-      <c r="N6" s="228"/>
-      <c r="O6" s="229"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="225" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="226"/>
-      <c r="C7" s="227"/>
-      <c r="D7" s="228"/>
-      <c r="E7" s="229"/>
-      <c r="F7" s="228"/>
-      <c r="G7" s="229"/>
-      <c r="H7" s="228"/>
-      <c r="I7" s="229"/>
-      <c r="J7" s="228"/>
-      <c r="K7" s="229"/>
-      <c r="L7" s="228"/>
-      <c r="M7" s="229"/>
-      <c r="N7" s="228"/>
-      <c r="O7" s="229"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="252" t="s">
+      <c r="B15" s="222"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="224"/>
+      <c r="E15" s="225"/>
+      <c r="F15" s="224"/>
+      <c r="G15" s="225"/>
+      <c r="H15" s="224"/>
+      <c r="I15" s="225"/>
+      <c r="J15" s="224"/>
+      <c r="K15" s="225"/>
+      <c r="L15" s="224"/>
+      <c r="M15" s="225"/>
+      <c r="N15" s="224"/>
+      <c r="O15" s="225"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="227" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="228"/>
+      <c r="C16" s="229"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="231"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="231"/>
+      <c r="H16" s="230"/>
+      <c r="I16" s="231"/>
+      <c r="J16" s="230"/>
+      <c r="K16" s="231"/>
+      <c r="L16" s="230"/>
+      <c r="M16" s="231"/>
+      <c r="N16" s="230"/>
+      <c r="O16" s="231"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="227" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="228"/>
+      <c r="C17" s="229"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="231"/>
+      <c r="F17" s="230"/>
+      <c r="G17" s="231"/>
+      <c r="H17" s="230"/>
+      <c r="I17" s="231"/>
+      <c r="J17" s="230"/>
+      <c r="K17" s="231"/>
+      <c r="L17" s="230"/>
+      <c r="M17" s="231"/>
+      <c r="N17" s="230"/>
+      <c r="O17" s="231"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="254" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="255"/>
+      <c r="C18" s="256"/>
+      <c r="D18" s="230"/>
+      <c r="E18" s="231"/>
+      <c r="F18" s="230"/>
+      <c r="G18" s="231"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="231"/>
+      <c r="J18" s="230"/>
+      <c r="K18" s="231"/>
+      <c r="L18" s="230"/>
+      <c r="M18" s="231"/>
+      <c r="N18" s="230"/>
+      <c r="O18" s="231"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="254" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="255"/>
+      <c r="C19" s="256"/>
+      <c r="D19" s="230"/>
+      <c r="E19" s="231"/>
+      <c r="F19" s="230"/>
+      <c r="G19" s="231"/>
+      <c r="H19" s="230"/>
+      <c r="I19" s="231"/>
+      <c r="J19" s="230"/>
+      <c r="K19" s="231"/>
+      <c r="L19" s="230"/>
+      <c r="M19" s="231"/>
+      <c r="N19" s="230"/>
+      <c r="O19" s="231"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="254" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="255"/>
+      <c r="C20" s="256"/>
+      <c r="D20" s="230"/>
+      <c r="E20" s="231"/>
+      <c r="F20" s="230"/>
+      <c r="G20" s="231"/>
+      <c r="H20" s="230"/>
+      <c r="I20" s="231"/>
+      <c r="J20" s="230"/>
+      <c r="K20" s="231"/>
+      <c r="L20" s="230"/>
+      <c r="M20" s="231"/>
+      <c r="N20" s="230"/>
+      <c r="O20" s="231"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="254" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="253"/>
-      <c r="C8" s="254"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="228"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="228"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="228"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="228"/>
-      <c r="O8" s="229"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="252" t="s">
+      <c r="B21" s="255"/>
+      <c r="C21" s="256"/>
+      <c r="D21" s="230"/>
+      <c r="E21" s="231"/>
+      <c r="F21" s="230"/>
+      <c r="G21" s="231"/>
+      <c r="H21" s="230"/>
+      <c r="I21" s="231"/>
+      <c r="J21" s="230"/>
+      <c r="K21" s="231"/>
+      <c r="L21" s="230"/>
+      <c r="M21" s="231"/>
+      <c r="N21" s="230"/>
+      <c r="O21" s="231"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="254" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="253"/>
-      <c r="C9" s="254"/>
-      <c r="D9" s="228"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="229"/>
-      <c r="J9" s="228"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="228"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="228"/>
-      <c r="O9" s="229"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="252" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="253"/>
-      <c r="C10" s="254"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="228"/>
-      <c r="I10" s="229"/>
-      <c r="J10" s="228"/>
-      <c r="K10" s="229"/>
-      <c r="L10" s="228"/>
-      <c r="M10" s="229"/>
-      <c r="N10" s="228"/>
-      <c r="O10" s="229"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="252" t="s">
+      <c r="B22" s="255"/>
+      <c r="C22" s="256"/>
+      <c r="D22" s="230"/>
+      <c r="E22" s="231"/>
+      <c r="F22" s="230"/>
+      <c r="G22" s="231"/>
+      <c r="H22" s="230"/>
+      <c r="I22" s="231"/>
+      <c r="J22" s="230"/>
+      <c r="K22" s="231"/>
+      <c r="L22" s="230"/>
+      <c r="M22" s="231"/>
+      <c r="N22" s="230"/>
+      <c r="O22" s="231"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="254" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="255"/>
+      <c r="C23" s="256"/>
+      <c r="D23" s="230"/>
+      <c r="E23" s="231"/>
+      <c r="F23" s="230"/>
+      <c r="G23" s="231"/>
+      <c r="H23" s="230"/>
+      <c r="I23" s="231"/>
+      <c r="J23" s="230"/>
+      <c r="K23" s="231"/>
+      <c r="L23" s="230"/>
+      <c r="M23" s="231"/>
+      <c r="N23" s="230"/>
+      <c r="O23" s="231"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="7.2" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="A26" s="24" t="s">
         <v>152</v>
-      </c>
-      <c r="B11" s="253"/>
-      <c r="C11" s="254"/>
-      <c r="D11" s="228"/>
-      <c r="E11" s="229"/>
-      <c r="F11" s="228"/>
-      <c r="G11" s="229"/>
-      <c r="H11" s="228"/>
-      <c r="I11" s="229"/>
-      <c r="J11" s="228"/>
-      <c r="K11" s="229"/>
-      <c r="L11" s="228"/>
-      <c r="M11" s="229"/>
-      <c r="N11" s="228"/>
-      <c r="O11" s="229"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="252" t="s">
-        <v>153</v>
-      </c>
-      <c r="B12" s="253"/>
-      <c r="C12" s="254"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="229"/>
-      <c r="H12" s="228"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="228"/>
-      <c r="K12" s="229"/>
-      <c r="L12" s="228"/>
-      <c r="M12" s="229"/>
-      <c r="N12" s="228"/>
-      <c r="O12" s="229"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="252" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="253"/>
-      <c r="C13" s="254"/>
-      <c r="D13" s="228"/>
-      <c r="E13" s="229"/>
-      <c r="F13" s="228"/>
-      <c r="G13" s="229"/>
-      <c r="H13" s="228"/>
-      <c r="I13" s="229"/>
-      <c r="J13" s="228"/>
-      <c r="K13" s="229"/>
-      <c r="L13" s="228"/>
-      <c r="M13" s="229"/>
-      <c r="N13" s="228"/>
-      <c r="O13" s="229"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="219" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="220"/>
-      <c r="C15" s="221"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="223"/>
-      <c r="F15" s="222"/>
-      <c r="G15" s="223"/>
-      <c r="H15" s="222"/>
-      <c r="I15" s="223"/>
-      <c r="J15" s="222"/>
-      <c r="K15" s="223"/>
-      <c r="L15" s="222"/>
-      <c r="M15" s="223"/>
-      <c r="N15" s="222"/>
-      <c r="O15" s="223"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="225" t="s">
-        <v>124</v>
-      </c>
-      <c r="B16" s="226"/>
-      <c r="C16" s="227"/>
-      <c r="D16" s="228"/>
-      <c r="E16" s="229"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="229"/>
-      <c r="H16" s="228"/>
-      <c r="I16" s="229"/>
-      <c r="J16" s="228"/>
-      <c r="K16" s="229"/>
-      <c r="L16" s="228"/>
-      <c r="M16" s="229"/>
-      <c r="N16" s="228"/>
-      <c r="O16" s="229"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="225" t="s">
-        <v>125</v>
-      </c>
-      <c r="B17" s="226"/>
-      <c r="C17" s="227"/>
-      <c r="D17" s="228"/>
-      <c r="E17" s="229"/>
-      <c r="F17" s="228"/>
-      <c r="G17" s="229"/>
-      <c r="H17" s="228"/>
-      <c r="I17" s="229"/>
-      <c r="J17" s="228"/>
-      <c r="K17" s="229"/>
-      <c r="L17" s="228"/>
-      <c r="M17" s="229"/>
-      <c r="N17" s="228"/>
-      <c r="O17" s="229"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="252" t="s">
-        <v>149</v>
-      </c>
-      <c r="B18" s="253"/>
-      <c r="C18" s="254"/>
-      <c r="D18" s="228"/>
-      <c r="E18" s="229"/>
-      <c r="F18" s="228"/>
-      <c r="G18" s="229"/>
-      <c r="H18" s="228"/>
-      <c r="I18" s="229"/>
-      <c r="J18" s="228"/>
-      <c r="K18" s="229"/>
-      <c r="L18" s="228"/>
-      <c r="M18" s="229"/>
-      <c r="N18" s="228"/>
-      <c r="O18" s="229"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="252" t="s">
-        <v>150</v>
-      </c>
-      <c r="B19" s="253"/>
-      <c r="C19" s="254"/>
-      <c r="D19" s="228"/>
-      <c r="E19" s="229"/>
-      <c r="F19" s="228"/>
-      <c r="G19" s="229"/>
-      <c r="H19" s="228"/>
-      <c r="I19" s="229"/>
-      <c r="J19" s="228"/>
-      <c r="K19" s="229"/>
-      <c r="L19" s="228"/>
-      <c r="M19" s="229"/>
-      <c r="N19" s="228"/>
-      <c r="O19" s="229"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="252" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="253"/>
-      <c r="C20" s="254"/>
-      <c r="D20" s="228"/>
-      <c r="E20" s="229"/>
-      <c r="F20" s="228"/>
-      <c r="G20" s="229"/>
-      <c r="H20" s="228"/>
-      <c r="I20" s="229"/>
-      <c r="J20" s="228"/>
-      <c r="K20" s="229"/>
-      <c r="L20" s="228"/>
-      <c r="M20" s="229"/>
-      <c r="N20" s="228"/>
-      <c r="O20" s="229"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="252" t="s">
-        <v>152</v>
-      </c>
-      <c r="B21" s="253"/>
-      <c r="C21" s="254"/>
-      <c r="D21" s="228"/>
-      <c r="E21" s="229"/>
-      <c r="F21" s="228"/>
-      <c r="G21" s="229"/>
-      <c r="H21" s="228"/>
-      <c r="I21" s="229"/>
-      <c r="J21" s="228"/>
-      <c r="K21" s="229"/>
-      <c r="L21" s="228"/>
-      <c r="M21" s="229"/>
-      <c r="N21" s="228"/>
-      <c r="O21" s="229"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="252" t="s">
-        <v>153</v>
-      </c>
-      <c r="B22" s="253"/>
-      <c r="C22" s="254"/>
-      <c r="D22" s="228"/>
-      <c r="E22" s="229"/>
-      <c r="F22" s="228"/>
-      <c r="G22" s="229"/>
-      <c r="H22" s="228"/>
-      <c r="I22" s="229"/>
-      <c r="J22" s="228"/>
-      <c r="K22" s="229"/>
-      <c r="L22" s="228"/>
-      <c r="M22" s="229"/>
-      <c r="N22" s="228"/>
-      <c r="O22" s="229"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="252" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="253"/>
-      <c r="C23" s="254"/>
-      <c r="D23" s="228"/>
-      <c r="E23" s="229"/>
-      <c r="F23" s="228"/>
-      <c r="G23" s="229"/>
-      <c r="H23" s="228"/>
-      <c r="I23" s="229"/>
-      <c r="J23" s="228"/>
-      <c r="K23" s="229"/>
-      <c r="L23" s="228"/>
-      <c r="M23" s="229"/>
-      <c r="N23" s="228"/>
-      <c r="O23" s="229"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="7.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>155</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
@@ -20722,7 +20764,7 @@
       <c r="G26" s="26"/>
       <c r="K26" s="11"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="140"/>
       <c r="B27" s="140"/>
       <c r="C27" s="140"/>
@@ -20730,191 +20772,191 @@
       <c r="E27" s="140"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:15" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="219" t="s">
+    <row r="28" spans="1:15" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="221" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="220"/>
-      <c r="C28" s="221"/>
-      <c r="D28" s="222"/>
-      <c r="E28" s="223"/>
-      <c r="F28" s="222"/>
-      <c r="G28" s="223"/>
-      <c r="H28" s="222"/>
-      <c r="I28" s="223"/>
-      <c r="J28" s="222"/>
-      <c r="K28" s="223"/>
-      <c r="L28" s="222"/>
-      <c r="M28" s="223"/>
-      <c r="N28" s="222"/>
-      <c r="O28" s="223"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="225" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="226"/>
-      <c r="C29" s="227"/>
-      <c r="D29" s="228"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="228"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="228"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="228"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="228"/>
-      <c r="M29" s="229"/>
-      <c r="N29" s="228"/>
-      <c r="O29" s="229"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="225" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="226"/>
-      <c r="C30" s="227"/>
-      <c r="D30" s="230"/>
-      <c r="E30" s="231"/>
-      <c r="F30" s="230"/>
-      <c r="G30" s="231"/>
-      <c r="H30" s="230"/>
-      <c r="I30" s="231"/>
-      <c r="J30" s="230"/>
-      <c r="K30" s="231"/>
-      <c r="L30" s="230"/>
-      <c r="M30" s="231"/>
-      <c r="N30" s="230"/>
-      <c r="O30" s="231"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="252" t="s">
+      <c r="B28" s="222"/>
+      <c r="C28" s="223"/>
+      <c r="D28" s="224"/>
+      <c r="E28" s="225"/>
+      <c r="F28" s="224"/>
+      <c r="G28" s="225"/>
+      <c r="H28" s="224"/>
+      <c r="I28" s="225"/>
+      <c r="J28" s="224"/>
+      <c r="K28" s="225"/>
+      <c r="L28" s="224"/>
+      <c r="M28" s="225"/>
+      <c r="N28" s="224"/>
+      <c r="O28" s="225"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="227" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="228"/>
+      <c r="C29" s="229"/>
+      <c r="D29" s="230"/>
+      <c r="E29" s="231"/>
+      <c r="F29" s="230"/>
+      <c r="G29" s="231"/>
+      <c r="H29" s="230"/>
+      <c r="I29" s="231"/>
+      <c r="J29" s="230"/>
+      <c r="K29" s="231"/>
+      <c r="L29" s="230"/>
+      <c r="M29" s="231"/>
+      <c r="N29" s="230"/>
+      <c r="O29" s="231"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="227" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="228"/>
+      <c r="C30" s="229"/>
+      <c r="D30" s="232"/>
+      <c r="E30" s="233"/>
+      <c r="F30" s="232"/>
+      <c r="G30" s="233"/>
+      <c r="H30" s="232"/>
+      <c r="I30" s="233"/>
+      <c r="J30" s="232"/>
+      <c r="K30" s="233"/>
+      <c r="L30" s="232"/>
+      <c r="M30" s="233"/>
+      <c r="N30" s="232"/>
+      <c r="O30" s="233"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="254" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="255"/>
+      <c r="C31" s="256"/>
+      <c r="D31" s="230"/>
+      <c r="E31" s="231"/>
+      <c r="F31" s="230"/>
+      <c r="G31" s="231"/>
+      <c r="H31" s="230"/>
+      <c r="I31" s="231"/>
+      <c r="J31" s="230"/>
+      <c r="K31" s="231"/>
+      <c r="L31" s="230"/>
+      <c r="M31" s="231"/>
+      <c r="N31" s="230"/>
+      <c r="O31" s="231"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="254" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="255"/>
+      <c r="C32" s="256"/>
+      <c r="D32" s="232"/>
+      <c r="E32" s="233"/>
+      <c r="F32" s="232"/>
+      <c r="G32" s="233"/>
+      <c r="H32" s="232"/>
+      <c r="I32" s="233"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="233"/>
+      <c r="L32" s="232"/>
+      <c r="M32" s="233"/>
+      <c r="N32" s="232"/>
+      <c r="O32" s="233"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" s="254" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="255"/>
+      <c r="C33" s="256"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="231"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="231"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="231"/>
+      <c r="J33" s="230"/>
+      <c r="K33" s="231"/>
+      <c r="L33" s="230"/>
+      <c r="M33" s="231"/>
+      <c r="N33" s="230"/>
+      <c r="O33" s="231"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="254" t="s">
         <v>149</v>
       </c>
-      <c r="B31" s="253"/>
-      <c r="C31" s="254"/>
-      <c r="D31" s="228"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="228"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="228"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="228"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="228"/>
-      <c r="M31" s="229"/>
-      <c r="N31" s="228"/>
-      <c r="O31" s="229"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="252" t="s">
+      <c r="B34" s="255"/>
+      <c r="C34" s="256"/>
+      <c r="D34" s="232"/>
+      <c r="E34" s="233"/>
+      <c r="F34" s="232"/>
+      <c r="G34" s="233"/>
+      <c r="H34" s="232"/>
+      <c r="I34" s="233"/>
+      <c r="J34" s="232"/>
+      <c r="K34" s="233"/>
+      <c r="L34" s="232"/>
+      <c r="M34" s="233"/>
+      <c r="N34" s="232"/>
+      <c r="O34" s="233"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="254" t="s">
         <v>150</v>
       </c>
-      <c r="B32" s="253"/>
-      <c r="C32" s="254"/>
-      <c r="D32" s="230"/>
-      <c r="E32" s="231"/>
-      <c r="F32" s="230"/>
-      <c r="G32" s="231"/>
-      <c r="H32" s="230"/>
-      <c r="I32" s="231"/>
-      <c r="J32" s="230"/>
-      <c r="K32" s="231"/>
-      <c r="L32" s="230"/>
-      <c r="M32" s="231"/>
-      <c r="N32" s="230"/>
-      <c r="O32" s="231"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="252" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" s="253"/>
-      <c r="C33" s="254"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="228"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="228"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="228"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="228"/>
-      <c r="M33" s="229"/>
-      <c r="N33" s="228"/>
-      <c r="O33" s="229"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="252" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" s="253"/>
-      <c r="C34" s="254"/>
-      <c r="D34" s="230"/>
-      <c r="E34" s="231"/>
-      <c r="F34" s="230"/>
-      <c r="G34" s="231"/>
-      <c r="H34" s="230"/>
-      <c r="I34" s="231"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="231"/>
-      <c r="L34" s="230"/>
-      <c r="M34" s="231"/>
-      <c r="N34" s="230"/>
-      <c r="O34" s="231"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="252" t="s">
-        <v>153</v>
-      </c>
-      <c r="B35" s="253"/>
-      <c r="C35" s="254"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="228"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="228"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="228"/>
-      <c r="K35" s="229"/>
-      <c r="L35" s="228"/>
-      <c r="M35" s="229"/>
-      <c r="N35" s="228"/>
-      <c r="O35" s="229"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="252" t="s">
-        <v>131</v>
-      </c>
-      <c r="B36" s="253"/>
-      <c r="C36" s="254"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="228"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="228"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="228"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="228"/>
-      <c r="M36" s="229"/>
-      <c r="N36" s="228"/>
-      <c r="O36" s="229"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B35" s="255"/>
+      <c r="C35" s="256"/>
+      <c r="D35" s="230"/>
+      <c r="E35" s="231"/>
+      <c r="F35" s="230"/>
+      <c r="G35" s="231"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="231"/>
+      <c r="J35" s="230"/>
+      <c r="K35" s="231"/>
+      <c r="L35" s="230"/>
+      <c r="M35" s="231"/>
+      <c r="N35" s="230"/>
+      <c r="O35" s="231"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="254" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" s="255"/>
+      <c r="C36" s="256"/>
+      <c r="D36" s="230"/>
+      <c r="E36" s="231"/>
+      <c r="F36" s="230"/>
+      <c r="G36" s="231"/>
+      <c r="H36" s="230"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="230"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="230"/>
+      <c r="M36" s="231"/>
+      <c r="N36" s="230"/>
+      <c r="O36" s="231"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="10.85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H38" s="15"/>
     </row>
-    <row r="39" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="122"/>
       <c r="B40" s="122"/>
       <c r="C40" s="122"/>
@@ -20925,59 +20967,59 @@
       <c r="H40" s="122"/>
       <c r="I40" s="122"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E41" s="144"/>
       <c r="F41" s="144"/>
       <c r="G41" s="144"/>
       <c r="H41" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="5.4" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="249" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" s="250"/>
-      <c r="C43" s="251"/>
-      <c r="D43" s="222"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="222"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="222"/>
-      <c r="I43" s="223"/>
-      <c r="J43" s="222"/>
-      <c r="K43" s="223"/>
-      <c r="L43" s="222"/>
-      <c r="M43" s="223"/>
-      <c r="N43" s="222"/>
-      <c r="O43" s="223"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="248" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="248"/>
-      <c r="C44" s="248"/>
-      <c r="D44" s="228"/>
-      <c r="E44" s="229"/>
-      <c r="F44" s="228"/>
-      <c r="G44" s="229"/>
-      <c r="H44" s="228"/>
-      <c r="I44" s="229"/>
-      <c r="J44" s="228"/>
-      <c r="K44" s="229"/>
-      <c r="L44" s="228"/>
-      <c r="M44" s="229"/>
-      <c r="N44" s="228"/>
-      <c r="O44" s="229"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="5.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="251" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="252"/>
+      <c r="C43" s="253"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="225"/>
+      <c r="F43" s="224"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="224"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="224"/>
+      <c r="K43" s="225"/>
+      <c r="L43" s="224"/>
+      <c r="M43" s="225"/>
+      <c r="N43" s="224"/>
+      <c r="O43" s="225"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="250" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="250"/>
+      <c r="C44" s="250"/>
+      <c r="D44" s="230"/>
+      <c r="E44" s="231"/>
+      <c r="F44" s="230"/>
+      <c r="G44" s="231"/>
+      <c r="H44" s="230"/>
+      <c r="I44" s="231"/>
+      <c r="J44" s="230"/>
+      <c r="K44" s="231"/>
+      <c r="L44" s="230"/>
+      <c r="M44" s="231"/>
+      <c r="N44" s="230"/>
+      <c r="O44" s="231"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -21209,238 +21251,238 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="15" width="4.88671875" customWidth="1"/>
+    <col min="4" max="15" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H2" s="15"/>
     </row>
-    <row r="3" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="218"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
+    <row r="3" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="220"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="220"/>
+      <c r="D3" s="220"/>
       <c r="E3" s="15"/>
       <c r="G3" s="16"/>
       <c r="H3" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="16"/>
       <c r="K3" s="22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="257" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="238"/>
+      <c r="C4" s="173"/>
+      <c r="D4" s="224"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="224"/>
+      <c r="G4" s="225"/>
+      <c r="H4" s="224"/>
+      <c r="I4" s="225"/>
+      <c r="J4" s="224"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="224"/>
+      <c r="M4" s="225"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="225"/>
+    </row>
+    <row r="5" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="270" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="248"/>
+      <c r="C5" s="247"/>
+      <c r="D5" s="230"/>
+      <c r="E5" s="231"/>
+      <c r="F5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="231"/>
+      <c r="L5" s="230"/>
+      <c r="M5" s="231"/>
+      <c r="N5" s="230"/>
+      <c r="O5" s="231"/>
+    </row>
+    <row r="6" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="264" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="265"/>
+      <c r="C6" s="266"/>
+      <c r="D6" s="271"/>
+      <c r="E6" s="272"/>
+      <c r="F6" s="271"/>
+      <c r="G6" s="272"/>
+      <c r="H6" s="271"/>
+      <c r="I6" s="272"/>
+      <c r="J6" s="271"/>
+      <c r="K6" s="272"/>
+      <c r="L6" s="271"/>
+      <c r="M6" s="272"/>
+      <c r="N6" s="271"/>
+      <c r="O6" s="272"/>
+    </row>
+    <row r="7" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="267"/>
+      <c r="B7" s="268"/>
+      <c r="C7" s="269"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="274"/>
+      <c r="F7" s="273"/>
+      <c r="G7" s="274"/>
+      <c r="H7" s="273"/>
+      <c r="I7" s="274"/>
+      <c r="J7" s="273"/>
+      <c r="K7" s="274"/>
+      <c r="L7" s="273"/>
+      <c r="M7" s="274"/>
+      <c r="N7" s="273"/>
+      <c r="O7" s="274"/>
+    </row>
+    <row r="8" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="258" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="255" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="236"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="222"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="222"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="222"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="222"/>
-      <c r="O4" s="223"/>
-    </row>
-    <row r="5" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="268" t="s">
+      <c r="B8" s="259"/>
+      <c r="C8" s="260"/>
+      <c r="D8" s="258"/>
+      <c r="E8" s="260"/>
+      <c r="F8" s="258"/>
+      <c r="G8" s="260"/>
+      <c r="H8" s="258"/>
+      <c r="I8" s="260"/>
+      <c r="J8" s="258"/>
+      <c r="K8" s="260"/>
+      <c r="L8" s="258"/>
+      <c r="M8" s="260"/>
+      <c r="N8" s="258"/>
+      <c r="O8" s="260"/>
+    </row>
+    <row r="9" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="261" t="s">
         <v>159</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="245"/>
-      <c r="D5" s="228"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="228"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="228"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="228"/>
-      <c r="M5" s="229"/>
-      <c r="N5" s="228"/>
-      <c r="O5" s="229"/>
-    </row>
-    <row r="6" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="262" t="s">
+      <c r="B9" s="262"/>
+      <c r="C9" s="263"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="231"/>
+      <c r="H9" s="230"/>
+      <c r="I9" s="231"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="231"/>
+      <c r="L9" s="230"/>
+      <c r="M9" s="231"/>
+      <c r="N9" s="230"/>
+      <c r="O9" s="231"/>
+    </row>
+    <row r="10" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="264" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="265"/>
+      <c r="C10" s="266"/>
+      <c r="D10" s="271"/>
+      <c r="E10" s="272"/>
+      <c r="F10" s="271"/>
+      <c r="G10" s="272"/>
+      <c r="H10" s="271"/>
+      <c r="I10" s="272"/>
+      <c r="J10" s="271"/>
+      <c r="K10" s="272"/>
+      <c r="L10" s="271"/>
+      <c r="M10" s="272"/>
+      <c r="N10" s="271"/>
+      <c r="O10" s="272"/>
+    </row>
+    <row r="11" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="267"/>
+      <c r="B11" s="268"/>
+      <c r="C11" s="269"/>
+      <c r="D11" s="273"/>
+      <c r="E11" s="274"/>
+      <c r="F11" s="273"/>
+      <c r="G11" s="274"/>
+      <c r="H11" s="273"/>
+      <c r="I11" s="274"/>
+      <c r="J11" s="273"/>
+      <c r="K11" s="274"/>
+      <c r="L11" s="273"/>
+      <c r="M11" s="274"/>
+      <c r="N11" s="273"/>
+      <c r="O11" s="274"/>
+    </row>
+    <row r="12" spans="1:15" ht="13.85" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="258" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="259"/>
+      <c r="C12" s="260"/>
+      <c r="D12" s="258"/>
+      <c r="E12" s="260"/>
+      <c r="F12" s="258"/>
+      <c r="G12" s="260"/>
+      <c r="H12" s="258"/>
+      <c r="I12" s="260"/>
+      <c r="J12" s="258"/>
+      <c r="K12" s="260"/>
+      <c r="L12" s="258"/>
+      <c r="M12" s="260"/>
+      <c r="N12" s="258"/>
+      <c r="O12" s="260"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B6" s="263"/>
-      <c r="C6" s="264"/>
-      <c r="D6" s="269"/>
-      <c r="E6" s="270"/>
-      <c r="F6" s="269"/>
-      <c r="G6" s="270"/>
-      <c r="H6" s="269"/>
-      <c r="I6" s="270"/>
-      <c r="J6" s="269"/>
-      <c r="K6" s="270"/>
-      <c r="L6" s="269"/>
-      <c r="M6" s="270"/>
-      <c r="N6" s="269"/>
-      <c r="O6" s="270"/>
-    </row>
-    <row r="7" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="265"/>
-      <c r="B7" s="266"/>
-      <c r="C7" s="267"/>
-      <c r="D7" s="271"/>
-      <c r="E7" s="272"/>
-      <c r="F7" s="271"/>
-      <c r="G7" s="272"/>
-      <c r="H7" s="271"/>
-      <c r="I7" s="272"/>
-      <c r="J7" s="271"/>
-      <c r="K7" s="272"/>
-      <c r="L7" s="271"/>
-      <c r="M7" s="272"/>
-      <c r="N7" s="271"/>
-      <c r="O7" s="272"/>
-    </row>
-    <row r="8" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="256" t="s">
+      <c r="J13" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="257"/>
-      <c r="C8" s="258"/>
-      <c r="D8" s="256"/>
-      <c r="E8" s="258"/>
-      <c r="F8" s="256"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="256"/>
-      <c r="I8" s="258"/>
-      <c r="J8" s="256"/>
-      <c r="K8" s="258"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="258"/>
-      <c r="N8" s="256"/>
-      <c r="O8" s="258"/>
-    </row>
-    <row r="9" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="259" t="s">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="260"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="228"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="229"/>
-      <c r="J9" s="228"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="228"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="228"/>
-      <c r="O9" s="229"/>
-    </row>
-    <row r="10" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="262" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="263"/>
-      <c r="C10" s="264"/>
-      <c r="D10" s="269"/>
-      <c r="E10" s="270"/>
-      <c r="F10" s="269"/>
-      <c r="G10" s="270"/>
-      <c r="H10" s="269"/>
-      <c r="I10" s="270"/>
-      <c r="J10" s="269"/>
-      <c r="K10" s="270"/>
-      <c r="L10" s="269"/>
-      <c r="M10" s="270"/>
-      <c r="N10" s="269"/>
-      <c r="O10" s="270"/>
-    </row>
-    <row r="11" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="265"/>
-      <c r="B11" s="266"/>
-      <c r="C11" s="267"/>
-      <c r="D11" s="271"/>
-      <c r="E11" s="272"/>
-      <c r="F11" s="271"/>
-      <c r="G11" s="272"/>
-      <c r="H11" s="271"/>
-      <c r="I11" s="272"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="272"/>
-      <c r="L11" s="271"/>
-      <c r="M11" s="272"/>
-      <c r="N11" s="271"/>
-      <c r="O11" s="272"/>
-    </row>
-    <row r="12" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="256" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" s="257"/>
-      <c r="C12" s="258"/>
-      <c r="D12" s="256"/>
-      <c r="E12" s="258"/>
-      <c r="F12" s="256"/>
-      <c r="G12" s="258"/>
-      <c r="H12" s="256"/>
-      <c r="I12" s="258"/>
-      <c r="J12" s="256"/>
-      <c r="K12" s="258"/>
-      <c r="L12" s="256"/>
-      <c r="M12" s="258"/>
-      <c r="N12" s="256"/>
-      <c r="O12" s="258"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="B14" t="s">
         <v>163</v>
       </c>
-      <c r="J13" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H15" s="140"/>
       <c r="I15" s="140"/>
@@ -21449,140 +21491,140 @@
       <c r="L15" s="140"/>
       <c r="M15" s="140"/>
     </row>
-    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
     </row>
-    <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F20" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J20" s="23"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F21" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="J21" s="23"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F22" s="21" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F20" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="J20" s="23"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F21" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="J21" s="23"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F22" s="21" t="s">
-        <v>171</v>
-      </c>
       <c r="J22" s="23"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B24" s="140"/>
       <c r="C24" s="140"/>
     </row>
-    <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F26" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J26" s="23"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F27" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="J27" s="23"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F28" s="21" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F26" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="J26" s="23"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F27" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="J27" s="23"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F28" s="21" t="s">
-        <v>171</v>
-      </c>
       <c r="J28" s="23"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B30" s="140"/>
       <c r="C30" s="140"/>
     </row>
-    <row r="31" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F32" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J32" s="23"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F33" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="J33" s="23"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F34" s="21" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F32" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="J32" s="23"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F33" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="J33" s="23"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F34" s="21" t="s">
-        <v>171</v>
-      </c>
       <c r="J34" s="23"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B36" s="140"/>
       <c r="C36" s="140"/>
     </row>
-    <row r="37" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F38" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J38" s="23"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F39" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="J39" s="23"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F40" s="21" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F38" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="J38" s="23"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F39" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="J39" s="23"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F40" s="21" t="s">
-        <v>171</v>
       </c>
       <c r="J40" s="23"/>
     </row>

--- a/wwwroot/ExcelModel/Woolworth_WET_sheet.xlsx
+++ b/wwwroot/ExcelModel/Woolworth_WET_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0232EC1-9C47-457F-A8C2-76A8B6A2F562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7416242F-8A40-4689-8BF6-A57E55485387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,18 +34,7 @@
     <definedName name="ReportNumber" localSheetId="2">'DStoWashing-G'!$P$1</definedName>
     <definedName name="ReportNumber" localSheetId="5">Spirality!$P$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -443,9 +432,6 @@
     <t>Dimensional Stability to Washing 尺寸稳定性-水洗</t>
   </si>
   <si>
-    <t>, with 4.0kg total dry ballast,</t>
-  </si>
-  <si>
     <t>(cotton&lt;=±5%, synthetics &lt;=±3%;)</t>
   </si>
   <si>
@@ -1461,10 +1447,6 @@
     <t>ballast,</t>
   </si>
   <si>
-    <t xml:space="preserve"> ,with 4.0kg total dry </t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>using domestic washing machine,</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -1539,9 +1521,17 @@
   </si>
   <si>
     <t xml:space="preserve">severe pillling was found on the Reverse side of </t>
-  </si>
-  <si>
-    <t xml:space="preserve">severe pillling was found on the Reverse side of </t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ,with 2.0kg total dry </t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>, with 2.0kg total dry ballast,</t>
+  </si>
+  <si>
+    <t>washed sample.</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -8662,7 +8652,7 @@
         <v>3</v>
       </c>
       <c r="AR3" s="90" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:79" x14ac:dyDescent="0.25">
@@ -9095,7 +9085,7 @@
       <c r="H14" s="128"/>
       <c r="I14" s="128"/>
       <c r="AR14" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:79" ht="14.4" x14ac:dyDescent="0.25">
@@ -9113,7 +9103,7 @@
         <v>38</v>
       </c>
       <c r="AR15" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:79" x14ac:dyDescent="0.25">
@@ -9187,15 +9177,15 @@
         <v>46</v>
       </c>
       <c r="AR19" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:63" x14ac:dyDescent="0.25">
       <c r="AR20" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="BK20" s="20" t="s">
         <v>179</v>
-      </c>
-      <c r="BK20" s="20" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:63" x14ac:dyDescent="0.25">
@@ -9213,10 +9203,10 @@
         <v>49</v>
       </c>
       <c r="AR21" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BK21" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:63" x14ac:dyDescent="0.25">
@@ -9224,10 +9214,10 @@
         <v>50</v>
       </c>
       <c r="AR22" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="BK22" s="20" t="s">
         <v>182</v>
-      </c>
-      <c r="BK22" s="20" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:63" x14ac:dyDescent="0.25">
@@ -9247,18 +9237,18 @@
         <v>18</v>
       </c>
       <c r="AR23" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BK23" s="20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:63" x14ac:dyDescent="0.25">
       <c r="AR24" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="BK24" s="20" t="s">
         <v>185</v>
-      </c>
-      <c r="BK24" s="20" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:63" x14ac:dyDescent="0.25">
@@ -9271,10 +9261,10 @@
         <v>54</v>
       </c>
       <c r="AR25" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BK25" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:63" x14ac:dyDescent="0.25">
@@ -9294,10 +9284,10 @@
         <v>56</v>
       </c>
       <c r="AR26" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="BK26" s="20" t="s">
         <v>188</v>
-      </c>
-      <c r="BK26" s="20" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:63" x14ac:dyDescent="0.25">
@@ -9314,18 +9304,18 @@
         <v>18</v>
       </c>
       <c r="AR27" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BK27" s="20" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:63" x14ac:dyDescent="0.25">
       <c r="AR28" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="BK28" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:63" x14ac:dyDescent="0.25">
@@ -9347,7 +9337,7 @@
       <c r="W29" s="128"/>
       <c r="X29" s="128"/>
       <c r="AR29" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:63" x14ac:dyDescent="0.25">
@@ -9372,17 +9362,17 @@
         <v>59</v>
       </c>
       <c r="AR30" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:63" x14ac:dyDescent="0.25">
       <c r="AR31" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:63" x14ac:dyDescent="0.25">
       <c r="AR32" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:79" x14ac:dyDescent="0.25">
@@ -9399,7 +9389,7 @@
       <c r="AD33" s="138"/>
       <c r="AE33" s="138"/>
       <c r="AR33" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:79" x14ac:dyDescent="0.25">
@@ -9525,7 +9515,7 @@
       <c r="AO35" s="72"/>
       <c r="AP35" s="77"/>
       <c r="AR35" s="80" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:79" x14ac:dyDescent="0.25">
@@ -9574,7 +9564,7 @@
       <c r="AO36" s="142"/>
       <c r="AP36" s="143"/>
       <c r="AV36" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:79" x14ac:dyDescent="0.25">
@@ -9709,7 +9699,7 @@
       <c r="AO38" s="145"/>
       <c r="AP38" s="146"/>
       <c r="AR38" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="BE38" s="147"/>
       <c r="BF38" s="147"/>
@@ -9726,7 +9716,7 @@
       <c r="BQ38" s="147"/>
       <c r="BR38" s="147"/>
       <c r="BS38" s="52" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:79" x14ac:dyDescent="0.25">
@@ -9773,7 +9763,7 @@
       <c r="AO39" s="12"/>
       <c r="AP39" s="116"/>
       <c r="AR39" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU39" s="127"/>
       <c r="AV39" s="127"/>
@@ -9786,7 +9776,7 @@
       <c r="BC39" s="127"/>
       <c r="BD39" s="127"/>
       <c r="BE39" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BF39" s="148"/>
       <c r="BG39" s="148"/>
@@ -9794,7 +9784,7 @@
       <c r="BI39" s="148"/>
       <c r="BJ39" s="148"/>
       <c r="BK39" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BL39" s="148"/>
       <c r="BM39" s="148"/>
@@ -10713,7 +10703,7 @@
       <c r="H4" s="128"/>
       <c r="I4" s="128"/>
       <c r="AR4" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AS4" s="117"/>
       <c r="AT4" s="117"/>
@@ -10728,12 +10718,12 @@
       <c r="BC4" s="151"/>
       <c r="BD4" s="151"/>
       <c r="BE4" s="117" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BF4" s="117"/>
       <c r="BG4" s="117"/>
       <c r="BH4" s="152" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BI4" s="152"/>
       <c r="BJ4" s="152"/>
@@ -10752,7 +10742,7 @@
       <c r="BW4" s="152"/>
       <c r="BX4" s="152"/>
       <c r="BY4" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BZ4" s="11"/>
       <c r="CA4" s="11"/>
@@ -10776,7 +10766,7 @@
       <c r="AN5" s="130"/>
       <c r="AO5" s="12"/>
       <c r="AR5" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BB5" s="147"/>
       <c r="BC5" s="147"/>
@@ -10793,7 +10783,7 @@
       <c r="BN5" s="147"/>
       <c r="BO5" s="147"/>
       <c r="BP5" s="52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BV5" s="11"/>
       <c r="BW5" s="47"/>
@@ -10824,7 +10814,7 @@
       <c r="AZ6" s="127"/>
       <c r="BA6" s="127"/>
       <c r="BB6" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BC6" s="148"/>
       <c r="BD6" s="148"/>
@@ -10832,7 +10822,7 @@
       <c r="BF6" s="148"/>
       <c r="BG6" s="148"/>
       <c r="BH6" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BI6" s="127"/>
       <c r="BJ6" s="127"/>
@@ -10861,12 +10851,12 @@
       <c r="Q7" s="70"/>
       <c r="R7" s="12"/>
       <c r="AR7" s="65" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AS7" s="85"/>
       <c r="AT7" s="85"/>
       <c r="AU7" s="147" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AV7" s="147"/>
       <c r="AW7" s="147"/>
@@ -10888,7 +10878,7 @@
       <c r="BM7" s="127"/>
       <c r="BN7" s="43"/>
       <c r="BP7" s="118" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:82" x14ac:dyDescent="0.25">
@@ -10898,7 +10888,7 @@
       <c r="Q8" s="70"/>
       <c r="R8" s="12"/>
       <c r="AR8" s="150" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AS8" s="150"/>
       <c r="AT8" s="150"/>
@@ -10947,7 +10937,7 @@
       <c r="H9" s="128"/>
       <c r="I9" s="128"/>
       <c r="AR9" s="150" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AS9" s="150"/>
       <c r="AT9" s="150"/>
@@ -11022,7 +11012,7 @@
       <c r="AO10" s="128"/>
       <c r="AP10" s="128"/>
       <c r="AR10" s="150" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AS10" s="150"/>
       <c r="AT10" s="150"/>
@@ -11181,12 +11171,12 @@
       <c r="AV13" s="133"/>
       <c r="AW13" s="133"/>
       <c r="AX13" s="156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AY13" s="157"/>
       <c r="AZ13" s="59"/>
       <c r="BA13" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BB13" s="158"/>
       <c r="BC13" s="132" t="s">
@@ -11209,12 +11199,12 @@
       <c r="BN13" s="135"/>
       <c r="BO13" s="135"/>
       <c r="BP13" s="156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="BQ13" s="157"/>
       <c r="BR13" s="59"/>
       <c r="BS13" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BT13" s="158"/>
       <c r="BU13" s="135" t="s">
@@ -11308,12 +11298,12 @@
       <c r="E15" s="133"/>
       <c r="F15" s="133"/>
       <c r="G15" s="156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H15" s="157"/>
       <c r="I15" s="76"/>
       <c r="J15" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K15" s="158"/>
       <c r="L15" s="132" t="s">
@@ -11336,12 +11326,12 @@
       <c r="W15" s="135"/>
       <c r="X15" s="135"/>
       <c r="Y15" s="156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Z15" s="157"/>
       <c r="AA15" s="76"/>
       <c r="AB15" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC15" s="158"/>
       <c r="AD15" s="135" t="s">
@@ -11860,11 +11850,11 @@
       <c r="AI21" s="145"/>
       <c r="AJ21" s="146"/>
       <c r="AR21" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BK21" s="12"/>
       <c r="BL21" s="65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:79" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -12075,12 +12065,12 @@
       <c r="AV24" s="133"/>
       <c r="AW24" s="133"/>
       <c r="AX24" s="156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AY24" s="157"/>
       <c r="AZ24" s="59"/>
       <c r="BA24" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BB24" s="158"/>
       <c r="BC24" s="132" t="s">
@@ -12103,12 +12093,12 @@
       <c r="BN24" s="135"/>
       <c r="BO24" s="135"/>
       <c r="BP24" s="156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="BQ24" s="157"/>
       <c r="BR24" s="59"/>
       <c r="BS24" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BT24" s="158"/>
       <c r="BU24" s="135" t="s">
@@ -12547,11 +12537,11 @@
     </row>
     <row r="30" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T30" s="12"/>
       <c r="U30" s="65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AR30" s="132" t="s">
         <v>72</v>
@@ -12652,11 +12642,11 @@
       <c r="H32" s="128"/>
       <c r="I32" s="128"/>
       <c r="AR32" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BK32" s="12"/>
       <c r="BL32" s="65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.25">
@@ -12798,7 +12788,7 @@
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F40" s="128"/>
       <c r="G40" s="128"/>
@@ -14357,7 +14347,7 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="117"/>
       <c r="C4" s="117"/>
@@ -14374,12 +14364,12 @@
       <c r="N4" s="147"/>
       <c r="O4" s="147"/>
       <c r="P4" s="117" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q4" s="117"/>
       <c r="R4" s="117"/>
       <c r="S4" s="152" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T4" s="152"/>
       <c r="U4" s="152"/>
@@ -14397,7 +14387,7 @@
       <c r="AG4" s="152"/>
       <c r="AH4" s="152"/>
       <c r="AI4" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="11"/>
@@ -14407,7 +14397,7 @@
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -14432,7 +14422,7 @@
       <c r="V5" s="147"/>
       <c r="W5" s="147"/>
       <c r="X5" s="52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y5" s="8"/>
       <c r="Z5" s="8"/>
@@ -14459,10 +14449,10 @@
       <c r="E6" s="127"/>
       <c r="F6" s="127"/>
       <c r="G6" s="47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H6" s="159" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I6" s="159"/>
       <c r="J6" s="160"/>
@@ -14538,7 +14528,7 @@
       <c r="AL7" s="43"/>
       <c r="AM7" s="43"/>
       <c r="AN7" s="62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO7" s="60"/>
     </row>
@@ -14559,39 +14549,39 @@
       <c r="N8" s="158"/>
       <c r="O8" s="158"/>
       <c r="P8" s="175" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q8" s="158"/>
       <c r="R8" s="158"/>
       <c r="S8" s="158"/>
       <c r="T8" s="163"/>
       <c r="U8" s="161" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V8" s="161"/>
       <c r="W8" s="59"/>
       <c r="X8" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y8" s="158"/>
       <c r="Z8" s="162" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA8" s="161"/>
       <c r="AB8" s="88"/>
       <c r="AC8" s="158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD8" s="163"/>
       <c r="AE8" s="162" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF8" s="161"/>
       <c r="AG8" s="161"/>
       <c r="AH8" s="161"/>
       <c r="AI8" s="176"/>
       <c r="AJ8" s="162" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AK8" s="161"/>
       <c r="AL8" s="161"/>
@@ -14620,14 +14610,14 @@
       <c r="S9" s="169"/>
       <c r="T9" s="171"/>
       <c r="U9" s="168" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V9" s="169"/>
       <c r="W9" s="169"/>
       <c r="X9" s="169"/>
       <c r="Y9" s="169"/>
       <c r="Z9" s="170" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA9" s="169"/>
       <c r="AB9" s="169"/>
@@ -14678,27 +14668,27 @@
       <c r="AC10" s="166"/>
       <c r="AD10" s="167"/>
       <c r="AE10" s="164" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF10" s="165"/>
       <c r="AG10" s="59"/>
       <c r="AH10" s="166" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI10" s="167"/>
       <c r="AJ10" s="165" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK10" s="165"/>
       <c r="AL10" s="61"/>
       <c r="AM10" s="166" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN10" s="167"/>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B11" s="33"/>
       <c r="C11" s="33"/>
@@ -14742,7 +14732,7 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G12" s="47"/>
       <c r="H12" s="47"/>
@@ -14778,7 +14768,7 @@
     </row>
     <row r="13" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G13" s="47"/>
       <c r="H13" s="47"/>
@@ -14814,7 +14804,7 @@
     </row>
     <row r="14" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="47"/>
       <c r="H14" s="47"/>
@@ -14850,7 +14840,7 @@
     </row>
     <row r="15" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" s="47"/>
       <c r="H15" s="47"/>
@@ -14886,7 +14876,7 @@
     </row>
     <row r="16" spans="1:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="47"/>
@@ -14922,7 +14912,7 @@
     </row>
     <row r="17" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G17" s="47"/>
       <c r="H17" s="47"/>
@@ -14958,7 +14948,7 @@
     </row>
     <row r="18" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G18" s="47"/>
       <c r="H18" s="47"/>
@@ -14994,7 +14984,7 @@
     </row>
     <row r="19" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G19" s="47"/>
       <c r="H19" s="47"/>
@@ -15030,7 +15020,7 @@
     </row>
     <row r="20" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G20" s="47"/>
       <c r="H20" s="47"/>
@@ -15066,7 +15056,7 @@
     </row>
     <row r="21" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="47"/>
       <c r="H21" s="47"/>
@@ -15102,7 +15092,7 @@
     </row>
     <row r="22" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22" s="47"/>
       <c r="H22" s="47"/>
@@ -15138,7 +15128,7 @@
     </row>
     <row r="23" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G23" s="47"/>
       <c r="H23" s="47"/>
@@ -15174,7 +15164,7 @@
     </row>
     <row r="24" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G24" s="47"/>
       <c r="H24" s="47"/>
@@ -15210,7 +15200,7 @@
     </row>
     <row r="25" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G25" s="47"/>
       <c r="H25" s="47"/>
@@ -15246,7 +15236,7 @@
     </row>
     <row r="26" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="49"/>
       <c r="C26" s="49"/>
@@ -15290,7 +15280,7 @@
     </row>
     <row r="27" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G27" s="47"/>
       <c r="H27" s="47"/>
@@ -15326,7 +15316,7 @@
     </row>
     <row r="28" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G28" s="47"/>
       <c r="H28" s="47"/>
@@ -15362,7 +15352,7 @@
     </row>
     <row r="29" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G29" s="47"/>
       <c r="H29" s="47"/>
@@ -15398,7 +15388,7 @@
     </row>
     <row r="30" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G30" s="47"/>
       <c r="H30" s="47"/>
@@ -15434,7 +15424,7 @@
     </row>
     <row r="31" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G31" s="47"/>
       <c r="H31" s="47"/>
@@ -15470,7 +15460,7 @@
     </row>
     <row r="32" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G32" s="47"/>
       <c r="H32" s="47"/>
@@ -15506,7 +15496,7 @@
     </row>
     <row r="33" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G33" s="47"/>
       <c r="H33" s="47"/>
@@ -15542,7 +15532,7 @@
     </row>
     <row r="34" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G34" s="47"/>
       <c r="H34" s="47"/>
@@ -15578,7 +15568,7 @@
     </row>
     <row r="35" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
@@ -15906,7 +15896,7 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N1" s="127"/>
       <c r="O1" s="127"/>
@@ -15989,7 +15979,7 @@
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="117"/>
       <c r="C4" s="117"/>
@@ -16006,12 +15996,12 @@
       <c r="N4" s="147"/>
       <c r="O4" s="147"/>
       <c r="P4" s="117" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q4" s="117"/>
       <c r="R4" s="117"/>
       <c r="S4" s="152" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T4" s="152"/>
       <c r="U4" s="152"/>
@@ -16029,7 +16019,7 @@
       <c r="AG4" s="152"/>
       <c r="AH4" s="152"/>
       <c r="AI4" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="11"/>
@@ -16040,7 +16030,7 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J5" s="147"/>
       <c r="K5" s="147"/>
@@ -16057,7 +16047,7 @@
       <c r="V5" s="147"/>
       <c r="W5" s="147"/>
       <c r="X5" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AE5" s="47"/>
@@ -16079,10 +16069,10 @@
       <c r="E6" s="127"/>
       <c r="F6" s="127"/>
       <c r="G6" s="47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H6" s="159" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I6" s="159"/>
       <c r="J6" s="160"/>
@@ -16163,7 +16153,7 @@
     </row>
     <row r="8" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="186" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B8" s="187"/>
       <c r="C8" s="187"/>
@@ -16180,39 +16170,39 @@
       <c r="N8" s="105"/>
       <c r="O8" s="105"/>
       <c r="P8" s="190" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q8" s="191"/>
       <c r="R8" s="191"/>
       <c r="S8" s="191"/>
       <c r="T8" s="192"/>
       <c r="U8" s="197" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V8" s="197"/>
       <c r="W8" s="101"/>
       <c r="X8" s="191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y8" s="191"/>
       <c r="Z8" s="198" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA8" s="197"/>
       <c r="AB8" s="101"/>
       <c r="AC8" s="191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD8" s="192"/>
       <c r="AE8" s="198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF8" s="197"/>
       <c r="AG8" s="197"/>
       <c r="AH8" s="197"/>
       <c r="AI8" s="200"/>
       <c r="AJ8" s="198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AK8" s="197"/>
       <c r="AL8" s="197"/>
@@ -16243,14 +16233,14 @@
       <c r="S9" s="193"/>
       <c r="T9" s="194"/>
       <c r="U9" s="204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V9" s="193"/>
       <c r="W9" s="193"/>
       <c r="X9" s="193"/>
       <c r="Y9" s="193"/>
       <c r="Z9" s="204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA9" s="193"/>
       <c r="AB9" s="193"/>
@@ -16303,27 +16293,27 @@
       <c r="AC10" s="195"/>
       <c r="AD10" s="195"/>
       <c r="AE10" s="205" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF10" s="195"/>
       <c r="AG10" s="100"/>
       <c r="AH10" s="195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI10" s="196"/>
       <c r="AJ10" s="205" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK10" s="195"/>
       <c r="AL10" s="100"/>
       <c r="AM10" s="195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN10" s="196"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="107" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="108"/>
@@ -16367,7 +16357,7 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G12" s="86"/>
       <c r="H12" s="86"/>
@@ -16406,7 +16396,7 @@
     </row>
     <row r="13" spans="1:44" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="110" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G13" s="86"/>
       <c r="H13" s="86"/>
@@ -16445,7 +16435,7 @@
     </row>
     <row r="14" spans="1:44" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="110" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G14" s="86"/>
       <c r="H14" s="86"/>
@@ -16484,7 +16474,7 @@
     </row>
     <row r="15" spans="1:44" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B15" s="74"/>
       <c r="C15" s="74"/>
@@ -16570,7 +16560,7 @@
     </row>
     <row r="17" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="186" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B17" s="187"/>
       <c r="C17" s="187"/>
@@ -16587,39 +16577,39 @@
       <c r="N17" s="105"/>
       <c r="O17" s="105"/>
       <c r="P17" s="190" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q17" s="191"/>
       <c r="R17" s="191"/>
       <c r="S17" s="191"/>
       <c r="T17" s="192"/>
       <c r="U17" s="197" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V17" s="197"/>
       <c r="W17" s="101"/>
       <c r="X17" s="191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y17" s="191"/>
       <c r="Z17" s="198" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA17" s="197"/>
       <c r="AB17" s="101"/>
       <c r="AC17" s="191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD17" s="192"/>
       <c r="AE17" s="198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF17" s="197"/>
       <c r="AG17" s="197"/>
       <c r="AH17" s="197"/>
       <c r="AI17" s="200"/>
       <c r="AJ17" s="198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AK17" s="197"/>
       <c r="AL17" s="197"/>
@@ -16648,14 +16638,14 @@
       <c r="S18" s="193"/>
       <c r="T18" s="194"/>
       <c r="U18" s="204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V18" s="193"/>
       <c r="W18" s="193"/>
       <c r="X18" s="193"/>
       <c r="Y18" s="193"/>
       <c r="Z18" s="204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA18" s="193"/>
       <c r="AB18" s="193"/>
@@ -16706,27 +16696,27 @@
       <c r="AC19" s="195"/>
       <c r="AD19" s="195"/>
       <c r="AE19" s="205" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF19" s="195"/>
       <c r="AG19" s="101"/>
       <c r="AH19" s="195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI19" s="196"/>
       <c r="AJ19" s="205" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK19" s="195"/>
       <c r="AL19" s="100"/>
       <c r="AM19" s="195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN19" s="196"/>
     </row>
     <row r="20" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="107" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B20" s="108"/>
       <c r="C20" s="108"/>
@@ -16770,7 +16760,7 @@
     </row>
     <row r="21" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="113" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G21" s="86"/>
       <c r="H21" s="86"/>
@@ -16806,7 +16796,7 @@
     </row>
     <row r="22" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="110" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G22" s="86"/>
       <c r="H22" s="86"/>
@@ -16842,7 +16832,7 @@
     </row>
     <row r="23" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="110" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G23" s="86"/>
       <c r="H23" s="86"/>
@@ -16878,7 +16868,7 @@
     </row>
     <row r="24" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="111" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
@@ -16964,7 +16954,7 @@
     </row>
     <row r="26" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="186" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B26" s="187"/>
       <c r="C26" s="187"/>
@@ -16981,39 +16971,39 @@
       <c r="N26" s="105"/>
       <c r="O26" s="105"/>
       <c r="P26" s="190" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q26" s="191"/>
       <c r="R26" s="191"/>
       <c r="S26" s="191"/>
       <c r="T26" s="192"/>
       <c r="U26" s="197" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V26" s="197"/>
       <c r="W26" s="101"/>
       <c r="X26" s="191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y26" s="191"/>
       <c r="Z26" s="198" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA26" s="197"/>
       <c r="AB26" s="101"/>
       <c r="AC26" s="191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD26" s="192"/>
       <c r="AE26" s="198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF26" s="197"/>
       <c r="AG26" s="197"/>
       <c r="AH26" s="197"/>
       <c r="AI26" s="200"/>
       <c r="AJ26" s="198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AK26" s="197"/>
       <c r="AL26" s="197"/>
@@ -17042,14 +17032,14 @@
       <c r="S27" s="193"/>
       <c r="T27" s="194"/>
       <c r="U27" s="204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V27" s="193"/>
       <c r="W27" s="193"/>
       <c r="X27" s="193"/>
       <c r="Y27" s="193"/>
       <c r="Z27" s="204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA27" s="193"/>
       <c r="AB27" s="193"/>
@@ -17100,27 +17090,27 @@
       <c r="AC28" s="195"/>
       <c r="AD28" s="195"/>
       <c r="AE28" s="205" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF28" s="195"/>
       <c r="AG28" s="101"/>
       <c r="AH28" s="195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI28" s="196"/>
       <c r="AJ28" s="205" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK28" s="195"/>
       <c r="AL28" s="100"/>
       <c r="AM28" s="195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN28" s="196"/>
     </row>
     <row r="29" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="107" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B29" s="108"/>
       <c r="C29" s="108"/>
@@ -17164,7 +17154,7 @@
     </row>
     <row r="30" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="110" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G30" s="86"/>
       <c r="H30" s="86"/>
@@ -17203,7 +17193,7 @@
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="110" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G31" s="86"/>
       <c r="H31" s="86"/>
@@ -17242,7 +17232,7 @@
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="110" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G32" s="86"/>
       <c r="H32" s="86"/>
@@ -17281,7 +17271,7 @@
     </row>
     <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="110" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G33" s="86"/>
       <c r="H33" s="86"/>
@@ -17320,7 +17310,7 @@
     </row>
     <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="111" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
@@ -17398,7 +17388,7 @@
     </row>
     <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="96" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G36" s="86"/>
       <c r="H36" s="86"/>
@@ -17434,7 +17424,7 @@
     </row>
     <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="96" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G37" s="86"/>
       <c r="H37" s="86"/>
@@ -17504,7 +17494,7 @@
     </row>
     <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="103" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G39" s="86"/>
       <c r="H39" s="86"/>
@@ -17928,7 +17918,7 @@
         <v>0</v>
       </c>
       <c r="AR1" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BC1" s="147"/>
       <c r="BD1" s="147"/>
@@ -17958,10 +17948,10 @@
     </row>
     <row r="2" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AR2" s="25" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:79" x14ac:dyDescent="0.25">
@@ -18026,7 +18016,7 @@
       <c r="AY4" s="147"/>
       <c r="AZ4" s="147"/>
       <c r="BA4" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="BB4" s="38"/>
       <c r="BC4" s="38"/>
@@ -18066,7 +18056,7 @@
       <c r="Q6" s="121"/>
       <c r="R6" s="41"/>
       <c r="AR6" s="227" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AS6" s="227"/>
       <c r="AT6" s="227"/>
@@ -18115,7 +18105,7 @@
       <c r="H7" s="220"/>
       <c r="I7" s="220"/>
       <c r="AR7" s="227" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AS7" s="227"/>
       <c r="AT7" s="227"/>
@@ -18190,7 +18180,7 @@
       <c r="AO8" s="220"/>
       <c r="AP8" s="220"/>
       <c r="AR8" s="227" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AS8" s="227"/>
       <c r="AT8" s="227"/>
@@ -18292,19 +18282,19 @@
       <c r="AS11" s="212"/>
       <c r="AT11" s="213"/>
       <c r="AU11" s="222" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AV11" s="222"/>
       <c r="AW11" s="222"/>
       <c r="AX11" s="221" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AY11" s="222"/>
       <c r="AZ11" s="61">
         <v>1</v>
       </c>
       <c r="BA11" s="222" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="BB11" s="223"/>
       <c r="BC11" s="209" t="s">
@@ -18314,7 +18304,7 @@
       <c r="BE11" s="210"/>
       <c r="BF11" s="180"/>
       <c r="BG11" s="221" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="BH11" s="222"/>
       <c r="BI11" s="223"/>
@@ -18322,19 +18312,19 @@
       <c r="BK11" s="212"/>
       <c r="BL11" s="213"/>
       <c r="BM11" s="224" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BN11" s="224"/>
       <c r="BO11" s="224"/>
       <c r="BP11" s="221" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="BQ11" s="222"/>
       <c r="BR11" s="61">
         <v>1</v>
       </c>
       <c r="BS11" s="222" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="BT11" s="223"/>
       <c r="BU11" s="181" t="s">
@@ -18344,7 +18334,7 @@
       <c r="BW11" s="181"/>
       <c r="BX11" s="181"/>
       <c r="BY11" s="224" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="BZ11" s="224"/>
       <c r="CA11" s="224"/>
@@ -18363,25 +18353,25 @@
       <c r="AS12" s="218"/>
       <c r="AT12" s="184"/>
       <c r="AU12" s="222" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AV12" s="222"/>
       <c r="AW12" s="222"/>
       <c r="AX12" s="221" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AY12" s="222"/>
       <c r="AZ12" s="222"/>
       <c r="BA12" s="222"/>
       <c r="BB12" s="223"/>
       <c r="BC12" s="221" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BD12" s="222"/>
       <c r="BE12" s="222"/>
       <c r="BF12" s="223"/>
       <c r="BG12" s="221" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BH12" s="222"/>
       <c r="BI12" s="223"/>
@@ -18389,25 +18379,25 @@
       <c r="BK12" s="218"/>
       <c r="BL12" s="184"/>
       <c r="BM12" s="224" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="BN12" s="224"/>
       <c r="BO12" s="224"/>
       <c r="BP12" s="224" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="BQ12" s="224"/>
       <c r="BR12" s="224"/>
       <c r="BS12" s="224"/>
       <c r="BT12" s="224"/>
       <c r="BU12" s="224" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BV12" s="224"/>
       <c r="BW12" s="224"/>
       <c r="BX12" s="224"/>
       <c r="BY12" s="224" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BZ12" s="224"/>
       <c r="CA12" s="224"/>
@@ -18427,7 +18417,7 @@
         <v>38</v>
       </c>
       <c r="AR13" s="221" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AS13" s="210"/>
       <c r="AT13" s="180"/>
@@ -18447,7 +18437,7 @@
       <c r="BH13" s="212"/>
       <c r="BI13" s="213"/>
       <c r="BJ13" s="221" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="BK13" s="210"/>
       <c r="BL13" s="180"/>
@@ -18484,7 +18474,7 @@
         <v>34</v>
       </c>
       <c r="AR14" s="221" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AS14" s="210"/>
       <c r="AT14" s="180"/>
@@ -18504,7 +18494,7 @@
       <c r="BH14" s="215"/>
       <c r="BI14" s="216"/>
       <c r="BJ14" s="221" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="BK14" s="210"/>
       <c r="BL14" s="180"/>
@@ -18535,7 +18525,7 @@
       <c r="H15" s="220"/>
       <c r="I15" s="220"/>
       <c r="AR15" s="221" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AS15" s="210"/>
       <c r="AT15" s="180"/>
@@ -18555,7 +18545,7 @@
       <c r="BH15" s="218"/>
       <c r="BI15" s="184"/>
       <c r="BJ15" s="221" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="BK15" s="210"/>
       <c r="BL15" s="180"/>
@@ -18594,7 +18584,7 @@
         <v>44</v>
       </c>
       <c r="AR16" s="221" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AS16" s="210"/>
       <c r="AT16" s="180"/>
@@ -18614,7 +18604,7 @@
       <c r="BH16" s="212"/>
       <c r="BI16" s="213"/>
       <c r="BJ16" s="221" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="BK16" s="210"/>
       <c r="BL16" s="180"/>
@@ -18648,7 +18638,7 @@
       <c r="K17" s="215"/>
       <c r="L17" s="41"/>
       <c r="AR17" s="221" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AS17" s="210"/>
       <c r="AT17" s="180"/>
@@ -18668,7 +18658,7 @@
       <c r="BH17" s="215"/>
       <c r="BI17" s="216"/>
       <c r="BJ17" s="221" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="BK17" s="210"/>
       <c r="BL17" s="180"/>
@@ -18703,7 +18693,7 @@
         <v>46</v>
       </c>
       <c r="AR18" s="221" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AS18" s="210"/>
       <c r="AT18" s="180"/>
@@ -18723,7 +18713,7 @@
       <c r="BH18" s="218"/>
       <c r="BI18" s="184"/>
       <c r="BJ18" s="221" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="BK18" s="210"/>
       <c r="BL18" s="180"/>
@@ -18745,7 +18735,7 @@
     </row>
     <row r="19" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F19" s="220"/>
       <c r="G19" s="220"/>
@@ -18838,19 +18828,19 @@
       <c r="AS22" s="212"/>
       <c r="AT22" s="213"/>
       <c r="AU22" s="222" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AV22" s="222"/>
       <c r="AW22" s="222"/>
       <c r="AX22" s="221" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AY22" s="222"/>
       <c r="AZ22" s="61">
         <v>1</v>
       </c>
       <c r="BA22" s="222" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="BB22" s="223"/>
       <c r="BC22" s="209" t="s">
@@ -18860,7 +18850,7 @@
       <c r="BE22" s="210"/>
       <c r="BF22" s="180"/>
       <c r="BG22" s="221" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="BH22" s="222"/>
       <c r="BI22" s="223"/>
@@ -18868,19 +18858,19 @@
       <c r="BK22" s="212"/>
       <c r="BL22" s="213"/>
       <c r="BM22" s="224" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BN22" s="224"/>
       <c r="BO22" s="224"/>
       <c r="BP22" s="221" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="BQ22" s="222"/>
       <c r="BR22" s="61">
         <v>1</v>
       </c>
       <c r="BS22" s="222" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="BT22" s="223"/>
       <c r="BU22" s="181" t="s">
@@ -18890,7 +18880,7 @@
       <c r="BW22" s="181"/>
       <c r="BX22" s="181"/>
       <c r="BY22" s="224" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="BZ22" s="224"/>
       <c r="CA22" s="224"/>
@@ -18915,25 +18905,25 @@
       <c r="AS23" s="218"/>
       <c r="AT23" s="184"/>
       <c r="AU23" s="222" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AV23" s="222"/>
       <c r="AW23" s="222"/>
       <c r="AX23" s="221" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AY23" s="222"/>
       <c r="AZ23" s="222"/>
       <c r="BA23" s="222"/>
       <c r="BB23" s="223"/>
       <c r="BC23" s="221" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BD23" s="222"/>
       <c r="BE23" s="222"/>
       <c r="BF23" s="223"/>
       <c r="BG23" s="221" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BH23" s="222"/>
       <c r="BI23" s="223"/>
@@ -18941,32 +18931,32 @@
       <c r="BK23" s="218"/>
       <c r="BL23" s="184"/>
       <c r="BM23" s="224" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="BN23" s="224"/>
       <c r="BO23" s="224"/>
       <c r="BP23" s="224" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="BQ23" s="224"/>
       <c r="BR23" s="224"/>
       <c r="BS23" s="224"/>
       <c r="BT23" s="224"/>
       <c r="BU23" s="224" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BV23" s="224"/>
       <c r="BW23" s="224"/>
       <c r="BX23" s="224"/>
       <c r="BY23" s="224" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="BZ23" s="224"/>
       <c r="CA23" s="224"/>
     </row>
     <row r="24" spans="1:79" x14ac:dyDescent="0.25">
       <c r="AR24" s="221" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AS24" s="210"/>
       <c r="AT24" s="180"/>
@@ -18986,7 +18976,7 @@
       <c r="BH24" s="212"/>
       <c r="BI24" s="213"/>
       <c r="BJ24" s="221" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="BK24" s="210"/>
       <c r="BL24" s="180"/>
@@ -19016,7 +19006,7 @@
         <v>54</v>
       </c>
       <c r="AR25" s="221" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AS25" s="210"/>
       <c r="AT25" s="180"/>
@@ -19036,7 +19026,7 @@
       <c r="BH25" s="215"/>
       <c r="BI25" s="216"/>
       <c r="BJ25" s="221" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="BK25" s="210"/>
       <c r="BL25" s="180"/>
@@ -19073,7 +19063,7 @@
         <v>56</v>
       </c>
       <c r="AR26" s="221" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AS26" s="210"/>
       <c r="AT26" s="180"/>
@@ -19093,7 +19083,7 @@
       <c r="BH26" s="218"/>
       <c r="BI26" s="184"/>
       <c r="BJ26" s="221" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="BK26" s="210"/>
       <c r="BL26" s="180"/>
@@ -19127,7 +19117,7 @@
         <v>18</v>
       </c>
       <c r="AR27" s="221" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AS27" s="210"/>
       <c r="AT27" s="180"/>
@@ -19147,7 +19137,7 @@
       <c r="BH27" s="212"/>
       <c r="BI27" s="213"/>
       <c r="BJ27" s="221" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="BK27" s="210"/>
       <c r="BL27" s="180"/>
@@ -19169,7 +19159,7 @@
     </row>
     <row r="28" spans="1:79" x14ac:dyDescent="0.25">
       <c r="AR28" s="221" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AS28" s="210"/>
       <c r="AT28" s="180"/>
@@ -19189,7 +19179,7 @@
       <c r="BH28" s="215"/>
       <c r="BI28" s="216"/>
       <c r="BJ28" s="221" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="BK28" s="210"/>
       <c r="BL28" s="180"/>
@@ -19228,7 +19218,7 @@
       <c r="W29" s="220"/>
       <c r="X29" s="220"/>
       <c r="AR29" s="221" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AS29" s="210"/>
       <c r="AT29" s="180"/>
@@ -19248,7 +19238,7 @@
       <c r="BH29" s="218"/>
       <c r="BI29" s="184"/>
       <c r="BJ29" s="221" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="BK29" s="210"/>
       <c r="BL29" s="180"/>
@@ -20259,6 +20249,7 @@
     <mergeCell ref="BP13:BT13"/>
     <mergeCell ref="BU13:BX13"/>
     <mergeCell ref="BY13:CA15"/>
+    <mergeCell ref="BU14:BX14"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="H14:L14"/>
     <mergeCell ref="AR14:AT14"/>
@@ -20268,7 +20259,6 @@
     <mergeCell ref="BJ14:BL14"/>
     <mergeCell ref="BM14:BO14"/>
     <mergeCell ref="BP14:BT14"/>
-    <mergeCell ref="BU14:BX14"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="AR15:AT15"/>
     <mergeCell ref="AU15:AW15"/>
@@ -20474,12 +20464,6 @@
     <mergeCell ref="X48:AB48"/>
     <mergeCell ref="AC48:AG48"/>
     <mergeCell ref="AH48:AL48"/>
-    <mergeCell ref="X46:AB46"/>
-    <mergeCell ref="AC46:AG46"/>
-    <mergeCell ref="AH46:AL46"/>
-    <mergeCell ref="X51:AB51"/>
-    <mergeCell ref="AC51:AG51"/>
-    <mergeCell ref="AH51:AL51"/>
     <mergeCell ref="A52:AP52"/>
     <mergeCell ref="AC49:AG49"/>
     <mergeCell ref="AH49:AL49"/>
@@ -20501,6 +20485,12 @@
     <mergeCell ref="D51:H51"/>
     <mergeCell ref="I51:M51"/>
     <mergeCell ref="N51:R51"/>
+    <mergeCell ref="X46:AB46"/>
+    <mergeCell ref="AC46:AG46"/>
+    <mergeCell ref="AH46:AL46"/>
+    <mergeCell ref="X51:AB51"/>
+    <mergeCell ref="AC51:AG51"/>
+    <mergeCell ref="AH51:AL51"/>
   </mergeCells>
   <phoneticPr fontId="51" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -20538,7 +20528,7 @@
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P1" s="127"/>
       <c r="Q1" s="127"/>
@@ -20568,7 +20558,7 @@
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
@@ -20593,7 +20583,7 @@
       <c r="S3" s="199"/>
       <c r="T3" s="199"/>
       <c r="U3" s="91" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="V3" s="92"/>
       <c r="W3" s="92"/>
@@ -20675,7 +20665,7 @@
       </c>
       <c r="D5" s="246"/>
       <c r="E5" s="92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" s="92"/>
       <c r="G5" s="92"/>
@@ -20763,7 +20753,7 @@
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="96" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="95"/>
       <c r="C7" s="95"/>
@@ -20794,7 +20784,7 @@
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="235" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" s="236"/>
       <c r="C8" s="236"/>
@@ -20805,7 +20795,7 @@
       <c r="H8" s="236"/>
       <c r="I8" s="237"/>
       <c r="J8" s="233" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K8" s="233"/>
       <c r="L8" s="233"/>
@@ -20818,7 +20808,7 @@
       <c r="S8" s="233"/>
       <c r="T8" s="233"/>
       <c r="U8" s="233" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V8" s="233"/>
       <c r="W8" s="233"/>
@@ -20830,7 +20820,7 @@
       <c r="AC8" s="233"/>
       <c r="AD8" s="233"/>
       <c r="AE8" s="233" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AF8" s="233"/>
       <c r="AG8" s="233"/>
@@ -21012,17 +21002,17 @@
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="96" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="235" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="236"/>
       <c r="C15" s="236"/>
@@ -21033,7 +21023,7 @@
       <c r="H15" s="236"/>
       <c r="I15" s="237"/>
       <c r="J15" s="233" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K15" s="233"/>
       <c r="L15" s="233"/>
@@ -21046,7 +21036,7 @@
       <c r="S15" s="233"/>
       <c r="T15" s="233"/>
       <c r="U15" s="233" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V15" s="233"/>
       <c r="W15" s="233"/>
@@ -21058,7 +21048,7 @@
       <c r="AC15" s="233"/>
       <c r="AD15" s="233"/>
       <c r="AE15" s="233" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AF15" s="233"/>
       <c r="AG15" s="233"/>
@@ -21198,17 +21188,17 @@
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A20" s="96" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A21" s="235" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="236"/>
       <c r="C21" s="236"/>
@@ -21219,7 +21209,7 @@
       <c r="H21" s="236"/>
       <c r="I21" s="237"/>
       <c r="J21" s="235" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K21" s="236"/>
       <c r="L21" s="236"/>
@@ -21228,7 +21218,7 @@
       <c r="O21" s="236"/>
       <c r="P21" s="237"/>
       <c r="Q21" s="235" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R21" s="236"/>
       <c r="S21" s="236"/>
@@ -21236,7 +21226,7 @@
       <c r="U21" s="236"/>
       <c r="V21" s="236"/>
       <c r="W21" s="235" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X21" s="236"/>
       <c r="Y21" s="236"/>
@@ -21244,7 +21234,7 @@
       <c r="AA21" s="236"/>
       <c r="AB21" s="236"/>
       <c r="AC21" s="235" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AD21" s="236"/>
       <c r="AE21" s="236"/>
@@ -21252,7 +21242,7 @@
       <c r="AG21" s="236"/>
       <c r="AH21" s="237"/>
       <c r="AI21" s="235" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AJ21" s="236"/>
       <c r="AK21" s="236"/>
@@ -21388,7 +21378,7 @@
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B25" s="97"/>
       <c r="C25" s="97"/>
@@ -21432,12 +21422,12 @@
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A26" s="96" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A27" s="235" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="236"/>
       <c r="C27" s="236"/>
@@ -21448,7 +21438,7 @@
       <c r="H27" s="236"/>
       <c r="I27" s="237"/>
       <c r="J27" s="233" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K27" s="233"/>
       <c r="L27" s="233"/>
@@ -21461,7 +21451,7 @@
       <c r="S27" s="233"/>
       <c r="T27" s="233"/>
       <c r="U27" s="233" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="V27" s="233"/>
       <c r="W27" s="233"/>
@@ -21473,7 +21463,7 @@
       <c r="AC27" s="233"/>
       <c r="AD27" s="233"/>
       <c r="AE27" s="233" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AF27" s="233"/>
       <c r="AG27" s="233"/>
@@ -21662,7 +21652,7 @@
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B32" s="97"/>
       <c r="C32" s="97"/>
@@ -21752,7 +21742,7 @@
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q34" s="127"/>
       <c r="R34" s="127"/>
@@ -21767,7 +21757,7 @@
       <c r="AA34" s="127"/>
       <c r="AB34" s="127"/>
       <c r="AC34" s="52" t="s">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AD34" s="52"/>
       <c r="AE34" s="43"/>
@@ -21796,7 +21786,7 @@
       <c r="O35" s="127"/>
       <c r="P35" s="127"/>
       <c r="Q35" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R35" s="127"/>
       <c r="S35" s="127"/>
@@ -21810,7 +21800,7 @@
       <c r="AA35" s="127"/>
       <c r="AB35" s="127"/>
       <c r="AC35" s="52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AD35" s="147"/>
       <c r="AE35" s="147"/>
@@ -21818,7 +21808,7 @@
       <c r="AG35" s="147"/>
       <c r="AH35" s="147"/>
       <c r="AI35" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AJ35" s="86"/>
       <c r="AK35" s="86"/>
@@ -21872,7 +21862,7 @@
     <row r="37" spans="1:42" ht="5.4" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="G44" s="98" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H44" s="98"/>
       <c r="I44" s="98"/>
@@ -21888,7 +21878,7 @@
       <c r="S44" s="98"/>
       <c r="T44" s="98"/>
       <c r="AB44" s="98" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:42" ht="5.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -21914,7 +21904,7 @@
     <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="98" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B52" s="98"/>
       <c r="C52" s="98"/>
@@ -21929,7 +21919,7 @@
       <c r="L52" s="98"/>
       <c r="N52" s="94"/>
       <c r="Q52" s="98" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V52" s="98"/>
       <c r="W52" s="98"/>
@@ -21939,7 +21929,7 @@
       <c r="AB52" s="94"/>
       <c r="AD52" s="98"/>
       <c r="AE52" s="98" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AF52" s="98"/>
       <c r="AG52" s="98"/>
@@ -21948,10 +21938,10 @@
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="99"/>
       <c r="C53" s="98" t="s">
+        <v>225</v>
+      </c>
+      <c r="S53" s="98" t="s">
         <v>226</v>
-      </c>
-      <c r="S53" s="98" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22098,7 +22088,7 @@
     </row>
     <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
@@ -22139,15 +22129,15 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H4" s="1"/>
       <c r="K4" s="1"/>
@@ -22160,7 +22150,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -22169,7 +22159,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="31"/>
       <c r="H5" s="1"/>
@@ -22178,7 +22168,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="2"/>
       <c r="M5" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="1"/>
@@ -22229,7 +22219,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="254" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" s="255"/>
       <c r="C8" s="256"/>
@@ -22251,7 +22241,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="261" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B9" s="249"/>
       <c r="C9" s="250"/>
@@ -22273,7 +22263,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="262" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B10" s="255"/>
       <c r="C10" s="256"/>
@@ -22295,7 +22285,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="262" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" s="255"/>
       <c r="C11" s="256"/>
@@ -22317,7 +22307,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="262" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12" s="255"/>
       <c r="C12" s="256"/>
@@ -22339,7 +22329,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="262" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="255"/>
       <c r="C13" s="256"/>
@@ -22361,7 +22351,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="261" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14" s="249"/>
       <c r="C14" s="250"/>
@@ -22383,7 +22373,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="261" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B15" s="249"/>
       <c r="C15" s="250"/>
@@ -22405,7 +22395,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -22467,7 +22457,7 @@
     </row>
     <row r="19" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -22530,7 +22520,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="248" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B22" s="249"/>
       <c r="C22" s="249"/>
@@ -22551,7 +22541,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="248" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B23" s="249"/>
       <c r="C23" s="250"/>
@@ -22572,7 +22562,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -22614,7 +22604,7 @@
     <row r="26" spans="1:18" ht="4.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -22631,7 +22621,7 @@
     </row>
     <row r="30" spans="1:18" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="119"/>
@@ -22673,7 +22663,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B32" s="36"/>
       <c r="C32" s="34"/>
@@ -22694,13 +22684,13 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="4.8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="38"/>
       <c r="M35" s="215"/>
@@ -22716,7 +22706,7 @@
     </row>
     <row r="37" spans="1:17" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="261" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="265"/>
       <c r="C37" s="266"/>
@@ -22737,7 +22727,7 @@
     </row>
     <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="262" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B38" s="267"/>
       <c r="C38" s="268"/>
@@ -22758,7 +22748,7 @@
     </row>
     <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="261" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B39" s="249"/>
       <c r="C39" s="250"/>
@@ -22779,7 +22769,7 @@
     </row>
     <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="262" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B40" s="255"/>
       <c r="C40" s="256"/>
@@ -22800,7 +22790,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="262" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B41" s="255"/>
       <c r="C41" s="256"/>
@@ -22821,7 +22811,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="262" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B42" s="255"/>
       <c r="C42" s="256"/>
@@ -22842,7 +22832,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="262" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B43" s="255"/>
       <c r="C43" s="256"/>
@@ -22863,7 +22853,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="261" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B44" s="249"/>
       <c r="C44" s="250"/>
@@ -22884,7 +22874,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="269" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B45" s="265"/>
       <c r="C45" s="266"/>
@@ -22905,7 +22895,7 @@
     </row>
     <row r="46" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -23127,7 +23117,7 @@
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -23141,7 +23131,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K4" s="11"/>
     </row>
@@ -23166,7 +23156,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="254" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B6" s="255"/>
       <c r="C6" s="256"/>
@@ -23185,7 +23175,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="254" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" s="255"/>
       <c r="C7" s="256"/>
@@ -23204,7 +23194,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="274" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B8" s="275"/>
       <c r="C8" s="276"/>
@@ -23223,7 +23213,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="274" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B9" s="275"/>
       <c r="C9" s="276"/>
@@ -23242,7 +23232,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="274" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B10" s="275"/>
       <c r="C10" s="276"/>
@@ -23261,7 +23251,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="274" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" s="275"/>
       <c r="C11" s="276"/>
@@ -23280,7 +23270,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="274" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" s="275"/>
       <c r="C12" s="276"/>
@@ -23299,7 +23289,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B13" s="275"/>
       <c r="C13" s="276"/>
@@ -23318,7 +23308,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -23342,7 +23332,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="254" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B16" s="255"/>
       <c r="C16" s="256"/>
@@ -23361,7 +23351,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="254" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B17" s="255"/>
       <c r="C17" s="256"/>
@@ -23380,7 +23370,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="274" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B18" s="275"/>
       <c r="C18" s="276"/>
@@ -23399,7 +23389,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="274" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B19" s="275"/>
       <c r="C19" s="276"/>
@@ -23418,7 +23408,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="274" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" s="275"/>
       <c r="C20" s="276"/>
@@ -23437,7 +23427,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="274" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" s="275"/>
       <c r="C21" s="276"/>
@@ -23456,7 +23446,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="274" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" s="275"/>
       <c r="C22" s="276"/>
@@ -23475,7 +23465,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B23" s="275"/>
       <c r="C23" s="276"/>
@@ -23494,13 +23484,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="7.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
@@ -23537,7 +23527,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="254" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" s="255"/>
       <c r="C29" s="256"/>
@@ -23556,7 +23546,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="254" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B30" s="255"/>
       <c r="C30" s="256"/>
@@ -23575,7 +23565,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="274" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B31" s="275"/>
       <c r="C31" s="276"/>
@@ -23594,7 +23584,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="274" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B32" s="275"/>
       <c r="C32" s="276"/>
@@ -23613,7 +23603,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="274" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="275"/>
       <c r="C33" s="276"/>
@@ -23632,7 +23622,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="274" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B34" s="275"/>
       <c r="C34" s="276"/>
@@ -23651,7 +23641,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="274" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B35" s="275"/>
       <c r="C35" s="276"/>
@@ -23670,7 +23660,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="274" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" s="275"/>
       <c r="C36" s="276"/>
@@ -23689,7 +23679,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -23697,7 +23687,7 @@
     </row>
     <row r="39" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -23713,19 +23703,19 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E41" s="151"/>
       <c r="F41" s="151"/>
       <c r="G41" s="151"/>
       <c r="H41" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="5.4" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="271" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B43" s="272"/>
       <c r="C43" s="273"/>
@@ -23744,7 +23734,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="270" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B44" s="270"/>
       <c r="C44" s="270"/>
@@ -23763,7 +23753,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -24021,7 +24011,7 @@
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H2" s="15"/>
     </row>
@@ -24033,12 +24023,12 @@
       <c r="E3" s="15"/>
       <c r="G3" s="16"/>
       <c r="H3" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="16"/>
       <c r="K3" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -24062,7 +24052,7 @@
     </row>
     <row r="5" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="289" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5" s="212"/>
       <c r="C5" s="213"/>
@@ -24081,7 +24071,7 @@
     </row>
     <row r="6" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="283" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B6" s="284"/>
       <c r="C6" s="285"/>
@@ -24117,7 +24107,7 @@
     </row>
     <row r="8" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="277" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" s="278"/>
       <c r="C8" s="279"/>
@@ -24136,7 +24126,7 @@
     </row>
     <row r="9" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="280" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="281"/>
       <c r="C9" s="282"/>
@@ -24155,7 +24145,7 @@
     </row>
     <row r="10" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="283" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B10" s="284"/>
       <c r="C10" s="285"/>
@@ -24191,7 +24181,7 @@
     </row>
     <row r="12" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="277" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12" s="278"/>
       <c r="C12" s="279"/>
@@ -24210,23 +24200,23 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" t="s">
         <v>162</v>
-      </c>
-      <c r="B14" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H15" s="147"/>
       <c r="I15" s="147"/>
@@ -24237,138 +24227,138 @@
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" s="147"/>
       <c r="C18" s="147"/>
     </row>
     <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="20" t="s">
         <v>164</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F20" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J20" s="23"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F21" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J21" s="23"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F22" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J22" s="23"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B24" s="147"/>
       <c r="C24" s="147"/>
     </row>
     <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" s="20" t="s">
         <v>164</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F26" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J26" s="23"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F27" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J27" s="23"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F28" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J28" s="23"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B30" s="147"/>
       <c r="C30" s="147"/>
     </row>
     <row r="31" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="20" t="s">
         <v>164</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F32" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J32" s="23"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F33" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J33" s="23"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F34" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J34" s="23"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="147"/>
       <c r="C36" s="147"/>
     </row>
     <row r="37" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F37" s="20" t="s">
         <v>164</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F38" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J38" s="23"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F39" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J39" s="23"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F40" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J40" s="23"/>
     </row>
